--- a/VA_result_ENE.xlsx
+++ b/VA_result_ENE.xlsx
@@ -2144,10 +2144,10 @@
         <v>26</v>
       </c>
       <c r="B98" t="n">
-        <v>1261292.76885855</v>
+        <v>1261292.76834057</v>
       </c>
       <c r="C98" t="n">
-        <v>126.129276885855</v>
+        <v>126.129276834057</v>
       </c>
     </row>
     <row r="99">
@@ -2155,10 +2155,10 @@
         <v>101</v>
       </c>
       <c r="B99" t="n">
-        <v>1273611.59100568</v>
+        <v>1273611.59062666</v>
       </c>
       <c r="C99" t="n">
-        <v>127.361159100568</v>
+        <v>127.361159062666</v>
       </c>
     </row>
     <row r="100">
@@ -2166,10 +2166,10 @@
         <v>102</v>
       </c>
       <c r="B100" t="n">
-        <v>1271370.00211277</v>
+        <v>1271370.0016308</v>
       </c>
       <c r="C100" t="n">
-        <v>127.137000211277</v>
+        <v>127.13700016308</v>
       </c>
     </row>
     <row r="101">
@@ -2177,10 +2177,10 @@
         <v>103</v>
       </c>
       <c r="B101" t="n">
-        <v>1307882.35075535</v>
+        <v>1307882.35024351</v>
       </c>
       <c r="C101" t="n">
-        <v>130.788235075535</v>
+        <v>130.788235024351</v>
       </c>
     </row>
     <row r="102">
@@ -2188,10 +2188,10 @@
         <v>104</v>
       </c>
       <c r="B102" t="n">
-        <v>1340678.60642513</v>
+        <v>1340678.60587972</v>
       </c>
       <c r="C102" t="n">
-        <v>134.067860642513</v>
+        <v>134.067860587972</v>
       </c>
     </row>
     <row r="103">
@@ -2199,10 +2199,10 @@
         <v>105</v>
       </c>
       <c r="B103" t="n">
-        <v>1328974.5247464</v>
+        <v>1328974.52417923</v>
       </c>
       <c r="C103" t="n">
-        <v>132.89745247464</v>
+        <v>132.897452417923</v>
       </c>
     </row>
     <row r="104">
@@ -2210,10 +2210,10 @@
         <v>106</v>
       </c>
       <c r="B104" t="n">
-        <v>1325711.50428996</v>
+        <v>1325711.50373124</v>
       </c>
       <c r="C104" t="n">
-        <v>132.571150428996</v>
+        <v>132.571150373124</v>
       </c>
     </row>
     <row r="105">
@@ -2221,10 +2221,10 @@
         <v>107</v>
       </c>
       <c r="B105" t="n">
-        <v>1377851.18454811</v>
+        <v>1377851.18393117</v>
       </c>
       <c r="C105" t="n">
-        <v>137.785118454811</v>
+        <v>137.785118393117</v>
       </c>
     </row>
     <row r="106">
@@ -2232,10 +2232,10 @@
         <v>108</v>
       </c>
       <c r="B106" t="n">
-        <v>1367345.37491873</v>
+        <v>1367345.37437951</v>
       </c>
       <c r="C106" t="n">
-        <v>136.734537491873</v>
+        <v>136.734537437951</v>
       </c>
     </row>
     <row r="107">
@@ -2243,10 +2243,10 @@
         <v>109</v>
       </c>
       <c r="B107" t="n">
-        <v>1369453.48693079</v>
+        <v>1369453.48624688</v>
       </c>
       <c r="C107" t="n">
-        <v>136.945348693079</v>
+        <v>136.945348624688</v>
       </c>
     </row>
     <row r="108">
@@ -2254,10 +2254,10 @@
         <v>110</v>
       </c>
       <c r="B108" t="n">
-        <v>1381101.27730878</v>
+        <v>1381101.27665598</v>
       </c>
       <c r="C108" t="n">
-        <v>138.110127730878</v>
+        <v>138.110127665598</v>
       </c>
     </row>
     <row r="109">
@@ -2265,10 +2265,10 @@
         <v>111</v>
       </c>
       <c r="B109" t="n">
-        <v>1441837.80708553</v>
+        <v>1441837.80638229</v>
       </c>
       <c r="C109" t="n">
-        <v>144.183780708553</v>
+        <v>144.183780638229</v>
       </c>
     </row>
     <row r="110">
@@ -2276,10 +2276,10 @@
         <v>112</v>
       </c>
       <c r="B110" t="n">
-        <v>1412511.235206</v>
+        <v>1412511.23452897</v>
       </c>
       <c r="C110" t="n">
-        <v>141.2511235206</v>
+        <v>141.251123452897</v>
       </c>
     </row>
     <row r="111">
@@ -2287,10 +2287,10 @@
         <v>113</v>
       </c>
       <c r="B111" t="n">
-        <v>1395198.53889187</v>
+        <v>1395198.53816163</v>
       </c>
       <c r="C111" t="n">
-        <v>139.519853889187</v>
+        <v>139.519853816163</v>
       </c>
     </row>
     <row r="112">
@@ -2298,10 +2298,10 @@
         <v>114</v>
       </c>
       <c r="B112" t="n">
-        <v>1437445.60758845</v>
+        <v>1437445.60682481</v>
       </c>
       <c r="C112" t="n">
-        <v>143.744560758845</v>
+        <v>143.744560682481</v>
       </c>
     </row>
     <row r="113">
@@ -2309,10 +2309,10 @@
         <v>115</v>
       </c>
       <c r="B113" t="n">
-        <v>1499730.70911503</v>
+        <v>1499730.708345</v>
       </c>
       <c r="C113" t="n">
-        <v>149.973070911503</v>
+        <v>149.9730708345</v>
       </c>
     </row>
     <row r="114">
@@ -2320,10 +2320,10 @@
         <v>116</v>
       </c>
       <c r="B114" t="n">
-        <v>1476261.53789072</v>
+        <v>1476261.53693146</v>
       </c>
       <c r="C114" t="n">
-        <v>147.626153789072</v>
+        <v>147.626153693146</v>
       </c>
     </row>
     <row r="115">
@@ -2331,10 +2331,10 @@
         <v>117</v>
       </c>
       <c r="B115" t="n">
-        <v>1488580.36003857</v>
+        <v>1488580.35921825</v>
       </c>
       <c r="C115" t="n">
-        <v>148.858036003857</v>
+        <v>148.858035921825</v>
       </c>
     </row>
     <row r="116">
@@ -2342,10 +2342,10 @@
         <v>118</v>
       </c>
       <c r="B116" t="n">
-        <v>1486338.77114574</v>
+        <v>1486338.77022248</v>
       </c>
       <c r="C116" t="n">
-        <v>148.633877114574</v>
+        <v>148.633877022248</v>
       </c>
     </row>
     <row r="117">
@@ -2353,10 +2353,10 @@
         <v>119</v>
       </c>
       <c r="B117" t="n">
-        <v>1522851.11978972</v>
+        <v>1522851.11883658</v>
       </c>
       <c r="C117" t="n">
-        <v>152.285111978972</v>
+        <v>152.285111883658</v>
       </c>
     </row>
     <row r="118">
@@ -2364,10 +2364,10 @@
         <v>120</v>
       </c>
       <c r="B118" t="n">
-        <v>1555647.37545958</v>
+        <v>1555647.37447288</v>
       </c>
       <c r="C118" t="n">
-        <v>155.564737545958</v>
+        <v>155.564737447288</v>
       </c>
     </row>
     <row r="119">
@@ -2375,10 +2375,10 @@
         <v>121</v>
       </c>
       <c r="B119" t="n">
-        <v>1543943.29377965</v>
+        <v>1543943.29277118</v>
       </c>
       <c r="C119" t="n">
-        <v>154.394329377965</v>
+        <v>154.394329277118</v>
       </c>
     </row>
     <row r="120">
@@ -2386,10 +2386,10 @@
         <v>122</v>
       </c>
       <c r="B120" t="n">
-        <v>1540680.27332502</v>
+        <v>1540680.27232501</v>
       </c>
       <c r="C120" t="n">
-        <v>154.068027332502</v>
+        <v>154.068027232501</v>
       </c>
     </row>
     <row r="121">
@@ -2397,10 +2397,10 @@
         <v>123</v>
       </c>
       <c r="B121" t="n">
-        <v>1592819.95358033</v>
+        <v>1592819.95252209</v>
       </c>
       <c r="C121" t="n">
-        <v>159.281995358033</v>
+        <v>159.281995252209</v>
       </c>
     </row>
     <row r="122">
@@ -2408,10 +2408,10 @@
         <v>124</v>
       </c>
       <c r="B122" t="n">
-        <v>1582314.14395162</v>
+        <v>1582314.14297111</v>
       </c>
       <c r="C122" t="n">
-        <v>158.231414395162</v>
+        <v>158.231414297111</v>
       </c>
     </row>
     <row r="123">
@@ -2419,10 +2419,10 @@
         <v>125</v>
       </c>
       <c r="B123" t="n">
-        <v>1584422.25596415</v>
+        <v>1584422.25483895</v>
       </c>
       <c r="C123" t="n">
-        <v>158.442225596415</v>
+        <v>158.442225483895</v>
       </c>
     </row>
     <row r="124">
@@ -2430,10 +2430,10 @@
         <v>126</v>
       </c>
       <c r="B124" t="n">
-        <v>1596070.04634369</v>
+        <v>1596070.04524959</v>
       </c>
       <c r="C124" t="n">
-        <v>159.607004634369</v>
+        <v>159.607004524959</v>
       </c>
     </row>
     <row r="125">
@@ -2441,10 +2441,10 @@
         <v>127</v>
       </c>
       <c r="B125" t="n">
-        <v>1656806.57611901</v>
+        <v>1656806.57497447</v>
       </c>
       <c r="C125" t="n">
-        <v>165.680657611901</v>
+        <v>165.680657497447</v>
       </c>
     </row>
     <row r="126">
@@ -2452,10 +2452,10 @@
         <v>128</v>
       </c>
       <c r="B126" t="n">
-        <v>1627480.00423924</v>
+        <v>1627480.00312092</v>
       </c>
       <c r="C126" t="n">
-        <v>162.748000423924</v>
+        <v>162.748000312092</v>
       </c>
     </row>
     <row r="127">
@@ -2463,10 +2463,10 @@
         <v>129</v>
       </c>
       <c r="B127" t="n">
-        <v>1610167.30792618</v>
+        <v>1610167.30675465</v>
       </c>
       <c r="C127" t="n">
-        <v>161.016730792618</v>
+        <v>161.016730675465</v>
       </c>
     </row>
     <row r="128">
@@ -2474,10 +2474,10 @@
         <v>130</v>
       </c>
       <c r="B128" t="n">
-        <v>1652414.37662279</v>
+        <v>1652414.37541785</v>
       </c>
       <c r="C128" t="n">
-        <v>165.241437662279</v>
+        <v>165.241437541785</v>
       </c>
     </row>
     <row r="129">
@@ -2485,10 +2485,10 @@
         <v>131</v>
       </c>
       <c r="B129" t="n">
-        <v>1714699.47814869</v>
+        <v>1714699.47693737</v>
       </c>
       <c r="C129" t="n">
-        <v>171.469947814869</v>
+        <v>171.469947693737</v>
       </c>
     </row>
     <row r="130">
@@ -2496,10 +2496,10 @@
         <v>132</v>
       </c>
       <c r="B130" t="n">
-        <v>1691230.30692495</v>
+        <v>1691230.30552438</v>
       </c>
       <c r="C130" t="n">
-        <v>169.123030692495</v>
+        <v>169.123030552438</v>
       </c>
     </row>
     <row r="131">
@@ -2507,10 +2507,10 @@
         <v>133</v>
       </c>
       <c r="B131" t="n">
-        <v>1703549.12907314</v>
+        <v>1703549.12781154</v>
       </c>
       <c r="C131" t="n">
-        <v>170.354912907314</v>
+        <v>170.354912781154</v>
       </c>
     </row>
     <row r="132">
@@ -2518,10 +2518,10 @@
         <v>134</v>
       </c>
       <c r="B132" t="n">
-        <v>1701307.54017952</v>
+        <v>1701307.53881497</v>
       </c>
       <c r="C132" t="n">
-        <v>170.130754017952</v>
+        <v>170.130753881497</v>
       </c>
     </row>
     <row r="133">
@@ -2529,10 +2529,10 @@
         <v>135</v>
       </c>
       <c r="B133" t="n">
-        <v>1737819.88882184</v>
+        <v>1737819.88742741</v>
       </c>
       <c r="C133" t="n">
-        <v>173.781988882184</v>
+        <v>173.781988742741</v>
       </c>
     </row>
     <row r="134">
@@ -2540,10 +2540,10 @@
         <v>136</v>
       </c>
       <c r="B134" t="n">
-        <v>1770616.14449143</v>
+        <v>1770616.14306343</v>
       </c>
       <c r="C134" t="n">
-        <v>177.061614449143</v>
+        <v>177.061614306343</v>
       </c>
     </row>
     <row r="135">
@@ -2551,10 +2551,10 @@
         <v>137</v>
       </c>
       <c r="B135" t="n">
-        <v>1758912.0628139</v>
+        <v>1758912.06136414</v>
       </c>
       <c r="C135" t="n">
-        <v>175.89120628139</v>
+        <v>175.891206136414</v>
       </c>
     </row>
     <row r="136">
@@ -2562,10 +2562,10 @@
         <v>138</v>
       </c>
       <c r="B136" t="n">
-        <v>1755649.04235779</v>
+        <v>1755649.04091649</v>
       </c>
       <c r="C136" t="n">
-        <v>175.564904235779</v>
+        <v>175.564904091649</v>
       </c>
     </row>
     <row r="137">
@@ -2573,10 +2573,10 @@
         <v>139</v>
       </c>
       <c r="B137" t="n">
-        <v>1807788.72261475</v>
+        <v>1807788.72111521</v>
       </c>
       <c r="C137" t="n">
-        <v>180.778872261475</v>
+        <v>180.778872111521</v>
       </c>
     </row>
   </sheetData>
@@ -2635,7 +2635,7 @@
         <v>47.6641645764148</v>
       </c>
       <c r="D3" t="n">
-        <v>13.7455943607813</v>
+        <v>13.7455943607816</v>
       </c>
       <c r="E3" t="n">
         <v>22.6854178133797</v>
@@ -2649,13 +2649,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>115.198648846785</v>
+        <v>115.198648846786</v>
       </c>
       <c r="C4" t="n">
         <v>47.9192759905859</v>
       </c>
       <c r="D4" t="n">
-        <v>14.4946439473829</v>
+        <v>14.494643947383</v>
       </c>
       <c r="E4" t="n">
         <v>0.535226865797966</v>
@@ -2669,13 +2669,13 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>130.774186067833</v>
+        <v>130.774186067834</v>
       </c>
       <c r="C5" t="n">
         <v>57.1198216438075</v>
       </c>
       <c r="D5" t="n">
-        <v>13.5205901952575</v>
+        <v>13.5205901952578</v>
       </c>
       <c r="E5" t="n">
         <v>19.2000932047243</v>
@@ -2689,13 +2689,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>87.732504115637</v>
+        <v>87.7325041156377</v>
       </c>
       <c r="C6" t="n">
         <v>56.4514912133363</v>
       </c>
       <c r="D6" t="n">
-        <v>-32.9129801885137</v>
+        <v>-32.9129801885136</v>
       </c>
       <c r="E6" t="n">
         <v>-1.17004992529369</v>
@@ -2715,7 +2715,7 @@
         <v>58.6314085482715</v>
       </c>
       <c r="D7" t="n">
-        <v>28.5954688955957</v>
+        <v>28.595468895595</v>
       </c>
       <c r="E7" t="n">
         <v>3.86157617466143</v>
@@ -2729,13 +2729,13 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>105.266669842471</v>
+        <v>105.266669842472</v>
       </c>
       <c r="C8" t="n">
         <v>61.7934463750931</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.69504832684761</v>
+        <v>-6.6950483268474</v>
       </c>
       <c r="E8" t="n">
         <v>5.39307839452343</v>
@@ -2749,13 +2749,13 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>88.5284103185264</v>
+        <v>88.5284103185272</v>
       </c>
       <c r="C9" t="n">
         <v>59.8141143128873</v>
       </c>
       <c r="D9" t="n">
-        <v>-15.9008160408164</v>
+        <v>-15.9008160408159</v>
       </c>
       <c r="E9" t="n">
         <v>-3.20314236916178</v>
@@ -2769,13 +2769,13 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>102.900497271748</v>
+        <v>102.900497271749</v>
       </c>
       <c r="C10" t="n">
         <v>63.6679518509542</v>
       </c>
       <c r="D10" t="n">
-        <v>16.2344346877017</v>
+        <v>16.2344346877015</v>
       </c>
       <c r="E10" t="n">
         <v>6.44302366145151</v>
@@ -2795,7 +2795,7 @@
         <v>65.675659854104</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.58793791137543</v>
+        <v>-2.58793791137547</v>
       </c>
       <c r="E11" t="n">
         <v>3.15340441270944</v>
@@ -2809,13 +2809,13 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>95.0989740607441</v>
+        <v>95.0989740607448</v>
       </c>
       <c r="C12" t="n">
         <v>65.6455742845469</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.12634734625946</v>
+        <v>-5.12634734625949</v>
       </c>
       <c r="E12" t="n">
         <v>-0.0458093144764193</v>
@@ -2829,13 +2829,13 @@
         <v>13</v>
       </c>
       <c r="B13" t="n">
-        <v>114.240042114501</v>
+        <v>114.240042114502</v>
       </c>
       <c r="C13" t="n">
         <v>69.0875478545522</v>
       </c>
       <c r="D13" t="n">
-        <v>20.1275231860341</v>
+        <v>20.127523186034</v>
       </c>
       <c r="E13" t="n">
         <v>5.24326827439379</v>
@@ -2849,13 +2849,13 @@
         <v>14</v>
       </c>
       <c r="B14" t="n">
-        <v>133.076334988048</v>
+        <v>133.076334988049</v>
       </c>
       <c r="C14" t="n">
         <v>71.3828801927589</v>
       </c>
       <c r="D14" t="n">
-        <v>16.4883455265779</v>
+        <v>16.488345526578</v>
       </c>
       <c r="E14" t="n">
         <v>3.32235317287428</v>
@@ -2869,7 +2869,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="n">
-        <v>159.951916216034</v>
+        <v>159.951916216036</v>
       </c>
       <c r="C15" t="n">
         <v>80.4184774998403</v>
@@ -2889,13 +2889,13 @@
         <v>16</v>
       </c>
       <c r="B16" t="n">
-        <v>188.010138809672</v>
+        <v>188.010138809673</v>
       </c>
       <c r="C16" t="n">
         <v>87.1333351987627</v>
       </c>
       <c r="D16" t="n">
-        <v>17.541660804952</v>
+        <v>17.5416608049519</v>
       </c>
       <c r="E16" t="n">
         <v>8.34989408862621</v>
@@ -2909,13 +2909,13 @@
         <v>17</v>
       </c>
       <c r="B17" t="n">
-        <v>166.916198043279</v>
+        <v>166.91619804328</v>
       </c>
       <c r="C17" t="n">
         <v>71.8299703800848</v>
       </c>
       <c r="D17" t="n">
-        <v>-11.2195761887858</v>
+        <v>-11.2195761887859</v>
       </c>
       <c r="E17" t="n">
         <v>-17.5631574113041</v>
@@ -2929,13 +2929,13 @@
         <v>18</v>
       </c>
       <c r="B18" t="n">
-        <v>380.98488268492</v>
+        <v>380.984882684921</v>
       </c>
       <c r="C18" t="n">
         <v>81.9933532265316</v>
       </c>
       <c r="D18" t="n">
-        <v>128.249197592037</v>
+        <v>128.249197592036</v>
       </c>
       <c r="E18" t="n">
         <v>14.149223217924</v>
@@ -2949,13 +2949,13 @@
         <v>19</v>
       </c>
       <c r="B19" t="n">
-        <v>646.806945030181</v>
+        <v>646.806945030182</v>
       </c>
       <c r="C19" t="n">
         <v>88.1099699808831</v>
       </c>
       <c r="D19" t="n">
-        <v>69.7723385956761</v>
+        <v>69.7723385956759</v>
       </c>
       <c r="E19" t="n">
         <v>7.45989341044806</v>
@@ -2969,7 +2969,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="n">
-        <v>607.441084491193</v>
+        <v>607.441084491194</v>
       </c>
       <c r="C20" t="n">
         <v>93.6685794113347</v>
@@ -2989,7 +2989,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="n">
-        <v>239.388999999999</v>
+        <v>239.389</v>
       </c>
       <c r="C21" t="n">
         <v>100</v>
@@ -3009,13 +3009,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="n">
-        <v>300.463999999999</v>
+        <v>300.464</v>
       </c>
       <c r="C22" t="n">
         <v>114.204720762983</v>
       </c>
       <c r="D22" t="n">
-        <v>25.5128681769005</v>
+        <v>25.5128681769004</v>
       </c>
       <c r="E22" t="n">
         <v>14.2047207629833</v>
@@ -3029,7 +3029,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="n">
-        <v>251.420840844649</v>
+        <v>251.42084084465</v>
       </c>
       <c r="C23" t="n">
         <v>113.731009645385</v>
@@ -3049,13 +3049,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="n">
-        <v>400.837090297354</v>
+        <v>400.837090297355</v>
       </c>
       <c r="C24" t="n">
         <v>115.01305405392</v>
       </c>
       <c r="D24" t="n">
-        <v>59.4287446302147</v>
+        <v>59.4287446302145</v>
       </c>
       <c r="E24" t="n">
         <v>1.1272602015338</v>
@@ -3069,13 +3069,13 @@
         <v>25</v>
       </c>
       <c r="B25" t="n">
-        <v>431.679681741254</v>
+        <v>431.679681741255</v>
       </c>
       <c r="C25" t="n">
         <v>123.509648717351</v>
       </c>
       <c r="D25" t="n">
-        <v>7.69454528796725</v>
+        <v>7.69454528796722</v>
       </c>
       <c r="E25" t="n">
         <v>7.38750460399697</v>
@@ -3089,16 +3089,16 @@
         <v>26</v>
       </c>
       <c r="B26" t="n">
-        <v>521.331863303596</v>
+        <v>521.331863303597</v>
       </c>
       <c r="C26" t="n">
-        <v>127.853917818309</v>
+        <v>127.853917771039</v>
       </c>
       <c r="D26" t="n">
         <v>20.7682189721587</v>
       </c>
       <c r="E26" t="n">
-        <v>3.51735200129943</v>
+        <v>3.51735196302716</v>
       </c>
       <c r="F26" t="s">
         <v>145</v>
@@ -3109,16 +3109,16 @@
         <v>104</v>
       </c>
       <c r="B27" t="n">
-        <v>534.263223359689</v>
+        <v>534.263223624607</v>
       </c>
       <c r="C27" t="n">
-        <v>134.33039550024</v>
+        <v>134.330395443034</v>
       </c>
       <c r="D27" t="n">
-        <v>2.48044690269829</v>
+        <v>2.48044695351359</v>
       </c>
       <c r="E27" t="n">
-        <v>5.06552931067392</v>
+        <v>5.06552930477524</v>
       </c>
       <c r="F27" t="s">
         <v>145</v>
@@ -3129,16 +3129,16 @@
         <v>108</v>
       </c>
       <c r="B28" t="n">
-        <v>546.754717018268</v>
+        <v>546.754717206278</v>
       </c>
       <c r="C28" t="n">
-        <v>138.993448656096</v>
+        <v>138.993448591616</v>
       </c>
       <c r="D28" t="n">
-        <v>2.33807851867975</v>
+        <v>2.33807850312537</v>
       </c>
       <c r="E28" t="n">
-        <v>3.47133136807256</v>
+        <v>3.4713313641364</v>
       </c>
       <c r="F28" t="s">
         <v>145</v>
@@ -3149,16 +3149,16 @@
         <v>112</v>
       </c>
       <c r="B29" t="n">
-        <v>563.924681743984</v>
+        <v>563.924681736289</v>
       </c>
       <c r="C29" t="n">
-        <v>143.622152270034</v>
+        <v>143.62215219651</v>
       </c>
       <c r="D29" t="n">
-        <v>3.14034139830601</v>
+        <v>3.14034136143231</v>
       </c>
       <c r="E29" t="n">
-        <v>3.33015955693747</v>
+        <v>3.33015955197551</v>
       </c>
       <c r="F29" t="s">
         <v>145</v>
@@ -3169,16 +3169,16 @@
         <v>116</v>
       </c>
       <c r="B30" t="n">
-        <v>589.340641378615</v>
+        <v>589.340641115997</v>
       </c>
       <c r="C30" t="n">
-        <v>149.350794721619</v>
+        <v>149.350794630219</v>
       </c>
       <c r="D30" t="n">
-        <v>4.50697769709782</v>
+        <v>4.50697765195405</v>
       </c>
       <c r="E30" t="n">
-        <v>3.98869001824602</v>
+        <v>3.98869000784148</v>
       </c>
       <c r="F30" t="s">
         <v>145</v>
@@ -3189,16 +3189,16 @@
         <v>120</v>
       </c>
       <c r="B31" t="n">
-        <v>620.033647868943</v>
+        <v>620.033647411535</v>
       </c>
       <c r="C31" t="n">
-        <v>155.827272403614</v>
+        <v>155.827272302279</v>
       </c>
       <c r="D31" t="n">
-        <v>5.20802475433038</v>
+        <v>5.20802472359911</v>
       </c>
       <c r="E31" t="n">
-        <v>4.33641996620613</v>
+        <v>4.33641996220706</v>
       </c>
       <c r="F31" t="s">
         <v>145</v>
@@ -3209,16 +3209,16 @@
         <v>124</v>
       </c>
       <c r="B32" t="n">
-        <v>642.441629111933</v>
+        <v>642.441628511481</v>
       </c>
       <c r="C32" t="n">
-        <v>160.490325559462</v>
+        <v>160.490325450853</v>
       </c>
       <c r="D32" t="n">
-        <v>3.61399438885397</v>
+        <v>3.61399436844971</v>
       </c>
       <c r="E32" t="n">
-        <v>2.9924499632962</v>
+        <v>2.99244996057459</v>
       </c>
       <c r="F32" t="s">
         <v>145</v>
@@ -3229,16 +3229,16 @@
         <v>128</v>
       </c>
       <c r="B33" t="n">
-        <v>665.148058397988</v>
+        <v>665.14805767128</v>
       </c>
       <c r="C33" t="n">
-        <v>165.119029173422</v>
+        <v>165.11902905577</v>
       </c>
       <c r="D33" t="n">
-        <v>3.53439569559701</v>
+        <v>3.53439567924765</v>
       </c>
       <c r="E33" t="n">
-        <v>2.8841013299868</v>
+        <v>2.88410132630337</v>
       </c>
       <c r="F33" t="s">
         <v>145</v>
@@ -3249,16 +3249,16 @@
         <v>132</v>
       </c>
       <c r="B34" t="n">
-        <v>693.655076188497</v>
+        <v>693.655075305024</v>
       </c>
       <c r="C34" t="n">
-        <v>170.847671624986</v>
+        <v>170.847671489457</v>
       </c>
       <c r="D34" t="n">
-        <v>4.28581538058881</v>
+        <v>4.28581536170298</v>
       </c>
       <c r="E34" t="n">
-        <v>3.46940172809946</v>
+        <v>3.46940171974541</v>
       </c>
       <c r="F34" t="s">
         <v>145</v>
@@ -3269,16 +3269,16 @@
         <v>136</v>
       </c>
       <c r="B35" t="n">
-        <v>726.073848358124</v>
+        <v>726.07384736782</v>
       </c>
       <c r="C35" t="n">
-        <v>177.324149306947</v>
+        <v>177.324149161482</v>
       </c>
       <c r="D35" t="n">
-        <v>4.67361564594349</v>
+        <v>4.67361563649491</v>
       </c>
       <c r="E35" t="n">
-        <v>3.79079072038897</v>
+        <v>3.79079071758011</v>
       </c>
       <c r="F35" t="s">
         <v>145</v>
@@ -3323,16 +3323,16 @@
         <v>100.61488020324</v>
       </c>
       <c r="C2" t="n">
-        <v>77.7820925015943</v>
+        <v>77.782092652818</v>
       </c>
       <c r="D2" t="n">
-        <v>22.832787701646</v>
+        <v>22.8327875504224</v>
       </c>
       <c r="E2" t="n">
         <v>47.6641645764148</v>
       </c>
       <c r="F2" t="n">
-        <v>27.5223693667206</v>
+        <v>27.5223690355917</v>
       </c>
     </row>
     <row r="3">
@@ -3343,16 +3343,16 @@
         <v>115.198648846786</v>
       </c>
       <c r="C3" t="n">
-        <v>89.7432142960947</v>
+        <v>89.7432143756157</v>
       </c>
       <c r="D3" t="n">
-        <v>25.4554345506913</v>
+        <v>25.4554344711703</v>
       </c>
       <c r="E3" t="n">
         <v>47.9192759905859</v>
       </c>
       <c r="F3" t="n">
-        <v>40.8218319659803</v>
+        <v>40.8218316360935</v>
       </c>
     </row>
     <row r="4">
@@ -3363,16 +3363,16 @@
         <v>130.774186067834</v>
       </c>
       <c r="C4" t="n">
-        <v>143.486718891129</v>
+        <v>143.486718926739</v>
       </c>
       <c r="D4" t="n">
-        <v>-12.7125328232959</v>
+        <v>-12.7125328589059</v>
       </c>
       <c r="E4" t="n">
         <v>57.1198216438075</v>
       </c>
       <c r="F4" t="n">
-        <v>10.079110823115</v>
+        <v>10.0791105380232</v>
       </c>
     </row>
     <row r="5">
@@ -3383,16 +3383,16 @@
         <v>87.7325041156375</v>
       </c>
       <c r="C5" t="n">
-        <v>122.958124111164</v>
+        <v>122.958124174597</v>
       </c>
       <c r="D5" t="n">
-        <v>-35.2256199955265</v>
+        <v>-35.2256200589597</v>
       </c>
       <c r="E5" t="n">
         <v>56.4514912133363</v>
       </c>
       <c r="F5" t="n">
-        <v>-29.5979987745932</v>
+        <v>-29.597999062939</v>
       </c>
     </row>
     <row r="6">
@@ -3403,16 +3403,16 @@
         <v>112.820025041352</v>
       </c>
       <c r="C6" t="n">
-        <v>111.780273956813</v>
+        <v>111.780274007248</v>
       </c>
       <c r="D6" t="n">
-        <v>1.03975108453847</v>
+        <v>1.0397510341036</v>
       </c>
       <c r="E6" t="n">
         <v>58.6314085482715</v>
       </c>
       <c r="F6" t="n">
-        <v>-15.4848241688878</v>
+        <v>-15.4848244466202</v>
       </c>
     </row>
     <row r="7">
@@ -3423,16 +3423,16 @@
         <v>105.266669842472</v>
       </c>
       <c r="C7" t="n">
-        <v>135.578455484367</v>
+        <v>135.578455525535</v>
       </c>
       <c r="D7" t="n">
-        <v>-30.3117856418957</v>
+        <v>-30.3117856830632</v>
       </c>
       <c r="E7" t="n">
         <v>61.7934463750931</v>
       </c>
       <c r="F7" t="n">
-        <v>-38.956809690297</v>
+        <v>-38.9568099526343</v>
       </c>
     </row>
     <row r="8">
@@ -3443,16 +3443,16 @@
         <v>88.528410318527</v>
       </c>
       <c r="C8" t="n">
-        <v>112.50922924236</v>
+        <v>112.509229301424</v>
       </c>
       <c r="D8" t="n">
-        <v>-23.9808189238334</v>
+        <v>-23.9808189828968</v>
       </c>
       <c r="E8" t="n">
         <v>59.8141143128873</v>
       </c>
       <c r="F8" t="n">
-        <v>-45.7305282727894</v>
+        <v>-45.7305285447635</v>
       </c>
     </row>
     <row r="9">
@@ -3463,16 +3463,16 @@
         <v>102.900497271749</v>
       </c>
       <c r="C9" t="n">
-        <v>128.12873652319</v>
+        <v>128.128736558013</v>
       </c>
       <c r="D9" t="n">
-        <v>-25.2282392514413</v>
+        <v>-25.2282392862641</v>
       </c>
       <c r="E9" t="n">
         <v>63.6679518509542</v>
       </c>
       <c r="F9" t="n">
-        <v>-50.7597952727682</v>
+        <v>-50.759795525979</v>
       </c>
     </row>
     <row r="10">
@@ -3483,16 +3483,16 @@
         <v>100.237496291859</v>
       </c>
       <c r="C10" t="n">
-        <v>135.42823145676</v>
+        <v>135.428231492211</v>
       </c>
       <c r="D10" t="n">
-        <v>-35.1907351649003</v>
+        <v>-35.1907352003519</v>
       </c>
       <c r="E10" t="n">
         <v>65.675659854104</v>
       </c>
       <c r="F10" t="n">
-        <v>-63.5301900436575</v>
+        <v>-63.5301902870934</v>
       </c>
     </row>
     <row r="11">
@@ -3503,16 +3503,16 @@
         <v>95.0989740607446</v>
       </c>
       <c r="C11" t="n">
-        <v>128.146910386655</v>
+        <v>128.146910427528</v>
       </c>
       <c r="D11" t="n">
-        <v>-33.0479363259105</v>
+        <v>-33.0479363667831</v>
       </c>
       <c r="E11" t="n">
         <v>65.6455742845469</v>
       </c>
       <c r="F11" t="n">
-        <v>-68.5172526509313</v>
+        <v>-68.5172528945136</v>
       </c>
     </row>
     <row r="12">
@@ -3523,16 +3523,16 @@
         <v>114.240042114501</v>
       </c>
       <c r="C12" t="n">
-        <v>142.690484092737</v>
+        <v>142.690484116698</v>
       </c>
       <c r="D12" t="n">
-        <v>-28.4504419782357</v>
+        <v>-28.4504420021972</v>
       </c>
       <c r="E12" t="n">
         <v>69.0875478545522</v>
       </c>
       <c r="F12" t="n">
-        <v>-66.7040939523594</v>
+        <v>-66.7040941791837</v>
       </c>
     </row>
     <row r="13">
@@ -3543,16 +3543,16 @@
         <v>133.076334988049</v>
       </c>
       <c r="C13" t="n">
-        <v>155.258171358942</v>
+        <v>155.25817138111</v>
       </c>
       <c r="D13" t="n">
-        <v>-22.1818363708934</v>
+        <v>-22.1818363930617</v>
       </c>
       <c r="E13" t="n">
         <v>71.3828801927589</v>
       </c>
       <c r="F13" t="n">
-        <v>-59.4231805399072</v>
+        <v>-59.4231807555562</v>
       </c>
     </row>
     <row r="14">
@@ -3563,16 +3563,16 @@
         <v>159.951916216035</v>
       </c>
       <c r="C14" t="n">
-        <v>204.811050640732</v>
+        <v>204.811050625252</v>
       </c>
       <c r="D14" t="n">
-        <v>-44.8591344246966</v>
+        <v>-44.8591344092167</v>
       </c>
       <c r="E14" t="n">
         <v>80.4184774998403</v>
       </c>
       <c r="F14" t="n">
-        <v>-78.0354590884903</v>
+        <v>-78.0354592601475</v>
       </c>
     </row>
     <row r="15">
@@ -3583,16 +3583,16 @@
         <v>188.010138809673</v>
       </c>
       <c r="C15" t="n">
-        <v>228.224169472816</v>
+        <v>228.224169448938</v>
       </c>
       <c r="D15" t="n">
-        <v>-40.2140306631433</v>
+        <v>-40.2140306392652</v>
       </c>
       <c r="E15" t="n">
         <v>87.1333351987627</v>
       </c>
       <c r="F15" t="n">
-        <v>-83.7818091254651</v>
+        <v>-83.7818092644295</v>
       </c>
     </row>
     <row r="16">
@@ -3603,16 +3603,16 @@
         <v>166.91619804328</v>
       </c>
       <c r="C16" t="n">
-        <v>147.974266090798</v>
+        <v>147.974266159599</v>
       </c>
       <c r="D16" t="n">
-        <v>18.941931952481</v>
+        <v>18.9419318836809</v>
       </c>
       <c r="E16" t="n">
         <v>71.8299703800848</v>
       </c>
       <c r="F16" t="n">
-        <v>-27.8341012521888</v>
+        <v>-27.834101465661</v>
       </c>
     </row>
     <row r="17">
@@ -3623,16 +3623,16 @@
         <v>380.98488268492</v>
       </c>
       <c r="C17" t="n">
-        <v>230.375993311586</v>
+        <v>230.375993290106</v>
       </c>
       <c r="D17" t="n">
-        <v>150.608889373334</v>
+        <v>150.608889394814</v>
       </c>
       <c r="E17" t="n">
         <v>81.9933532265316</v>
       </c>
       <c r="F17" t="n">
-        <v>135.06911883157</v>
+        <v>135.06911866758</v>
       </c>
     </row>
     <row r="18">
@@ -3643,16 +3643,16 @@
         <v>646.806945030182</v>
       </c>
       <c r="C18" t="n">
-        <v>352.119626519368</v>
+        <v>352.119626498067</v>
       </c>
       <c r="D18" t="n">
-        <v>294.687318510814</v>
+        <v>294.687318532115</v>
       </c>
       <c r="E18" t="n">
         <v>88.1099699808831</v>
       </c>
       <c r="F18" t="n">
-        <v>370.09832977221</v>
+        <v>370.098329638001</v>
       </c>
     </row>
     <row r="19">
@@ -3663,16 +3663,16 @@
         <v>607.441084491194</v>
       </c>
       <c r="C19" t="n">
-        <v>511.322874544388</v>
+        <v>511.322874516017</v>
       </c>
       <c r="D19" t="n">
-        <v>96.1182099468053</v>
+        <v>96.1182099751766</v>
       </c>
       <c r="E19" t="n">
         <v>93.6685794113347</v>
       </c>
       <c r="F19" t="n">
-        <v>302.748791150652</v>
+        <v>302.748791043506</v>
       </c>
     </row>
     <row r="20">
@@ -3683,16 +3683,16 @@
         <v>239.389</v>
       </c>
       <c r="C20" t="n">
-        <v>505.595073021604</v>
+        <v>505.595072976552</v>
       </c>
       <c r="D20" t="n">
-        <v>-266.206073021604</v>
+        <v>-266.206072976552</v>
       </c>
       <c r="E20" t="n">
         <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>-97.1775305531693</v>
+        <v>-97.1775306294895</v>
       </c>
     </row>
     <row r="21">
@@ -3703,16 +3703,16 @@
         <v>300.464</v>
       </c>
       <c r="C21" t="n">
-        <v>353.822259358075</v>
+        <v>353.822259255347</v>
       </c>
       <c r="D21" t="n">
-        <v>-53.3582593580747</v>
+        <v>-53.3582592553471</v>
       </c>
       <c r="E21" t="n">
         <v>114.204720762983</v>
       </c>
       <c r="F21" t="n">
-        <v>-107.61328122878</v>
+        <v>-107.613281235941</v>
       </c>
     </row>
     <row r="22">
@@ -3723,16 +3723,16 @@
         <v>251.42084084465</v>
       </c>
       <c r="C22" t="n">
-        <v>345.611055764981</v>
+        <v>345.611055703023</v>
       </c>
       <c r="D22" t="n">
-        <v>-94.1902149203311</v>
+        <v>-94.1902148583726</v>
       </c>
       <c r="E22" t="n">
         <v>113.731009645385</v>
       </c>
       <c r="F22" t="n">
-        <v>-154.271639008019</v>
+        <v>-154.271639017486</v>
       </c>
     </row>
     <row r="23">
@@ -3743,16 +3743,16 @@
         <v>400.837090297355</v>
       </c>
       <c r="C23" t="n">
-        <v>326.015335795968</v>
+        <v>326.015335725812</v>
       </c>
       <c r="D23" t="n">
-        <v>74.8217545013874</v>
+        <v>74.8217545715436</v>
       </c>
       <c r="E23" t="n">
         <v>115.01305405392</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.3095789465415</v>
+        <v>-11.3095789497673</v>
       </c>
     </row>
     <row r="24">
@@ -3763,16 +3763,16 @@
         <v>431.679681741255</v>
       </c>
       <c r="C24" t="n">
-        <v>448.607095276022</v>
+        <v>448.60709517003</v>
       </c>
       <c r="D24" t="n">
-        <v>-16.9274135347664</v>
+        <v>-16.9274134287748</v>
       </c>
       <c r="E24" t="n">
         <v>123.509648717351</v>
       </c>
       <c r="F24" t="n">
-        <v>-23.2413491185133</v>
+        <v>-23.2413490803715</v>
       </c>
     </row>
     <row r="25">
@@ -3783,16 +3783,16 @@
         <v>521.331863303597</v>
       </c>
       <c r="C25" t="n">
-        <v>463.81577877544</v>
+        <v>463.815778433252</v>
       </c>
       <c r="D25" t="n">
-        <v>57.5160845281568</v>
+        <v>57.5160848703452</v>
       </c>
       <c r="E25" t="n">
-        <v>127.853917818309</v>
+        <v>127.853917771039</v>
       </c>
       <c r="F25" t="n">
-        <v>44.5405014651366</v>
+        <v>44.5405017624004</v>
       </c>
     </row>
   </sheetData>
@@ -3849,31 +3849,31 @@
         <v>11.1469028155255</v>
       </c>
       <c r="C2" t="n">
-        <v>8.39961637108207</v>
+        <v>8.39961588747034</v>
       </c>
       <c r="D2" t="n">
-        <v>15.5734541021666</v>
+        <v>15.5734541437172</v>
       </c>
       <c r="E2" t="n">
-        <v>77.7820925015943</v>
+        <v>77.782092652818</v>
       </c>
       <c r="F2" t="n">
         <v>100.61488020324</v>
       </c>
       <c r="G2" t="n">
-        <v>22.832787701646</v>
+        <v>22.8327875504223</v>
       </c>
       <c r="H2" t="n">
-        <v>5.11412997764104</v>
+        <v>5.11412995513863</v>
       </c>
       <c r="I2" t="n">
-        <v>20.6875840798076</v>
+        <v>20.6875840988558</v>
       </c>
       <c r="J2" t="n">
         <v>100.61488020324</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.000000000000440536496171262</v>
+        <v>-0.000000000000198951966012828</v>
       </c>
     </row>
     <row r="3">
@@ -3884,31 +3884,31 @@
         <v>11.6813206587827</v>
       </c>
       <c r="C3" t="n">
-        <v>8.39961637108207</v>
+        <v>8.39961588747034</v>
       </c>
       <c r="D3" t="n">
-        <v>18.2638710264715</v>
+        <v>18.2638710654203</v>
       </c>
       <c r="E3" t="n">
-        <v>77.7820925015943</v>
+        <v>77.782092652818</v>
       </c>
       <c r="F3" t="n">
         <v>100.61488020324</v>
       </c>
       <c r="G3" t="n">
-        <v>22.832787701646</v>
+        <v>22.8327875504223</v>
       </c>
       <c r="H3" t="n">
-        <v>5.35175675674919</v>
+        <v>5.35175672812538</v>
       </c>
       <c r="I3" t="n">
-        <v>23.6156277832207</v>
+        <v>23.6156277935456</v>
       </c>
       <c r="J3" t="n">
         <v>100.61488020324</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.000000000000440536496171262</v>
+        <v>-0.000000000000198951966012828</v>
       </c>
     </row>
     <row r="4">
@@ -3919,31 +3919,31 @@
         <v>11.8182562487431</v>
       </c>
       <c r="C4" t="n">
-        <v>8.39961637108207</v>
+        <v>8.39961588747034</v>
       </c>
       <c r="D4" t="n">
-        <v>18.9532451434055</v>
+        <v>18.9532451816875</v>
       </c>
       <c r="E4" t="n">
-        <v>77.7820925015943</v>
+        <v>77.782092652818</v>
       </c>
       <c r="F4" t="n">
         <v>100.61488020324</v>
       </c>
       <c r="G4" t="n">
-        <v>22.832787701646</v>
+        <v>22.8327875504223</v>
       </c>
       <c r="H4" t="n">
-        <v>5.82701031496547</v>
+        <v>5.82701027409891</v>
       </c>
       <c r="I4" t="n">
-        <v>24.780255458371</v>
+        <v>24.7802554557865</v>
       </c>
       <c r="J4" t="n">
         <v>100.61488020324</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000000000000440536496171262</v>
+        <v>-0.000000000000198951966012828</v>
       </c>
     </row>
     <row r="5">
@@ -3954,31 +3954,31 @@
         <v>13.0176848533636</v>
       </c>
       <c r="C5" t="n">
-        <v>8.39961637108207</v>
+        <v>8.39961588747034</v>
       </c>
       <c r="D5" t="n">
-        <v>24.9915222295507</v>
+        <v>24.991522261993</v>
       </c>
       <c r="E5" t="n">
-        <v>77.7820925015943</v>
+        <v>77.782092652818</v>
       </c>
       <c r="F5" t="n">
         <v>100.61488020324</v>
       </c>
       <c r="G5" t="n">
-        <v>22.832787701646</v>
+        <v>22.8327875504223</v>
       </c>
       <c r="H5" t="n">
-        <v>6.53989065228989</v>
+        <v>6.53989059305921</v>
       </c>
       <c r="I5" t="n">
-        <v>31.5314128818406</v>
+        <v>31.5314128550522</v>
       </c>
       <c r="J5" t="n">
         <v>100.61488020324</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.000000000000440536496171262</v>
+        <v>-0.000000000000198951966012828</v>
       </c>
     </row>
     <row r="6">
@@ -3989,31 +3989,31 @@
         <v>12.3892763792865</v>
       </c>
       <c r="C6" t="n">
-        <v>27.5223693667206</v>
+        <v>27.5223690355917</v>
       </c>
       <c r="D6" t="n">
-        <v>24.4970301862052</v>
+        <v>24.4970302942709</v>
       </c>
       <c r="E6" t="n">
-        <v>89.7428042139813</v>
+        <v>89.7428046542183</v>
       </c>
       <c r="F6" t="n">
         <v>115.198648846786</v>
       </c>
       <c r="G6" t="n">
-        <v>25.4558446328047</v>
+        <v>25.4558441925677</v>
       </c>
       <c r="H6" t="n">
-        <v>7.49039776872244</v>
+        <v>7.49039768500628</v>
       </c>
       <c r="I6" t="n">
-        <v>31.9874279549276</v>
+        <v>31.9874279792772</v>
       </c>
       <c r="J6" t="n">
-        <v>115.198648846785</v>
+        <v>115.198648846786</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.000000000000596855898038484</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="7">
@@ -4024,31 +4024,31 @@
         <v>12.2749895402599</v>
       </c>
       <c r="C7" t="n">
-        <v>27.5223693667206</v>
+        <v>27.5223690355917</v>
       </c>
       <c r="D7" t="n">
-        <v>23.9216765564154</v>
+        <v>23.9216766650376</v>
       </c>
       <c r="E7" t="n">
-        <v>89.7428042139813</v>
+        <v>89.7428046542183</v>
       </c>
       <c r="F7" t="n">
         <v>115.198648846786</v>
       </c>
       <c r="G7" t="n">
-        <v>25.4558446328047</v>
+        <v>25.4558441925677</v>
       </c>
       <c r="H7" t="n">
-        <v>7.4200259710869</v>
+        <v>7.42002586703935</v>
       </c>
       <c r="I7" t="n">
-        <v>31.3417025275023</v>
+        <v>31.3417025320769</v>
       </c>
       <c r="J7" t="n">
-        <v>115.198648846785</v>
+        <v>115.198648846786</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000000000000596855898038484</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="8">
@@ -4059,31 +4059,31 @@
         <v>11.7356560380167</v>
       </c>
       <c r="C8" t="n">
-        <v>27.5223693667206</v>
+        <v>27.5223690355917</v>
       </c>
       <c r="D8" t="n">
-        <v>21.2065127560525</v>
+        <v>21.2065128673005</v>
       </c>
       <c r="E8" t="n">
-        <v>89.7428042139813</v>
+        <v>89.7428046542183</v>
       </c>
       <c r="F8" t="n">
         <v>115.198648846786</v>
       </c>
       <c r="G8" t="n">
-        <v>25.4558446328047</v>
+        <v>25.4558441925677</v>
       </c>
       <c r="H8" t="n">
-        <v>6.32877525938325</v>
+        <v>6.32877513915841</v>
       </c>
       <c r="I8" t="n">
-        <v>27.5352880154357</v>
+        <v>27.5352880064589</v>
       </c>
       <c r="J8" t="n">
-        <v>115.198648846785</v>
+        <v>115.198648846786</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.000000000000596855898038484</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="9">
@@ -4094,31 +4094,31 @@
         <v>11.5193540330228</v>
       </c>
       <c r="C9" t="n">
-        <v>27.5223693667206</v>
+        <v>27.5223690355917</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1175847153082</v>
+        <v>20.1175848276093</v>
       </c>
       <c r="E9" t="n">
-        <v>89.7428042139813</v>
+        <v>89.7428046542183</v>
       </c>
       <c r="F9" t="n">
         <v>115.198648846786</v>
       </c>
       <c r="G9" t="n">
-        <v>25.4558446328047</v>
+        <v>25.4558441925677</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2166456336115</v>
+        <v>4.21664550136344</v>
       </c>
       <c r="I9" t="n">
-        <v>24.3342303489197</v>
+        <v>24.3342303289728</v>
       </c>
       <c r="J9" t="n">
-        <v>115.198648846785</v>
+        <v>115.198648846786</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000000000000596855898038484</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="10">
@@ -4129,31 +4129,31 @@
         <v>13.2313468461927</v>
       </c>
       <c r="C10" t="n">
-        <v>40.8218319659803</v>
+        <v>40.8218316360935</v>
       </c>
       <c r="D10" t="n">
-        <v>30.5925636024979</v>
+        <v>30.5925637423017</v>
       </c>
       <c r="E10" t="n">
-        <v>143.486272635767</v>
+        <v>143.486273174561</v>
       </c>
       <c r="F10" t="n">
         <v>130.774186067834</v>
       </c>
       <c r="G10" t="n">
-        <v>-12.7120865679334</v>
+        <v>-12.7120871067275</v>
       </c>
       <c r="H10" t="n">
-        <v>1.08363709377165</v>
+        <v>1.08363695365446</v>
       </c>
       <c r="I10" t="n">
-        <v>31.6762006962695</v>
+        <v>31.6762006959562</v>
       </c>
       <c r="J10" t="n">
-        <v>130.774186067833</v>
+        <v>130.774186067834</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.00000000000056843418860808</v>
+        <v>0.00000000000014210854715202</v>
       </c>
     </row>
     <row r="11">
@@ -4164,31 +4164,31 @@
         <v>14.1226585458536</v>
       </c>
       <c r="C11" t="n">
-        <v>40.8218319659803</v>
+        <v>40.8218316360935</v>
       </c>
       <c r="D11" t="n">
-        <v>35.0796893821755</v>
+        <v>35.0796895176398</v>
       </c>
       <c r="E11" t="n">
-        <v>143.486272635767</v>
+        <v>143.486273174561</v>
       </c>
       <c r="F11" t="n">
         <v>130.774186067834</v>
       </c>
       <c r="G11" t="n">
-        <v>-12.7120865679334</v>
+        <v>-12.7120871067275</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.87422981646635</v>
+        <v>-1.87422995756365</v>
       </c>
       <c r="I11" t="n">
-        <v>33.2054595657092</v>
+        <v>33.2054595600762</v>
       </c>
       <c r="J11" t="n">
-        <v>130.774186067833</v>
+        <v>130.774186067834</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.00000000000056843418860808</v>
+        <v>0.00000000000014210854715202</v>
       </c>
     </row>
     <row r="12">
@@ -4199,31 +4199,31 @@
         <v>14.2539598031749</v>
       </c>
       <c r="C12" t="n">
-        <v>40.8218319659803</v>
+        <v>40.8218316360935</v>
       </c>
       <c r="D12" t="n">
-        <v>35.7406986080776</v>
+        <v>35.7406987429026</v>
       </c>
       <c r="E12" t="n">
-        <v>143.486272635767</v>
+        <v>143.486273174561</v>
       </c>
       <c r="F12" t="n">
         <v>130.774186067834</v>
       </c>
       <c r="G12" t="n">
-        <v>-12.7120865679334</v>
+        <v>-12.7120871067275</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.6569550971025</v>
+        <v>-4.65695523229088</v>
       </c>
       <c r="I12" t="n">
-        <v>31.0837435109751</v>
+        <v>31.0837435106118</v>
       </c>
       <c r="J12" t="n">
-        <v>130.774186067833</v>
+        <v>130.774186067834</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.00000000000056843418860808</v>
+        <v>0.00000000000014210854715202</v>
       </c>
     </row>
     <row r="13">
@@ -4234,31 +4234,31 @@
         <v>15.5118564485863</v>
       </c>
       <c r="C13" t="n">
-        <v>40.8218319659803</v>
+        <v>40.8218316360935</v>
       </c>
       <c r="D13" t="n">
-        <v>42.0733210430161</v>
+        <v>42.0733211717168</v>
       </c>
       <c r="E13" t="n">
-        <v>143.486272635767</v>
+        <v>143.486273174561</v>
       </c>
       <c r="F13" t="n">
         <v>130.774186067834</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.7120865679334</v>
+        <v>-12.7120871067275</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.26453874813681</v>
+        <v>-7.26453887052724</v>
       </c>
       <c r="I13" t="n">
-        <v>34.8087822948793</v>
+        <v>34.8087823011896</v>
       </c>
       <c r="J13" t="n">
-        <v>130.774186067833</v>
+        <v>130.774186067834</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.00000000000056843418860808</v>
+        <v>0.00000000000014210854715202</v>
       </c>
     </row>
     <row r="14">
@@ -4269,31 +4269,31 @@
         <v>16.1184436592147</v>
       </c>
       <c r="C14" t="n">
-        <v>10.079110823115</v>
+        <v>10.0791105380232</v>
       </c>
       <c r="D14" t="n">
-        <v>40.8360751300521</v>
+        <v>40.8360751796104</v>
       </c>
       <c r="E14" t="n">
-        <v>122.957761473023</v>
+        <v>122.957761710314</v>
       </c>
       <c r="F14" t="n">
         <v>87.7325041156375</v>
       </c>
       <c r="G14" t="n">
-        <v>-35.2252573573855</v>
+        <v>-35.2252575946769</v>
       </c>
       <c r="H14" t="n">
-        <v>-9.69698076956928</v>
+        <v>-9.69698087227273</v>
       </c>
       <c r="I14" t="n">
-        <v>31.1390943604829</v>
+        <v>31.1390943073377</v>
       </c>
       <c r="J14" t="n">
-        <v>87.732504115637</v>
+        <v>87.7325041156377</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000000000000468958205601666</v>
+        <v>0.000000000000198951966012828</v>
       </c>
     </row>
     <row r="15">
@@ -4304,31 +4304,31 @@
         <v>16.415677221503</v>
       </c>
       <c r="C15" t="n">
-        <v>10.079110823115</v>
+        <v>10.0791105380232</v>
       </c>
       <c r="D15" t="n">
-        <v>42.3324364820198</v>
+        <v>42.3324365301309</v>
       </c>
       <c r="E15" t="n">
-        <v>122.957761473023</v>
+        <v>122.957761710314</v>
       </c>
       <c r="F15" t="n">
         <v>87.7325041156375</v>
       </c>
       <c r="G15" t="n">
-        <v>-35.2252573573855</v>
+        <v>-35.2252575946769</v>
       </c>
       <c r="H15" t="n">
-        <v>-10.3136910060532</v>
+        <v>-10.3136910835295</v>
       </c>
       <c r="I15" t="n">
-        <v>32.0187454759667</v>
+        <v>32.0187454466014</v>
       </c>
       <c r="J15" t="n">
-        <v>87.732504115637</v>
+        <v>87.7325041156377</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.000000000000468958205601666</v>
+        <v>0.000000000000198951966012828</v>
       </c>
     </row>
     <row r="16">
@@ -4339,31 +4339,31 @@
         <v>12.2234703618602</v>
       </c>
       <c r="C16" t="n">
-        <v>10.079110823115</v>
+        <v>10.0791105380232</v>
       </c>
       <c r="D16" t="n">
-        <v>21.2276316412426</v>
+        <v>21.2276317097644</v>
       </c>
       <c r="E16" t="n">
-        <v>122.957761473023</v>
+        <v>122.957761710314</v>
       </c>
       <c r="F16" t="n">
         <v>87.7325041156375</v>
       </c>
       <c r="G16" t="n">
-        <v>-35.2252573573855</v>
+        <v>-35.2252575946769</v>
       </c>
       <c r="H16" t="n">
-        <v>-9.11466945758843</v>
+        <v>-9.11466950429756</v>
       </c>
       <c r="I16" t="n">
-        <v>12.1129621836542</v>
+        <v>12.1129622054669</v>
       </c>
       <c r="J16" t="n">
-        <v>87.732504115637</v>
+        <v>87.7325041156377</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.000000000000468958205601666</v>
+        <v>0.000000000000198951966012828</v>
       </c>
     </row>
     <row r="17">
@@ -4374,31 +4374,31 @@
         <v>11.6938999707585</v>
       </c>
       <c r="C17" t="n">
-        <v>10.079110823115</v>
+        <v>10.0791105380232</v>
       </c>
       <c r="D17" t="n">
-        <v>18.5616182197084</v>
+        <v>18.5616182908086</v>
       </c>
       <c r="E17" t="n">
-        <v>122.957761473023</v>
+        <v>122.957761710314</v>
       </c>
       <c r="F17" t="n">
         <v>87.7325041156375</v>
       </c>
       <c r="G17" t="n">
-        <v>-35.2252573573855</v>
+        <v>-35.2252575946769</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.0999161241751</v>
+        <v>-6.0999161345769</v>
       </c>
       <c r="I17" t="n">
-        <v>12.4617020955333</v>
+        <v>12.4617021562317</v>
       </c>
       <c r="J17" t="n">
-        <v>87.732504115637</v>
+        <v>87.7325041156377</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000000000000468958205601666</v>
+        <v>0.000000000000198951966012828</v>
       </c>
     </row>
     <row r="18">
@@ -4409,31 +4409,31 @@
         <v>15.3258805423762</v>
       </c>
       <c r="C18" t="n">
-        <v>-29.5979987745932</v>
+        <v>-29.597999062939</v>
       </c>
       <c r="D18" t="n">
-        <v>31.308056679947</v>
+        <v>31.3080566265094</v>
       </c>
       <c r="E18" t="n">
-        <v>111.780019236564</v>
+        <v>111.780019035824</v>
       </c>
       <c r="F18" t="n">
         <v>112.820025041352</v>
       </c>
       <c r="G18" t="n">
-        <v>1.04000580478743</v>
+        <v>1.04000600552808</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.26943100581318</v>
+        <v>-1.26943097436752</v>
       </c>
       <c r="I18" t="n">
-        <v>30.0386256741338</v>
+        <v>30.0386256521418</v>
       </c>
       <c r="J18" t="n">
         <v>112.820025041351</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.000000000000326849658449646</v>
+        <v>-0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="19">
@@ -4444,31 +4444,31 @@
         <v>14.8733170138056</v>
       </c>
       <c r="C19" t="n">
-        <v>-29.5979987745932</v>
+        <v>-29.597999062939</v>
       </c>
       <c r="D19" t="n">
-        <v>29.0297184995288</v>
+        <v>29.0297184482946</v>
       </c>
       <c r="E19" t="n">
-        <v>111.780019236564</v>
+        <v>111.780019035824</v>
       </c>
       <c r="F19" t="n">
         <v>112.820025041352</v>
       </c>
       <c r="G19" t="n">
-        <v>1.04000580478743</v>
+        <v>1.04000600552808</v>
       </c>
       <c r="H19" t="n">
-        <v>1.27453602433556</v>
+        <v>1.27453608001604</v>
       </c>
       <c r="I19" t="n">
-        <v>30.3042545238644</v>
+        <v>30.3042545283106</v>
       </c>
       <c r="J19" t="n">
         <v>112.820025041351</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000000000000326849658449646</v>
+        <v>-0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="20">
@@ -4479,31 +4479,31 @@
         <v>13.8768502823917</v>
       </c>
       <c r="C20" t="n">
-        <v>-29.5979987745932</v>
+        <v>-29.597999062939</v>
       </c>
       <c r="D20" t="n">
-        <v>24.0132112991639</v>
+        <v>24.0132112527812</v>
       </c>
       <c r="E20" t="n">
-        <v>111.780019236564</v>
+        <v>111.780019035824</v>
       </c>
       <c r="F20" t="n">
         <v>112.820025041352</v>
       </c>
       <c r="G20" t="n">
-        <v>1.04000580478743</v>
+        <v>1.04000600552808</v>
       </c>
       <c r="H20" t="n">
-        <v>1.53198496627115</v>
+        <v>1.53198502857377</v>
       </c>
       <c r="I20" t="n">
-        <v>25.5451962654351</v>
+        <v>25.545196281355</v>
       </c>
       <c r="J20" t="n">
         <v>112.820025041351</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.000000000000326849658449646</v>
+        <v>-0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="21">
@@ -4514,31 +4514,31 @@
         <v>14.555360709698</v>
       </c>
       <c r="C21" t="n">
-        <v>-29.5979987745932</v>
+        <v>-29.597999062939</v>
       </c>
       <c r="D21" t="n">
-        <v>27.4290327579245</v>
+        <v>27.4290327082383</v>
       </c>
       <c r="E21" t="n">
-        <v>111.780019236564</v>
+        <v>111.780019035824</v>
       </c>
       <c r="F21" t="n">
         <v>112.820025041352</v>
       </c>
       <c r="G21" t="n">
-        <v>1.04000580478743</v>
+        <v>1.04000600552808</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.49708418000644</v>
+        <v>-0.497084128694312</v>
       </c>
       <c r="I21" t="n">
-        <v>26.931948577918</v>
+        <v>26.931948579544</v>
       </c>
       <c r="J21" t="n">
         <v>112.820025041351</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.000000000000326849658449646</v>
+        <v>-0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="22">
@@ -4549,31 +4549,31 @@
         <v>15.0667257975563</v>
       </c>
       <c r="C22" t="n">
-        <v>-15.4848241688878</v>
+        <v>-15.4848244466202</v>
       </c>
       <c r="D22" t="n">
-        <v>31.9732735221817</v>
+        <v>31.9732735093339</v>
       </c>
       <c r="E22" t="n">
-        <v>135.578162377652</v>
+        <v>135.578162318828</v>
       </c>
       <c r="F22" t="n">
         <v>105.266669842472</v>
       </c>
       <c r="G22" t="n">
-        <v>-30.3114925351799</v>
+        <v>-30.3114924763566</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.81267141449719</v>
+        <v>-4.81267139178822</v>
       </c>
       <c r="I22" t="n">
-        <v>27.1606021076845</v>
+        <v>27.1606021175457</v>
       </c>
       <c r="J22" t="n">
-        <v>105.266669842471</v>
+        <v>105.266669842472</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.00000000000042632564145606</v>
+        <v>0.000000000000014210854715202</v>
       </c>
     </row>
     <row r="23">
@@ -4584,31 +4584,31 @@
         <v>15.6731164614357</v>
       </c>
       <c r="C23" t="n">
-        <v>-15.4848241688878</v>
+        <v>-15.4848244466202</v>
       </c>
       <c r="D23" t="n">
-        <v>35.0260228370221</v>
+        <v>35.026022821222</v>
       </c>
       <c r="E23" t="n">
-        <v>135.578162377652</v>
+        <v>135.578162318828</v>
       </c>
       <c r="F23" t="n">
         <v>105.266669842472</v>
       </c>
       <c r="G23" t="n">
-        <v>-30.3114925351799</v>
+        <v>-30.3114924763566</v>
       </c>
       <c r="H23" t="n">
-        <v>-7.64498699601265</v>
+        <v>-7.64498698794615</v>
       </c>
       <c r="I23" t="n">
-        <v>27.3810358410094</v>
+        <v>27.3810358332759</v>
       </c>
       <c r="J23" t="n">
-        <v>105.266669842471</v>
+        <v>105.266669842472</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.00000000000042632564145606</v>
+        <v>0.000000000000014210854715202</v>
       </c>
     </row>
     <row r="24">
@@ -4619,31 +4619,31 @@
         <v>15.7338178579393</v>
       </c>
       <c r="C24" t="n">
-        <v>-15.4848241688878</v>
+        <v>-15.4848244466202</v>
       </c>
       <c r="D24" t="n">
-        <v>35.3316115566782</v>
+        <v>35.3316115405826</v>
       </c>
       <c r="E24" t="n">
-        <v>135.578162377652</v>
+        <v>135.578162318828</v>
       </c>
       <c r="F24" t="n">
         <v>105.266669842472</v>
       </c>
       <c r="G24" t="n">
-        <v>-30.3114925351799</v>
+        <v>-30.3114924763566</v>
       </c>
       <c r="H24" t="n">
-        <v>-8.9940309245528</v>
+        <v>-8.9940309171681</v>
       </c>
       <c r="I24" t="n">
-        <v>26.3375806321254</v>
+        <v>26.3375806234145</v>
       </c>
       <c r="J24" t="n">
-        <v>105.266669842471</v>
+        <v>105.266669842472</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.00000000000042632564145606</v>
+        <v>0.000000000000014210854715202</v>
       </c>
     </row>
     <row r="25">
@@ -4654,31 +4654,31 @@
         <v>15.3197862581617</v>
       </c>
       <c r="C25" t="n">
-        <v>-15.4848241688878</v>
+        <v>-15.4848244466202</v>
       </c>
       <c r="D25" t="n">
-        <v>33.2472544617696</v>
+        <v>33.2472544476897</v>
       </c>
       <c r="E25" t="n">
-        <v>135.578162377652</v>
+        <v>135.578162318828</v>
       </c>
       <c r="F25" t="n">
         <v>105.266669842472</v>
       </c>
       <c r="G25" t="n">
-        <v>-30.3114925351799</v>
+        <v>-30.3114924763566</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.85980320011765</v>
+        <v>-8.85980317945409</v>
       </c>
       <c r="I25" t="n">
-        <v>24.3874512616519</v>
+        <v>24.3874512682357</v>
       </c>
       <c r="J25" t="n">
-        <v>105.266669842471</v>
+        <v>105.266669842472</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.00000000000042632564145606</v>
+        <v>0.000000000000014210854715202</v>
       </c>
     </row>
     <row r="26">
@@ -4689,31 +4689,31 @@
         <v>14.7328890677592</v>
       </c>
       <c r="C26" t="n">
-        <v>-38.956809690297</v>
+        <v>-38.9568099526343</v>
       </c>
       <c r="D26" t="n">
-        <v>27.0164856726878</v>
+        <v>27.0164856006704</v>
       </c>
       <c r="E26" t="n">
-        <v>112.50899997717</v>
+        <v>112.508999684803</v>
       </c>
       <c r="F26" t="n">
         <v>88.528410318527</v>
       </c>
       <c r="G26" t="n">
-        <v>-23.980589658643</v>
+        <v>-23.9805893662763</v>
       </c>
       <c r="H26" t="n">
-        <v>-7.2423038227072</v>
+        <v>-7.24230377480409</v>
       </c>
       <c r="I26" t="n">
-        <v>19.7741818499806</v>
+        <v>19.7741818258663</v>
       </c>
       <c r="J26" t="n">
-        <v>88.5284103185264</v>
+        <v>88.5284103185272</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.000000000000611066752753686</v>
+        <v>0.000000000000270006239588838</v>
       </c>
     </row>
     <row r="27">
@@ -4724,31 +4724,31 @@
         <v>14.7581102218019</v>
       </c>
       <c r="C27" t="n">
-        <v>-38.956809690297</v>
+        <v>-38.9568099526343</v>
       </c>
       <c r="D27" t="n">
-        <v>27.1434563952095</v>
+        <v>27.1434563230693</v>
       </c>
       <c r="E27" t="n">
-        <v>112.50899997717</v>
+        <v>112.508999684803</v>
       </c>
       <c r="F27" t="n">
         <v>88.528410318527</v>
       </c>
       <c r="G27" t="n">
-        <v>-23.980589658643</v>
+        <v>-23.9805893662763</v>
       </c>
       <c r="H27" t="n">
-        <v>-6.09644150852449</v>
+        <v>-6.09644143965006</v>
       </c>
       <c r="I27" t="n">
-        <v>21.047014886685</v>
+        <v>21.0470148834192</v>
       </c>
       <c r="J27" t="n">
-        <v>88.5284103185264</v>
+        <v>88.5284103185272</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.000000000000611066752753686</v>
+        <v>0.000000000000270006239588838</v>
       </c>
     </row>
     <row r="28">
@@ -4759,31 +4759,31 @@
         <v>14.9432457255233</v>
       </c>
       <c r="C28" t="n">
-        <v>-38.956809690297</v>
+        <v>-38.9568099526343</v>
       </c>
       <c r="D28" t="n">
-        <v>28.0754830832894</v>
+        <v>28.0754830102478</v>
       </c>
       <c r="E28" t="n">
-        <v>112.50899997717</v>
+        <v>112.508999684803</v>
       </c>
       <c r="F28" t="n">
         <v>88.528410318527</v>
       </c>
       <c r="G28" t="n">
-        <v>-23.980589658643</v>
+        <v>-23.9805893662763</v>
       </c>
       <c r="H28" t="n">
-        <v>-5.42221625756954</v>
+        <v>-5.42221617399198</v>
       </c>
       <c r="I28" t="n">
-        <v>22.6532668257199</v>
+        <v>22.6532668362559</v>
       </c>
       <c r="J28" t="n">
-        <v>88.5284103185264</v>
+        <v>88.5284103185272</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.000000000000611066752753686</v>
+        <v>0.000000000000270006239588838</v>
       </c>
     </row>
     <row r="29">
@@ -4794,31 +4794,31 @@
         <v>15.3798692978029</v>
       </c>
       <c r="C29" t="n">
-        <v>-38.956809690297</v>
+        <v>-38.9568099526343</v>
       </c>
       <c r="D29" t="n">
-        <v>30.2735748259832</v>
+        <v>30.2735747508158</v>
       </c>
       <c r="E29" t="n">
-        <v>112.50899997717</v>
+        <v>112.508999684803</v>
       </c>
       <c r="F29" t="n">
         <v>88.528410318527</v>
       </c>
       <c r="G29" t="n">
-        <v>-23.980589658643</v>
+        <v>-23.9805893662763</v>
       </c>
       <c r="H29" t="n">
-        <v>-5.21962806984234</v>
+        <v>-5.21962797782987</v>
       </c>
       <c r="I29" t="n">
-        <v>25.0539467561409</v>
+        <v>25.0539467729859</v>
       </c>
       <c r="J29" t="n">
-        <v>88.5284103185264</v>
+        <v>88.5284103185272</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.000000000000611066752753686</v>
+        <v>0.000000000000270006239588838</v>
       </c>
     </row>
     <row r="30">
@@ -4829,31 +4829,31 @@
         <v>16.3753445128911</v>
       </c>
       <c r="C30" t="n">
-        <v>-45.7305282727894</v>
+        <v>-45.7305285447635</v>
       </c>
       <c r="D30" t="n">
-        <v>34.3396333788206</v>
+        <v>34.3396332792966</v>
       </c>
       <c r="E30" t="n">
-        <v>128.128525681857</v>
+        <v>128.128525292688</v>
       </c>
       <c r="F30" t="n">
         <v>102.900497271749</v>
       </c>
       <c r="G30" t="n">
-        <v>-25.2280284101087</v>
+        <v>-25.2280280209392</v>
       </c>
       <c r="H30" t="n">
-        <v>-5.48867694534289</v>
+        <v>-5.48867685116371</v>
       </c>
       <c r="I30" t="n">
-        <v>28.8509564334777</v>
+        <v>28.8509564281329</v>
       </c>
       <c r="J30" t="n">
-        <v>102.900497271748</v>
+        <v>102.900497271749</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.000000000000582645043323282</v>
+        <v>0.000000000000270006239588838</v>
       </c>
     </row>
     <row r="31">
@@ -4864,31 +4864,31 @@
         <v>15.0887588439557</v>
       </c>
       <c r="C31" t="n">
-        <v>-45.7305282727894</v>
+        <v>-45.7305285447635</v>
       </c>
       <c r="D31" t="n">
-        <v>27.862581944356</v>
+        <v>27.8625818510961</v>
       </c>
       <c r="E31" t="n">
-        <v>128.128525681857</v>
+        <v>128.128525292688</v>
       </c>
       <c r="F31" t="n">
         <v>102.900497271749</v>
       </c>
       <c r="G31" t="n">
-        <v>-25.2280284101087</v>
+        <v>-25.2280280209392</v>
       </c>
       <c r="H31" t="n">
-        <v>-5.92362855841689</v>
+        <v>-5.92362846212566</v>
       </c>
       <c r="I31" t="n">
-        <v>21.9389533859392</v>
+        <v>21.9389533889704</v>
       </c>
       <c r="J31" t="n">
-        <v>102.900497271748</v>
+        <v>102.900497271749</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.000000000000582645043323282</v>
+        <v>0.000000000000270006239588838</v>
       </c>
     </row>
     <row r="32">
@@ -4899,31 +4899,31 @@
         <v>15.4220345279437</v>
       </c>
       <c r="C32" t="n">
-        <v>-45.7305282727894</v>
+        <v>-45.7305285447635</v>
       </c>
       <c r="D32" t="n">
-        <v>29.5403899591404</v>
+        <v>29.5403898642579</v>
       </c>
       <c r="E32" t="n">
-        <v>128.128525681857</v>
+        <v>128.128525292688</v>
       </c>
       <c r="F32" t="n">
         <v>102.900497271749</v>
       </c>
       <c r="G32" t="n">
-        <v>-25.2280284101087</v>
+        <v>-25.2280280209392</v>
       </c>
       <c r="H32" t="n">
-        <v>-6.52448290906433</v>
+        <v>-6.52448281071572</v>
       </c>
       <c r="I32" t="n">
-        <v>23.0159070500761</v>
+        <v>23.0159070535421</v>
       </c>
       <c r="J32" t="n">
-        <v>102.900497271748</v>
+        <v>102.900497271749</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.000000000000582645043323282</v>
+        <v>0.000000000000270006239588838</v>
       </c>
     </row>
     <row r="33">
@@ -4934,31 +4934,31 @@
         <v>16.7818139661638</v>
       </c>
       <c r="C33" t="n">
-        <v>-45.7305282727894</v>
+        <v>-45.7305285447635</v>
       </c>
       <c r="D33" t="n">
-        <v>36.3859203995403</v>
+        <v>36.3859202980373</v>
       </c>
       <c r="E33" t="n">
-        <v>128.128525681857</v>
+        <v>128.128525292688</v>
       </c>
       <c r="F33" t="n">
         <v>102.900497271749</v>
       </c>
       <c r="G33" t="n">
-        <v>-25.2280284101087</v>
+        <v>-25.2280280209392</v>
       </c>
       <c r="H33" t="n">
-        <v>-7.29123999728522</v>
+        <v>-7.29123989693389</v>
       </c>
       <c r="I33" t="n">
-        <v>29.0946804022551</v>
+        <v>29.0946804011035</v>
       </c>
       <c r="J33" t="n">
-        <v>102.900497271748</v>
+        <v>102.900497271749</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.000000000000582645043323282</v>
+        <v>0.000000000000270006239588838</v>
       </c>
     </row>
     <row r="34">
@@ -4969,31 +4969,31 @@
         <v>16.6647643679365</v>
       </c>
       <c r="C34" t="n">
-        <v>-50.7597952727682</v>
+        <v>-50.759795525979</v>
       </c>
       <c r="D34" t="n">
-        <v>35.0946869311274</v>
+        <v>35.0946868193264</v>
       </c>
       <c r="E34" t="n">
-        <v>135.428034294546</v>
+        <v>135.42803385213</v>
       </c>
       <c r="F34" t="n">
         <v>100.237496291859</v>
       </c>
       <c r="G34" t="n">
-        <v>-35.1905380026865</v>
+        <v>-35.1905375602707</v>
       </c>
       <c r="H34" t="n">
-        <v>-8.22389982307957</v>
+        <v>-8.22389972078017</v>
       </c>
       <c r="I34" t="n">
-        <v>26.8707871080478</v>
+        <v>26.8707870985463</v>
       </c>
       <c r="J34" t="n">
         <v>100.237496291859</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.00000000000056843418860808</v>
+        <v>0.00000000000021316282072803</v>
       </c>
     </row>
     <row r="35">
@@ -5004,31 +5004,31 @@
         <v>15.8762559792141</v>
       </c>
       <c r="C35" t="n">
-        <v>-50.7597952727682</v>
+        <v>-50.759795525979</v>
       </c>
       <c r="D35" t="n">
-        <v>31.1251033164679</v>
+        <v>31.125103208506</v>
       </c>
       <c r="E35" t="n">
-        <v>135.428034294546</v>
+        <v>135.42803385213</v>
       </c>
       <c r="F35" t="n">
         <v>100.237496291859</v>
       </c>
       <c r="G35" t="n">
-        <v>-35.1905380026865</v>
+        <v>-35.1905375602707</v>
       </c>
       <c r="H35" t="n">
-        <v>-8.82645762443419</v>
+        <v>-8.82645751803366</v>
       </c>
       <c r="I35" t="n">
-        <v>22.2986456920337</v>
+        <v>22.2986456904723</v>
       </c>
       <c r="J35" t="n">
         <v>100.237496291859</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.00000000000056843418860808</v>
+        <v>0.00000000000021316282072803</v>
       </c>
     </row>
     <row r="36">
@@ -5039,31 +5039,31 @@
         <v>16.2633429336138</v>
       </c>
       <c r="C36" t="n">
-        <v>-50.7597952727682</v>
+        <v>-50.759795525979</v>
       </c>
       <c r="D36" t="n">
-        <v>33.073813125533</v>
+        <v>33.0738130156864</v>
       </c>
       <c r="E36" t="n">
-        <v>135.428034294546</v>
+        <v>135.42803385213</v>
       </c>
       <c r="F36" t="n">
         <v>100.237496291859</v>
       </c>
       <c r="G36" t="n">
-        <v>-35.1905380026865</v>
+        <v>-35.1905375602707</v>
       </c>
       <c r="H36" t="n">
-        <v>-9.09891340134908</v>
+        <v>-9.09891328869436</v>
       </c>
       <c r="I36" t="n">
-        <v>23.9748997241839</v>
+        <v>23.9748997269921</v>
       </c>
       <c r="J36" t="n">
         <v>100.237496291859</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.00000000000056843418860808</v>
+        <v>0.00000000000021316282072803</v>
       </c>
     </row>
     <row r="37">
@@ -5074,31 +5074,31 @@
         <v>16.8712965733395</v>
       </c>
       <c r="C37" t="n">
-        <v>-50.7597952727682</v>
+        <v>-50.759795525979</v>
       </c>
       <c r="D37" t="n">
-        <v>36.1344309214175</v>
+        <v>36.134430808611</v>
       </c>
       <c r="E37" t="n">
-        <v>135.428034294546</v>
+        <v>135.42803385213</v>
       </c>
       <c r="F37" t="n">
         <v>100.237496291859</v>
       </c>
       <c r="G37" t="n">
-        <v>-35.1905380026865</v>
+        <v>-35.1905375602707</v>
       </c>
       <c r="H37" t="n">
-        <v>-9.04126715382424</v>
+        <v>-9.04126703276226</v>
       </c>
       <c r="I37" t="n">
-        <v>27.0931637675933</v>
+        <v>27.0931637758488</v>
       </c>
       <c r="J37" t="n">
         <v>100.237496291859</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.00000000000056843418860808</v>
+        <v>0.00000000000021316282072803</v>
       </c>
     </row>
     <row r="38">
@@ -5109,31 +5109,31 @@
         <v>16.0508175345883</v>
       </c>
       <c r="C38" t="n">
-        <v>-63.5301900436575</v>
+        <v>-63.5301902870934</v>
       </c>
       <c r="D38" t="n">
-        <v>30.2214409542519</v>
+        <v>30.2214408125586</v>
       </c>
       <c r="E38" t="n">
-        <v>128.146747958677</v>
+        <v>128.146747384882</v>
       </c>
       <c r="F38" t="n">
         <v>95.0989740607446</v>
       </c>
       <c r="G38" t="n">
-        <v>-33.0477738979325</v>
+        <v>-33.0477733241372</v>
       </c>
       <c r="H38" t="n">
-        <v>-8.65351888185967</v>
+        <v>-8.65351875023737</v>
       </c>
       <c r="I38" t="n">
-        <v>21.5679220723922</v>
+        <v>21.5679220623213</v>
       </c>
       <c r="J38" t="n">
-        <v>95.0989740607441</v>
+        <v>95.0989740607448</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.000000000000540012479177676</v>
+        <v>0.000000000000170530256582424</v>
       </c>
     </row>
     <row r="39">
@@ -5144,31 +5144,31 @@
         <v>16.0463647623357</v>
       </c>
       <c r="C39" t="n">
-        <v>-63.5301900436575</v>
+        <v>-63.5301902870934</v>
       </c>
       <c r="D39" t="n">
-        <v>30.1990243864303</v>
+        <v>30.1990242447587</v>
       </c>
       <c r="E39" t="n">
-        <v>128.146747958677</v>
+        <v>128.146747384882</v>
       </c>
       <c r="F39" t="n">
         <v>95.0989740607446</v>
       </c>
       <c r="G39" t="n">
-        <v>-33.0477738979325</v>
+        <v>-33.0477733241372</v>
       </c>
       <c r="H39" t="n">
-        <v>-8.34178941012328</v>
+        <v>-8.34178926954617</v>
       </c>
       <c r="I39" t="n">
-        <v>21.857234976307</v>
+        <v>21.8572349752125</v>
       </c>
       <c r="J39" t="n">
-        <v>95.0989740607441</v>
+        <v>95.0989740607448</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.000000000000540012479177676</v>
+        <v>0.000000000000170530256582424</v>
       </c>
     </row>
     <row r="40">
@@ -5179,31 +5179,31 @@
         <v>16.1262140171378</v>
       </c>
       <c r="C40" t="n">
-        <v>-63.5301900436575</v>
+        <v>-63.5301902870934</v>
       </c>
       <c r="D40" t="n">
-        <v>30.6010090679364</v>
+        <v>30.601008925876</v>
       </c>
       <c r="E40" t="n">
-        <v>128.146747958677</v>
+        <v>128.146747384882</v>
       </c>
       <c r="F40" t="n">
         <v>95.0989740607446</v>
       </c>
       <c r="G40" t="n">
-        <v>-33.0477738979325</v>
+        <v>-33.0477733241372</v>
       </c>
       <c r="H40" t="n">
-        <v>-8.10607873861507</v>
+        <v>-8.10607859068866</v>
       </c>
       <c r="I40" t="n">
-        <v>22.4949303293213</v>
+        <v>22.4949303351873</v>
       </c>
       <c r="J40" t="n">
-        <v>95.0989740607441</v>
+        <v>95.0989740607448</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.000000000000540012479177676</v>
+        <v>0.000000000000170530256582424</v>
       </c>
     </row>
     <row r="41">
@@ -5214,31 +5214,31 @@
         <v>17.4221779704851</v>
       </c>
       <c r="C41" t="n">
-        <v>-63.5301900436575</v>
+        <v>-63.5301902870934</v>
       </c>
       <c r="D41" t="n">
-        <v>37.1252735500586</v>
+        <v>37.1252734016885</v>
       </c>
       <c r="E41" t="n">
-        <v>128.146747958677</v>
+        <v>128.146747384882</v>
       </c>
       <c r="F41" t="n">
         <v>95.0989740607446</v>
       </c>
       <c r="G41" t="n">
-        <v>-33.0477738979325</v>
+        <v>-33.0477733241372</v>
       </c>
       <c r="H41" t="n">
-        <v>-7.94638686733504</v>
+        <v>-7.94638671366484</v>
       </c>
       <c r="I41" t="n">
-        <v>29.1788866827235</v>
+        <v>29.1788866880237</v>
       </c>
       <c r="J41" t="n">
-        <v>95.0989740607441</v>
+        <v>95.0989740607448</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.000000000000540012479177676</v>
+        <v>0.000000000000170530256582424</v>
       </c>
     </row>
     <row r="42">
@@ -5249,31 +5249,31 @@
         <v>16.5941465714623</v>
       </c>
       <c r="C42" t="n">
-        <v>-68.5172526509313</v>
+        <v>-68.5172528945136</v>
       </c>
       <c r="D42" t="n">
-        <v>32.2606389322992</v>
+        <v>32.2606387745666</v>
       </c>
       <c r="E42" t="n">
-        <v>142.690335229086</v>
+        <v>142.690334584956</v>
       </c>
       <c r="F42" t="n">
         <v>114.240042114501</v>
       </c>
       <c r="G42" t="n">
-        <v>-28.4502931145847</v>
+        <v>-28.4502924704552</v>
       </c>
       <c r="H42" t="n">
-        <v>-7.86271379628318</v>
+        <v>-7.86271363847471</v>
       </c>
       <c r="I42" t="n">
-        <v>24.3979251360161</v>
+        <v>24.3979251360919</v>
       </c>
       <c r="J42" t="n">
-        <v>114.240042114501</v>
+        <v>114.240042114502</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.00000000000042632564145606</v>
+        <v>0.000000000000383693077310454</v>
       </c>
     </row>
     <row r="43">
@@ -5284,31 +5284,31 @@
         <v>16.300238106994</v>
       </c>
       <c r="C43" t="n">
-        <v>-68.5172526509313</v>
+        <v>-68.5172528945136</v>
       </c>
       <c r="D43" t="n">
-        <v>30.781017102716</v>
+        <v>30.7810169464143</v>
       </c>
       <c r="E43" t="n">
-        <v>142.690335229086</v>
+        <v>142.690334584956</v>
       </c>
       <c r="F43" t="n">
         <v>114.240042114501</v>
       </c>
       <c r="G43" t="n">
-        <v>-28.4502931145847</v>
+        <v>-28.4502924704552</v>
       </c>
       <c r="H43" t="n">
-        <v>-7.52918836080767</v>
+        <v>-7.52918820005425</v>
       </c>
       <c r="I43" t="n">
-        <v>23.2518287419084</v>
+        <v>23.2518287463601</v>
       </c>
       <c r="J43" t="n">
-        <v>114.240042114501</v>
+        <v>114.240042114502</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.00000000000042632564145606</v>
+        <v>0.000000000000383693077310454</v>
       </c>
     </row>
     <row r="44">
@@ -5319,31 +5319,31 @@
         <v>17.5421545403324</v>
       </c>
       <c r="C44" t="n">
-        <v>-68.5172526509313</v>
+        <v>-68.5172528945136</v>
       </c>
       <c r="D44" t="n">
-        <v>37.033190440459</v>
+        <v>37.0331902781107</v>
       </c>
       <c r="E44" t="n">
-        <v>142.690335229086</v>
+        <v>142.690334584956</v>
       </c>
       <c r="F44" t="n">
         <v>114.240042114501</v>
       </c>
       <c r="G44" t="n">
-        <v>-28.4502931145847</v>
+        <v>-28.4502924704552</v>
       </c>
       <c r="H44" t="n">
-        <v>-6.94581056090852</v>
+        <v>-6.94581039840347</v>
       </c>
       <c r="I44" t="n">
-        <v>30.0873798795504</v>
+        <v>30.0873798797072</v>
       </c>
       <c r="J44" t="n">
-        <v>114.240042114501</v>
+        <v>114.240042114502</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.00000000000042632564145606</v>
+        <v>0.000000000000383693077310454</v>
       </c>
     </row>
     <row r="45">
@@ -5354,31 +5354,31 @@
         <v>18.6510086357636</v>
       </c>
       <c r="C45" t="n">
-        <v>-68.5172526509313</v>
+        <v>-68.5172528945136</v>
       </c>
       <c r="D45" t="n">
-        <v>42.6154887536117</v>
+        <v>42.6154885858648</v>
       </c>
       <c r="E45" t="n">
-        <v>142.690335229086</v>
+        <v>142.690334584956</v>
       </c>
       <c r="F45" t="n">
         <v>114.240042114501</v>
       </c>
       <c r="G45" t="n">
-        <v>-28.4502931145847</v>
+        <v>-28.4502924704552</v>
       </c>
       <c r="H45" t="n">
-        <v>-6.11258039658572</v>
+        <v>-6.11258023352236</v>
       </c>
       <c r="I45" t="n">
-        <v>36.502908357026</v>
+        <v>36.5029083523424</v>
       </c>
       <c r="J45" t="n">
-        <v>114.240042114501</v>
+        <v>114.240042114502</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.00000000000042632564145606</v>
+        <v>0.000000000000383693077310454</v>
       </c>
     </row>
     <row r="46">
@@ -5389,31 +5389,31 @@
         <v>18.361815043837</v>
       </c>
       <c r="C46" t="n">
-        <v>-66.7040939523594</v>
+        <v>-66.7040941791837</v>
       </c>
       <c r="D46" t="n">
-        <v>41.412678700324</v>
+        <v>41.4126785411864</v>
       </c>
       <c r="E46" t="n">
-        <v>155.258017563675</v>
+        <v>155.258016937175</v>
       </c>
       <c r="F46" t="n">
         <v>133.076334988049</v>
       </c>
       <c r="G46" t="n">
-        <v>-22.1816825756265</v>
+        <v>-22.1816819491269</v>
       </c>
       <c r="H46" t="n">
-        <v>-5.02949786783929</v>
+        <v>-5.02949770541093</v>
       </c>
       <c r="I46" t="n">
-        <v>36.3831808324847</v>
+        <v>36.3831808357755</v>
       </c>
       <c r="J46" t="n">
-        <v>133.076334988048</v>
+        <v>133.076334988049</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="47">
@@ -5424,31 +5424,31 @@
         <v>17.2006632053819</v>
       </c>
       <c r="C47" t="n">
-        <v>-66.7040939523594</v>
+        <v>-66.7040941791837</v>
       </c>
       <c r="D47" t="n">
-        <v>35.567098135821</v>
+        <v>35.5670979823367</v>
       </c>
       <c r="E47" t="n">
-        <v>155.258017563675</v>
+        <v>155.258016937175</v>
       </c>
       <c r="F47" t="n">
         <v>133.076334988049</v>
       </c>
       <c r="G47" t="n">
-        <v>-22.1816825756265</v>
+        <v>-22.1816819491269</v>
       </c>
       <c r="H47" t="n">
-        <v>-4.80263396676771</v>
+        <v>-4.80263380691464</v>
       </c>
       <c r="I47" t="n">
-        <v>30.7644641690533</v>
+        <v>30.7644641754221</v>
       </c>
       <c r="J47" t="n">
-        <v>133.076334988048</v>
+        <v>133.076334988049</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="48">
@@ -5459,31 +5459,31 @@
         <v>17.7851196072229</v>
       </c>
       <c r="C48" t="n">
-        <v>-66.7040939523594</v>
+        <v>-66.7040941791837</v>
       </c>
       <c r="D48" t="n">
-        <v>38.5094239111882</v>
+        <v>38.5094237548583</v>
       </c>
       <c r="E48" t="n">
-        <v>155.258017563675</v>
+        <v>155.258016937175</v>
       </c>
       <c r="F48" t="n">
         <v>133.076334988049</v>
       </c>
       <c r="G48" t="n">
-        <v>-22.1816825756265</v>
+        <v>-22.1816819491269</v>
       </c>
       <c r="H48" t="n">
-        <v>-5.43198869337099</v>
+        <v>-5.43198853803347</v>
       </c>
       <c r="I48" t="n">
-        <v>33.0774352178172</v>
+        <v>33.0774352168248</v>
       </c>
       <c r="J48" t="n">
-        <v>133.076334988048</v>
+        <v>133.076334988049</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="49">
@@ -5494,31 +5494,31 @@
         <v>18.0352823363172</v>
       </c>
       <c r="C49" t="n">
-        <v>-66.7040939523594</v>
+        <v>-66.7040941791837</v>
       </c>
       <c r="D49" t="n">
-        <v>39.7688168163418</v>
+        <v>39.768816658794</v>
       </c>
       <c r="E49" t="n">
-        <v>155.258017563675</v>
+        <v>155.258016937175</v>
       </c>
       <c r="F49" t="n">
         <v>133.076334988049</v>
       </c>
       <c r="G49" t="n">
-        <v>-22.1816825756265</v>
+        <v>-22.1816819491269</v>
       </c>
       <c r="H49" t="n">
-        <v>-6.91756204764912</v>
+        <v>-6.91756189876745</v>
       </c>
       <c r="I49" t="n">
-        <v>32.8512547686927</v>
+        <v>32.8512547600265</v>
       </c>
       <c r="J49" t="n">
-        <v>133.076334988048</v>
+        <v>133.076334988049</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="50">
@@ -5529,31 +5529,31 @@
         <v>19.9983332810654</v>
       </c>
       <c r="C50" t="n">
-        <v>-59.4231805399072</v>
+        <v>-59.4231807555562</v>
       </c>
       <c r="D50" t="n">
-        <v>50.667643739671</v>
+        <v>50.6676435936504</v>
       </c>
       <c r="E50" t="n">
-        <v>204.810877042086</v>
+        <v>204.810876455934</v>
       </c>
       <c r="F50" t="n">
         <v>159.951916216035</v>
       </c>
       <c r="G50" t="n">
-        <v>-44.858960826051</v>
+        <v>-44.8589602398986</v>
       </c>
       <c r="H50" t="n">
-        <v>-9.2593540296021</v>
+        <v>-9.25935388911656</v>
       </c>
       <c r="I50" t="n">
-        <v>41.4082897100689</v>
+        <v>41.4082897045338</v>
       </c>
       <c r="J50" t="n">
-        <v>159.951916216034</v>
+        <v>159.951916216036</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.00000000000056843418860808</v>
       </c>
     </row>
     <row r="51">
@@ -5564,31 +5564,31 @@
         <v>19.8484447947693</v>
       </c>
       <c r="C51" t="n">
-        <v>-59.4231805399072</v>
+        <v>-59.4231807555562</v>
       </c>
       <c r="D51" t="n">
-        <v>49.913060925161</v>
+        <v>49.9130607798702</v>
       </c>
       <c r="E51" t="n">
-        <v>204.810877042086</v>
+        <v>204.810876455934</v>
       </c>
       <c r="F51" t="n">
         <v>159.951916216035</v>
       </c>
       <c r="G51" t="n">
-        <v>-44.858960826051</v>
+        <v>-44.8589602398986</v>
       </c>
       <c r="H51" t="n">
-        <v>-10.9782252931476</v>
+        <v>-10.9782251535994</v>
       </c>
       <c r="I51" t="n">
-        <v>38.9348356320134</v>
+        <v>38.9348356262708</v>
       </c>
       <c r="J51" t="n">
-        <v>159.951916216034</v>
+        <v>159.951916216036</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.00000000000056843418860808</v>
       </c>
     </row>
     <row r="52">
@@ -5599,31 +5599,31 @@
         <v>19.9193142906925</v>
       </c>
       <c r="C52" t="n">
-        <v>-59.4231805399072</v>
+        <v>-59.4231807555562</v>
       </c>
       <c r="D52" t="n">
-        <v>50.2698388539941</v>
+        <v>50.2698387083582</v>
       </c>
       <c r="E52" t="n">
-        <v>204.810877042086</v>
+        <v>204.810876455934</v>
       </c>
       <c r="F52" t="n">
         <v>159.951916216035</v>
       </c>
       <c r="G52" t="n">
-        <v>-44.858960826051</v>
+        <v>-44.8589602398986</v>
       </c>
       <c r="H52" t="n">
-        <v>-12.0741758382857</v>
+        <v>-12.0741756922159</v>
       </c>
       <c r="I52" t="n">
-        <v>38.1956630157084</v>
+        <v>38.1956630161423</v>
       </c>
       <c r="J52" t="n">
-        <v>159.951916216034</v>
+        <v>159.951916216036</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.00000000000056843418860808</v>
       </c>
     </row>
     <row r="53">
@@ -5634,31 +5634,31 @@
         <v>20.6523851333131</v>
       </c>
       <c r="C53" t="n">
-        <v>-59.4231805399072</v>
+        <v>-59.4231807555562</v>
       </c>
       <c r="D53" t="n">
-        <v>53.9603335232598</v>
+        <v>53.9603333740548</v>
       </c>
       <c r="E53" t="n">
-        <v>204.810877042086</v>
+        <v>204.810876455934</v>
       </c>
       <c r="F53" t="n">
         <v>159.951916216035</v>
       </c>
       <c r="G53" t="n">
-        <v>-44.858960826051</v>
+        <v>-44.8589602398986</v>
       </c>
       <c r="H53" t="n">
-        <v>-12.5472056650162</v>
+        <v>-12.5472055049661</v>
       </c>
       <c r="I53" t="n">
-        <v>41.4131278582436</v>
+        <v>41.4131278690887</v>
       </c>
       <c r="J53" t="n">
-        <v>159.951916216034</v>
+        <v>159.951916216036</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.00000000000056843418860808</v>
       </c>
     </row>
     <row r="54">
@@ -5669,31 +5669,31 @@
         <v>20.5110058990967</v>
       </c>
       <c r="C54" t="n">
-        <v>-78.0354590884903</v>
+        <v>-78.0354592601475</v>
       </c>
       <c r="D54" t="n">
-        <v>50.6507379977954</v>
+        <v>50.6507378055072</v>
       </c>
       <c r="E54" t="n">
-        <v>228.224046497764</v>
+        <v>228.224045703833</v>
       </c>
       <c r="F54" t="n">
         <v>188.010138809673</v>
       </c>
       <c r="G54" t="n">
-        <v>-40.2139076880911</v>
+        <v>-40.2139068941598</v>
       </c>
       <c r="H54" t="n">
-        <v>-12.3973147733393</v>
+        <v>-12.3973145918501</v>
       </c>
       <c r="I54" t="n">
-        <v>38.2534232244561</v>
+        <v>38.2534232136571</v>
       </c>
       <c r="J54" t="n">
-        <v>188.010138809672</v>
+        <v>188.010138809673</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.000000000000596855898038484</v>
       </c>
     </row>
     <row r="55">
@@ -5704,31 +5704,31 @@
         <v>20.2414536890036</v>
       </c>
       <c r="C55" t="n">
-        <v>-78.0354590884903</v>
+        <v>-78.0354592601475</v>
       </c>
       <c r="D55" t="n">
-        <v>49.2937327309086</v>
+        <v>49.2937325399328</v>
       </c>
       <c r="E55" t="n">
-        <v>228.224046497764</v>
+        <v>228.224045703833</v>
       </c>
       <c r="F55" t="n">
         <v>188.010138809673</v>
       </c>
       <c r="G55" t="n">
-        <v>-40.2139076880911</v>
+        <v>-40.2139068941598</v>
       </c>
       <c r="H55" t="n">
-        <v>-11.399823276142</v>
+        <v>-11.3998230792795</v>
       </c>
       <c r="I55" t="n">
-        <v>37.8939094547667</v>
+        <v>37.8939094606533</v>
       </c>
       <c r="J55" t="n">
-        <v>188.010138809672</v>
+        <v>188.010138809673</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.000000000000596855898038484</v>
       </c>
     </row>
     <row r="56">
@@ -5739,31 +5739,31 @@
         <v>21.9972618567386</v>
       </c>
       <c r="C56" t="n">
-        <v>-78.0354590884903</v>
+        <v>-78.0354592601475</v>
       </c>
       <c r="D56" t="n">
-        <v>58.1329885115851</v>
+        <v>58.1329883120607</v>
       </c>
       <c r="E56" t="n">
-        <v>228.224046497764</v>
+        <v>228.224045703833</v>
       </c>
       <c r="F56" t="n">
         <v>188.010138809673</v>
       </c>
       <c r="G56" t="n">
-        <v>-40.2139076880911</v>
+        <v>-40.2139068941598</v>
       </c>
       <c r="H56" t="n">
-        <v>-9.55473117342428</v>
+        <v>-9.55473096725453</v>
       </c>
       <c r="I56" t="n">
-        <v>48.5782573381608</v>
+        <v>48.5782573448062</v>
       </c>
       <c r="J56" t="n">
-        <v>188.010138809672</v>
+        <v>188.010138809673</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.000000000000596855898038484</v>
       </c>
     </row>
     <row r="57">
@@ -5774,31 +5774,31 @@
         <v>24.3836137539239</v>
       </c>
       <c r="C57" t="n">
-        <v>-78.0354590884903</v>
+        <v>-78.0354592601475</v>
       </c>
       <c r="D57" t="n">
-        <v>70.1465872574747</v>
+        <v>70.1465870463319</v>
       </c>
       <c r="E57" t="n">
-        <v>228.224046497764</v>
+        <v>228.224045703833</v>
       </c>
       <c r="F57" t="n">
         <v>188.010138809673</v>
       </c>
       <c r="G57" t="n">
-        <v>-40.2139076880911</v>
+        <v>-40.2139068941598</v>
       </c>
       <c r="H57" t="n">
-        <v>-6.8620384651862</v>
+        <v>-6.86203825577507</v>
       </c>
       <c r="I57" t="n">
-        <v>63.2845487922885</v>
+        <v>63.2845487905568</v>
       </c>
       <c r="J57" t="n">
-        <v>188.010138809672</v>
+        <v>188.010138809673</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.000000000000596855898038484</v>
       </c>
     </row>
     <row r="58">
@@ -5809,31 +5809,31 @@
         <v>17.8294871120887</v>
       </c>
       <c r="C58" t="n">
-        <v>-83.7818091254651</v>
+        <v>-83.7818092644295</v>
       </c>
       <c r="D58" t="n">
-        <v>36.3491223600031</v>
+        <v>36.3491221699239</v>
       </c>
       <c r="E58" t="n">
-        <v>147.974158745261</v>
+        <v>147.974157982452</v>
       </c>
       <c r="F58" t="n">
         <v>166.91619804328</v>
       </c>
       <c r="G58" t="n">
-        <v>18.9420392980181</v>
+        <v>18.9420400608279</v>
       </c>
       <c r="H58" t="n">
-        <v>-3.3217451514277</v>
+        <v>-3.32174494484113</v>
       </c>
       <c r="I58" t="n">
-        <v>33.0273772085754</v>
+        <v>33.0273772250828</v>
       </c>
       <c r="J58" t="n">
-        <v>166.916198043279</v>
+        <v>166.91619804328</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.00000000000056843418860808</v>
+        <v>0.000000000000483169060316868</v>
       </c>
     </row>
     <row r="59">
@@ -5844,31 +5844,31 @@
         <v>16.337537831675</v>
       </c>
       <c r="C59" t="n">
-        <v>-83.7818091254651</v>
+        <v>-83.7818092644295</v>
       </c>
       <c r="D59" t="n">
-        <v>28.8382099814683</v>
+        <v>28.8382097986529</v>
       </c>
       <c r="E59" t="n">
-        <v>147.974158745261</v>
+        <v>147.974157982452</v>
       </c>
       <c r="F59" t="n">
         <v>166.91619804328</v>
       </c>
       <c r="G59" t="n">
-        <v>18.9420392980181</v>
+        <v>18.9420400608279</v>
       </c>
       <c r="H59" t="n">
-        <v>1.31727416444852</v>
+        <v>1.31727436355173</v>
       </c>
       <c r="I59" t="n">
-        <v>30.1554841459168</v>
+        <v>30.1554841622047</v>
       </c>
       <c r="J59" t="n">
-        <v>166.916198043279</v>
+        <v>166.91619804328</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.00000000000056843418860808</v>
+        <v>0.000000000000483169060316868</v>
       </c>
     </row>
     <row r="60">
@@ -5879,31 +5879,31 @@
         <v>18.1861209559625</v>
       </c>
       <c r="C60" t="n">
-        <v>-83.7818091254651</v>
+        <v>-83.7818092644295</v>
       </c>
       <c r="D60" t="n">
-        <v>38.1445222356697</v>
+        <v>38.1445220438542</v>
       </c>
       <c r="E60" t="n">
-        <v>147.974158745261</v>
+        <v>147.974157982452</v>
       </c>
       <c r="F60" t="n">
         <v>166.91619804328</v>
       </c>
       <c r="G60" t="n">
-        <v>18.9420392980181</v>
+        <v>18.9420400608279</v>
       </c>
       <c r="H60" t="n">
-        <v>7.0550194824425</v>
+        <v>7.05501966940354</v>
       </c>
       <c r="I60" t="n">
-        <v>45.1995417181122</v>
+        <v>45.1995417132577</v>
       </c>
       <c r="J60" t="n">
-        <v>166.916198043279</v>
+        <v>166.91619804328</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.00000000000056843418860808</v>
+        <v>0.000000000000483169060316868</v>
       </c>
     </row>
     <row r="61">
@@ -5914,31 +5914,31 @@
         <v>19.4768244803585</v>
       </c>
       <c r="C61" t="n">
-        <v>-83.7818091254651</v>
+        <v>-83.7818092644295</v>
       </c>
       <c r="D61" t="n">
-        <v>44.6423041681202</v>
+        <v>44.6423039700206</v>
       </c>
       <c r="E61" t="n">
-        <v>147.974158745261</v>
+        <v>147.974157982452</v>
       </c>
       <c r="F61" t="n">
         <v>166.91619804328</v>
       </c>
       <c r="G61" t="n">
-        <v>18.9420392980181</v>
+        <v>18.9420400608279</v>
       </c>
       <c r="H61" t="n">
-        <v>13.8914908025542</v>
+        <v>13.8914909727143</v>
       </c>
       <c r="I61" t="n">
-        <v>58.5337949706745</v>
+        <v>58.5337949427349</v>
       </c>
       <c r="J61" t="n">
-        <v>166.916198043279</v>
+        <v>166.91619804328</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.00000000000056843418860808</v>
+        <v>0.000000000000483169060316868</v>
       </c>
     </row>
     <row r="62">
@@ -5949,31 +5949,31 @@
         <v>19.9117759252905</v>
       </c>
       <c r="C62" t="n">
-        <v>-27.8341012521888</v>
+        <v>-27.834101465661</v>
       </c>
       <c r="D62" t="n">
-        <v>54.6410055515842</v>
+        <v>54.641005491</v>
       </c>
       <c r="E62" t="n">
-        <v>230.375733793706</v>
+        <v>230.375733539946</v>
       </c>
       <c r="F62" t="n">
         <v>380.98488268492</v>
       </c>
       <c r="G62" t="n">
-        <v>150.609148891214</v>
+        <v>150.609149144974</v>
       </c>
       <c r="H62" t="n">
-        <v>21.8266881247837</v>
+        <v>21.826688273484</v>
       </c>
       <c r="I62" t="n">
-        <v>76.4676936763679</v>
+        <v>76.467693764484</v>
       </c>
       <c r="J62" t="n">
-        <v>380.98488268492</v>
+        <v>380.984882684921</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="63">
@@ -5984,31 +5984,31 @@
         <v>19.5096031794059</v>
       </c>
       <c r="C63" t="n">
-        <v>-27.8341012521888</v>
+        <v>-27.834101465661</v>
       </c>
       <c r="D63" t="n">
-        <v>52.6163494221639</v>
+        <v>52.6163493635378</v>
       </c>
       <c r="E63" t="n">
-        <v>230.375733793706</v>
+        <v>230.375733539946</v>
       </c>
       <c r="F63" t="n">
         <v>380.98488268492</v>
       </c>
       <c r="G63" t="n">
-        <v>150.609148891214</v>
+        <v>150.609149144974</v>
       </c>
       <c r="H63" t="n">
-        <v>31.3310066928833</v>
+        <v>31.3310067988957</v>
       </c>
       <c r="I63" t="n">
-        <v>83.9473561150473</v>
+        <v>83.9473561624335</v>
       </c>
       <c r="J63" t="n">
-        <v>380.98488268492</v>
+        <v>380.984882684921</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="64">
@@ -6019,31 +6019,31 @@
         <v>20.3047333337203</v>
       </c>
       <c r="C64" t="n">
-        <v>-27.8341012521888</v>
+        <v>-27.834101465661</v>
       </c>
       <c r="D64" t="n">
-        <v>56.6192689563519</v>
+        <v>56.6192688938545</v>
       </c>
       <c r="E64" t="n">
-        <v>230.375733793706</v>
+        <v>230.375733539946</v>
       </c>
       <c r="F64" t="n">
         <v>380.98488268492</v>
       </c>
       <c r="G64" t="n">
-        <v>150.609148891214</v>
+        <v>150.609149144974</v>
       </c>
       <c r="H64" t="n">
-        <v>42.4044465068531</v>
+        <v>42.4044465489494</v>
       </c>
       <c r="I64" t="n">
-        <v>99.023715463205</v>
+        <v>99.0237154428039</v>
       </c>
       <c r="J64" t="n">
-        <v>380.98488268492</v>
+        <v>380.984882684921</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="65">
@@ -6054,31 +6054,31 @@
         <v>22.267240788115</v>
       </c>
       <c r="C65" t="n">
-        <v>-27.8341012521888</v>
+        <v>-27.834101465661</v>
       </c>
       <c r="D65" t="n">
-        <v>66.4991098636063</v>
+        <v>66.499109791554</v>
       </c>
       <c r="E65" t="n">
-        <v>230.375733793706</v>
+        <v>230.375733539946</v>
       </c>
       <c r="F65" t="n">
         <v>380.98488268492</v>
       </c>
       <c r="G65" t="n">
-        <v>150.609148891214</v>
+        <v>150.609149144974</v>
       </c>
       <c r="H65" t="n">
-        <v>55.047007566693</v>
+        <v>55.0470075236452</v>
       </c>
       <c r="I65" t="n">
-        <v>121.546117430299</v>
+        <v>121.546117315199</v>
       </c>
       <c r="J65" t="n">
-        <v>380.98488268492</v>
+        <v>380.984882684921</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.000000000000625277607468888</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="66">
@@ -6089,31 +6089,31 @@
         <v>22.7451956072487</v>
       </c>
       <c r="C66" t="n">
-        <v>135.06911883157</v>
+        <v>135.06911866758</v>
       </c>
       <c r="D66" t="n">
-        <v>91.6428599644806</v>
+        <v>91.6428603338588</v>
       </c>
       <c r="E66" t="n">
-        <v>352.118923920521</v>
+        <v>352.118925412011</v>
       </c>
       <c r="F66" t="n">
         <v>646.806945030182</v>
       </c>
       <c r="G66" t="n">
-        <v>294.688021109661</v>
+        <v>294.688019618171</v>
       </c>
       <c r="H66" t="n">
-        <v>69.2586898724031</v>
+        <v>69.2586897229829</v>
       </c>
       <c r="I66" t="n">
-        <v>160.901549836884</v>
+        <v>160.901550056842</v>
       </c>
       <c r="J66" t="n">
-        <v>646.806945030181</v>
+        <v>646.806945030182</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -6124,31 +6124,31 @@
         <v>22.1727590834854</v>
       </c>
       <c r="C67" t="n">
-        <v>135.06911883157</v>
+        <v>135.06911866758</v>
       </c>
       <c r="D67" t="n">
-        <v>88.7610457978039</v>
+        <v>88.7610461699691</v>
       </c>
       <c r="E67" t="n">
-        <v>352.118923920521</v>
+        <v>352.118925412011</v>
       </c>
       <c r="F67" t="n">
         <v>646.806945030182</v>
       </c>
       <c r="G67" t="n">
-        <v>294.688021109661</v>
+        <v>294.688019618171</v>
       </c>
       <c r="H67" t="n">
-        <v>76.7086889566919</v>
+        <v>76.708688675342</v>
       </c>
       <c r="I67" t="n">
-        <v>165.469734754496</v>
+        <v>165.469734845311</v>
       </c>
       <c r="J67" t="n">
-        <v>646.806945030181</v>
+        <v>646.806945030182</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -6159,31 +6159,31 @@
         <v>20.7446089013393</v>
       </c>
       <c r="C68" t="n">
-        <v>135.06911883157</v>
+        <v>135.06911866758</v>
       </c>
       <c r="D68" t="n">
-        <v>81.571316882547</v>
+        <v>81.5713172616654</v>
       </c>
       <c r="E68" t="n">
-        <v>352.118923920521</v>
+        <v>352.118925412011</v>
       </c>
       <c r="F68" t="n">
         <v>646.806945030182</v>
       </c>
       <c r="G68" t="n">
-        <v>294.688021109661</v>
+        <v>294.688019618171</v>
       </c>
       <c r="H68" t="n">
-        <v>77.3970048195595</v>
+        <v>77.3970043807224</v>
       </c>
       <c r="I68" t="n">
-        <v>158.968321702106</v>
+        <v>158.968321642388</v>
       </c>
       <c r="J68" t="n">
-        <v>646.806945030181</v>
+        <v>646.806945030182</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -6194,31 +6194,31 @@
         <v>22.4474063888097</v>
       </c>
       <c r="C69" t="n">
-        <v>135.06911883157</v>
+        <v>135.06911866758</v>
       </c>
       <c r="D69" t="n">
-        <v>90.1437012756895</v>
+        <v>90.1437016465175</v>
       </c>
       <c r="E69" t="n">
-        <v>352.118923920521</v>
+        <v>352.118925412011</v>
       </c>
       <c r="F69" t="n">
         <v>646.806945030182</v>
       </c>
       <c r="G69" t="n">
-        <v>294.688021109661</v>
+        <v>294.688019618171</v>
       </c>
       <c r="H69" t="n">
-        <v>71.3236374610059</v>
+        <v>71.323636839124</v>
       </c>
       <c r="I69" t="n">
-        <v>161.467338736695</v>
+        <v>161.467338485642</v>
       </c>
       <c r="J69" t="n">
-        <v>646.806945030181</v>
+        <v>646.806945030182</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -6229,31 +6229,31 @@
         <v>23.697173383041</v>
       </c>
       <c r="C70" t="n">
-        <v>370.09832977221</v>
+        <v>370.098329638001</v>
       </c>
       <c r="D70" t="n">
-        <v>129.240129322096</v>
+        <v>129.240130321264</v>
       </c>
       <c r="E70" t="n">
-        <v>511.32153268887</v>
+        <v>511.321536690996</v>
       </c>
       <c r="F70" t="n">
         <v>607.441084491194</v>
       </c>
       <c r="G70" t="n">
-        <v>96.1195518023233</v>
+        <v>96.1195478001975</v>
       </c>
       <c r="H70" t="n">
-        <v>58.488586881031</v>
+        <v>58.488586050547</v>
       </c>
       <c r="I70" t="n">
-        <v>187.728716203127</v>
+        <v>187.728716371811</v>
       </c>
       <c r="J70" t="n">
-        <v>607.441084491193</v>
+        <v>607.441084491194</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -6264,31 +6264,31 @@
         <v>23.7909819053948</v>
       </c>
       <c r="C71" t="n">
-        <v>370.09832977221</v>
+        <v>370.098329638001</v>
       </c>
       <c r="D71" t="n">
-        <v>129.712389070473</v>
+        <v>129.712390069184</v>
       </c>
       <c r="E71" t="n">
-        <v>511.32153268887</v>
+        <v>511.321536690996</v>
       </c>
       <c r="F71" t="n">
         <v>607.441084491194</v>
       </c>
       <c r="G71" t="n">
-        <v>96.1195518023233</v>
+        <v>96.1195478001975</v>
       </c>
       <c r="H71" t="n">
-        <v>39.5710870768609</v>
+        <v>39.5710860949171</v>
       </c>
       <c r="I71" t="n">
-        <v>169.283476147334</v>
+        <v>169.283476164101</v>
       </c>
       <c r="J71" t="n">
-        <v>607.441084491193</v>
+        <v>607.441084491194</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -6299,31 +6299,31 @@
         <v>21.7619159153809</v>
       </c>
       <c r="C72" t="n">
-        <v>370.09832977221</v>
+        <v>370.098329638001</v>
       </c>
       <c r="D72" t="n">
-        <v>119.497472879064</v>
+        <v>119.497473887654</v>
       </c>
       <c r="E72" t="n">
-        <v>511.32153268887</v>
+        <v>511.321536690996</v>
       </c>
       <c r="F72" t="n">
         <v>607.441084491194</v>
       </c>
       <c r="G72" t="n">
-        <v>96.1195518023233</v>
+        <v>96.1195478001975</v>
       </c>
       <c r="H72" t="n">
-        <v>14.5711380484955</v>
+        <v>14.5711369722344</v>
       </c>
       <c r="I72" t="n">
-        <v>134.068610927559</v>
+        <v>134.068610859889</v>
       </c>
       <c r="J72" t="n">
-        <v>607.441084491193</v>
+        <v>607.441084491194</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6334,31 +6334,31 @@
         <v>24.418508207518</v>
       </c>
       <c r="C73" t="n">
-        <v>370.09832977221</v>
+        <v>370.098329638001</v>
       </c>
       <c r="D73" t="n">
-        <v>132.871541417238</v>
+        <v>132.871542412894</v>
       </c>
       <c r="E73" t="n">
-        <v>511.32153268887</v>
+        <v>511.321536690996</v>
       </c>
       <c r="F73" t="n">
         <v>607.441084491194</v>
       </c>
       <c r="G73" t="n">
-        <v>96.1195518023233</v>
+        <v>96.1195478001975</v>
       </c>
       <c r="H73" t="n">
-        <v>-16.5112602040651</v>
+        <v>-16.5112613175011</v>
       </c>
       <c r="I73" t="n">
-        <v>116.360281213173</v>
+        <v>116.360281095393</v>
       </c>
       <c r="J73" t="n">
-        <v>607.441084491193</v>
+        <v>607.441084491194</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6369,31 +6369,31 @@
         <v>23.6932818309947</v>
       </c>
       <c r="C74" t="n">
-        <v>302.748791150652</v>
+        <v>302.748791043506</v>
       </c>
       <c r="D74" t="n">
-        <v>119.820074214394</v>
+        <v>119.82007503675</v>
       </c>
       <c r="E74" t="n">
-        <v>505.593914350302</v>
+        <v>505.593917614278</v>
       </c>
       <c r="F74" t="n">
         <v>239.389</v>
       </c>
       <c r="G74" t="n">
-        <v>-266.204914350302</v>
+        <v>-266.204917614278</v>
       </c>
       <c r="H74" t="n">
-        <v>-53.676107680821</v>
+        <v>-53.6761087742895</v>
       </c>
       <c r="I74" t="n">
-        <v>66.1439665335733</v>
+        <v>66.1439662624607</v>
       </c>
       <c r="J74" t="n">
-        <v>239.388999999999</v>
+        <v>239.389</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.00000000000116529008664656</v>
+        <v>-0.000000000000369482222595252</v>
       </c>
     </row>
     <row r="75">
@@ -6404,31 +6404,31 @@
         <v>23.1865842158533</v>
       </c>
       <c r="C75" t="n">
-        <v>302.748791150652</v>
+        <v>302.748791043506</v>
       </c>
       <c r="D75" t="n">
-        <v>117.269209088011</v>
+        <v>117.269209912834</v>
       </c>
       <c r="E75" t="n">
-        <v>505.593914350302</v>
+        <v>505.593917614278</v>
       </c>
       <c r="F75" t="n">
         <v>239.389</v>
       </c>
       <c r="G75" t="n">
-        <v>-266.204914350302</v>
+        <v>-266.204917614278</v>
       </c>
       <c r="H75" t="n">
-        <v>-73.6920950342253</v>
+        <v>-73.6920960087169</v>
       </c>
       <c r="I75" t="n">
-        <v>43.577114053786</v>
+        <v>43.5771139041173</v>
       </c>
       <c r="J75" t="n">
-        <v>239.388999999999</v>
+        <v>239.389</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.00000000000116529008664656</v>
+        <v>-0.000000000000369482222595252</v>
       </c>
     </row>
     <row r="76">
@@ -6439,31 +6439,31 @@
         <v>25.2577942325929</v>
       </c>
       <c r="C76" t="n">
-        <v>302.748791150652</v>
+        <v>302.748791043506</v>
       </c>
       <c r="D76" t="n">
-        <v>127.696290730466</v>
+        <v>127.696291545204</v>
       </c>
       <c r="E76" t="n">
-        <v>505.593914350302</v>
+        <v>505.593917614278</v>
       </c>
       <c r="F76" t="n">
         <v>239.389</v>
       </c>
       <c r="G76" t="n">
-        <v>-266.204914350302</v>
+        <v>-266.204917614278</v>
       </c>
       <c r="H76" t="n">
-        <v>-76.5592222642781</v>
+        <v>-76.5592230207833</v>
       </c>
       <c r="I76" t="n">
-        <v>51.1370684661875</v>
+        <v>51.137068524421</v>
       </c>
       <c r="J76" t="n">
-        <v>239.388999999999</v>
+        <v>239.389</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.00000000000116529008664656</v>
+        <v>-0.000000000000369482222595252</v>
       </c>
     </row>
     <row r="77">
@@ -6474,31 +6474,31 @@
         <v>27.8623397205592</v>
       </c>
       <c r="C77" t="n">
-        <v>302.748791150652</v>
+        <v>302.748791043506</v>
       </c>
       <c r="D77" t="n">
-        <v>140.808340317431</v>
+        <v>140.808341119489</v>
       </c>
       <c r="E77" t="n">
-        <v>505.593914350302</v>
+        <v>505.593917614278</v>
       </c>
       <c r="F77" t="n">
         <v>239.389</v>
       </c>
       <c r="G77" t="n">
-        <v>-266.204914350302</v>
+        <v>-266.204917614278</v>
       </c>
       <c r="H77" t="n">
-        <v>-62.2774893709793</v>
+        <v>-62.2774898104887</v>
       </c>
       <c r="I77" t="n">
-        <v>78.5308509464521</v>
+        <v>78.5308513090006</v>
       </c>
       <c r="J77" t="n">
-        <v>239.388999999999</v>
+        <v>239.389</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.00000000000116529008664656</v>
+        <v>-0.000000000000369482222595252</v>
       </c>
     </row>
     <row r="78">
@@ -6509,31 +6509,31 @@
         <v>26.3851917433467</v>
       </c>
       <c r="C78" t="n">
-        <v>-97.1775305531693</v>
+        <v>-97.1775306294895</v>
       </c>
       <c r="D78" t="n">
-        <v>77.551322916811</v>
+        <v>77.5513226578973</v>
       </c>
       <c r="E78" t="n">
-        <v>353.822188447601</v>
+        <v>353.822187369764</v>
       </c>
       <c r="F78" t="n">
         <v>300.464</v>
       </c>
       <c r="G78" t="n">
-        <v>-53.3581884476013</v>
+        <v>-53.3581873697644</v>
       </c>
       <c r="H78" t="n">
-        <v>-30.846896354329</v>
+        <v>-30.8468963778332</v>
       </c>
       <c r="I78" t="n">
-        <v>46.7044265624819</v>
+        <v>46.7044262800641</v>
       </c>
       <c r="J78" t="n">
-        <v>300.463999999999</v>
+        <v>300.464</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.00000000000113686837721616</v>
+        <v>-0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="79">
@@ -6544,31 +6544,31 @@
         <v>27.1759284750954</v>
       </c>
       <c r="C79" t="n">
-        <v>-97.1775305531693</v>
+        <v>-97.1775306294895</v>
       </c>
       <c r="D79" t="n">
-        <v>81.5321246669928</v>
+        <v>81.5321244042293</v>
       </c>
       <c r="E79" t="n">
-        <v>353.822188447601</v>
+        <v>353.822187369764</v>
       </c>
       <c r="F79" t="n">
         <v>300.464</v>
       </c>
       <c r="G79" t="n">
-        <v>-53.3581884476013</v>
+        <v>-53.3581873697644</v>
       </c>
       <c r="H79" t="n">
-        <v>-11.2717194506976</v>
+        <v>-11.2717191906142</v>
       </c>
       <c r="I79" t="n">
-        <v>70.2604052162952</v>
+        <v>70.2604052136151</v>
       </c>
       <c r="J79" t="n">
-        <v>300.463999999999</v>
+        <v>300.464</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.00000000000113686837721616</v>
+        <v>-0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="80">
@@ -6579,31 +6579,31 @@
         <v>29.7979194213777</v>
       </c>
       <c r="C80" t="n">
-        <v>-97.1775305531693</v>
+        <v>-97.1775306294895</v>
       </c>
       <c r="D80" t="n">
-        <v>94.7319998325726</v>
+        <v>94.7319995570433</v>
       </c>
       <c r="E80" t="n">
-        <v>353.822188447601</v>
+        <v>353.822187369764</v>
       </c>
       <c r="F80" t="n">
         <v>300.464</v>
       </c>
       <c r="G80" t="n">
-        <v>-53.3581884476013</v>
+        <v>-53.3581873697644</v>
       </c>
       <c r="H80" t="n">
-        <v>-3.55195866008488</v>
+        <v>-3.55195824883168</v>
       </c>
       <c r="I80" t="n">
-        <v>91.1800411724877</v>
+        <v>91.1800413082116</v>
       </c>
       <c r="J80" t="n">
-        <v>300.463999999999</v>
+        <v>300.464</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.00000000000113686837721616</v>
+        <v>-0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="81">
@@ -6614,31 +6614,31 @@
         <v>30.8456811231635</v>
       </c>
       <c r="C81" t="n">
-        <v>-97.1775305531693</v>
+        <v>-97.1775306294895</v>
       </c>
       <c r="D81" t="n">
-        <v>100.006741031225</v>
+        <v>100.006740750595</v>
       </c>
       <c r="E81" t="n">
-        <v>353.822188447601</v>
+        <v>353.822187369764</v>
       </c>
       <c r="F81" t="n">
         <v>300.464</v>
       </c>
       <c r="G81" t="n">
-        <v>-53.3581884476013</v>
+        <v>-53.3581873697644</v>
       </c>
       <c r="H81" t="n">
-        <v>-7.68761398249101</v>
+        <v>-7.68761355248571</v>
       </c>
       <c r="I81" t="n">
-        <v>92.319127048734</v>
+        <v>92.3191271981088</v>
       </c>
       <c r="J81" t="n">
-        <v>300.463999999999</v>
+        <v>300.464</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.00000000000113686837721616</v>
+        <v>-0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="82">
@@ -6649,31 +6649,31 @@
         <v>28.3199367135976</v>
       </c>
       <c r="C82" t="n">
-        <v>-107.61328122878</v>
+        <v>-107.613281235941</v>
       </c>
       <c r="D82" t="n">
-        <v>85.8348058386561</v>
+        <v>85.8348055519906</v>
       </c>
       <c r="E82" t="n">
-        <v>345.611013238738</v>
+        <v>345.611012089879</v>
       </c>
       <c r="F82" t="n">
         <v>251.42084084465</v>
       </c>
       <c r="G82" t="n">
-        <v>-94.190172394088</v>
+        <v>-94.1901712452289</v>
       </c>
       <c r="H82" t="n">
-        <v>-23.6786854179159</v>
+        <v>-23.6786851015763</v>
       </c>
       <c r="I82" t="n">
-        <v>62.1561204207402</v>
+        <v>62.1561204504143</v>
       </c>
       <c r="J82" t="n">
-        <v>251.420840844649</v>
+        <v>251.42084084465</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.00000000000110844666778576</v>
+        <v>-0.00000000000028421709430404</v>
       </c>
     </row>
     <row r="83">
@@ -6684,31 +6684,31 @@
         <v>27.291562099305</v>
       </c>
       <c r="C83" t="n">
-        <v>-107.61328122878</v>
+        <v>-107.613281235941</v>
       </c>
       <c r="D83" t="n">
-        <v>80.6576649521245</v>
+        <v>80.6576646704659</v>
       </c>
       <c r="E83" t="n">
-        <v>345.611013238738</v>
+        <v>345.611012089879</v>
       </c>
       <c r="F83" t="n">
         <v>251.42084084465</v>
       </c>
       <c r="G83" t="n">
-        <v>-94.190172394088</v>
+        <v>-94.1901712452289</v>
       </c>
       <c r="H83" t="n">
-        <v>-30.0226570643285</v>
+        <v>-30.0226568051049</v>
       </c>
       <c r="I83" t="n">
-        <v>50.635007887796</v>
+        <v>50.6350078653609</v>
       </c>
       <c r="J83" t="n">
-        <v>251.420840844649</v>
+        <v>251.42084084465</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.00000000000110844666778576</v>
+        <v>-0.00000000000028421709430404</v>
       </c>
     </row>
     <row r="84">
@@ -6719,31 +6719,31 @@
         <v>27.9939672419872</v>
       </c>
       <c r="C84" t="n">
-        <v>-107.61328122878</v>
+        <v>-107.613281235941</v>
       </c>
       <c r="D84" t="n">
-        <v>84.1937794502365</v>
+        <v>84.1937791651581</v>
       </c>
       <c r="E84" t="n">
-        <v>345.611013238738</v>
+        <v>345.611012089879</v>
       </c>
       <c r="F84" t="n">
         <v>251.42084084465</v>
       </c>
       <c r="G84" t="n">
-        <v>-94.190172394088</v>
+        <v>-94.1901712452289</v>
       </c>
       <c r="H84" t="n">
-        <v>-26.7195289217285</v>
+        <v>-26.7195286630716</v>
       </c>
       <c r="I84" t="n">
-        <v>57.474250528508</v>
+        <v>57.4742505020865</v>
       </c>
       <c r="J84" t="n">
-        <v>251.420840844649</v>
+        <v>251.42084084465</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.00000000000110844666778576</v>
+        <v>-0.00000000000028421709430404</v>
       </c>
     </row>
     <row r="85">
@@ -6754,31 +6754,31 @@
         <v>30.1255435904953</v>
       </c>
       <c r="C85" t="n">
-        <v>-107.61328122878</v>
+        <v>-107.613281235941</v>
       </c>
       <c r="D85" t="n">
-        <v>94.9247629977211</v>
+        <v>94.9247627022646</v>
       </c>
       <c r="E85" t="n">
-        <v>345.611013238738</v>
+        <v>345.611012089879</v>
       </c>
       <c r="F85" t="n">
         <v>251.42084084465</v>
       </c>
       <c r="G85" t="n">
-        <v>-94.190172394088</v>
+        <v>-94.1901712452289</v>
       </c>
       <c r="H85" t="n">
-        <v>-13.7693009901162</v>
+        <v>-13.7693006754764</v>
       </c>
       <c r="I85" t="n">
-        <v>81.1554620076049</v>
+        <v>81.1554620267882</v>
       </c>
       <c r="J85" t="n">
-        <v>251.420840844649</v>
+        <v>251.42084084465</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.00000000000110844666778576</v>
+        <v>-0.00000000000028421709430404</v>
       </c>
     </row>
     <row r="86">
@@ -6789,31 +6789,31 @@
         <v>28.3958802543955</v>
       </c>
       <c r="C86" t="n">
-        <v>-154.271639008019</v>
+        <v>-154.271639017486</v>
       </c>
       <c r="D86" t="n">
-        <v>79.7046823912818</v>
+        <v>79.7046819788029</v>
       </c>
       <c r="E86" t="n">
-        <v>326.015420175935</v>
+        <v>326.01541851906</v>
       </c>
       <c r="F86" t="n">
         <v>400.837090297355</v>
       </c>
       <c r="G86" t="n">
-        <v>74.82167012142</v>
+        <v>74.8216717782959</v>
       </c>
       <c r="H86" t="n">
-        <v>8.8280267305086</v>
+        <v>8.82802715768073</v>
       </c>
       <c r="I86" t="n">
-        <v>88.5327091217904</v>
+        <v>88.5327091364836</v>
       </c>
       <c r="J86" t="n">
-        <v>400.837090297354</v>
+        <v>400.837090297355</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.00000000000136424205265939</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="87">
@@ -6824,31 +6824,31 @@
         <v>27.5791815217975</v>
       </c>
       <c r="C87" t="n">
-        <v>-154.271639008019</v>
+        <v>-154.271639017486</v>
       </c>
       <c r="D87" t="n">
-        <v>75.5931802774143</v>
+        <v>75.5931798689116</v>
       </c>
       <c r="E87" t="n">
-        <v>326.015420175935</v>
+        <v>326.01541851906</v>
       </c>
       <c r="F87" t="n">
         <v>400.837090297355</v>
       </c>
       <c r="G87" t="n">
-        <v>74.82167012142</v>
+        <v>74.8216717782959</v>
       </c>
       <c r="H87" t="n">
-        <v>21.8179141386969</v>
+        <v>21.8179146057008</v>
       </c>
       <c r="I87" t="n">
-        <v>97.4110944161112</v>
+        <v>97.4110944746124</v>
       </c>
       <c r="J87" t="n">
-        <v>400.837090297354</v>
+        <v>400.837090297355</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.00000000000136424205265939</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="88">
@@ -6859,31 +6859,31 @@
         <v>28.596445544594</v>
       </c>
       <c r="C88" t="n">
-        <v>-154.271639008019</v>
+        <v>-154.271639017486</v>
       </c>
       <c r="D88" t="n">
-        <v>80.7143871718883</v>
+        <v>80.7143867584328</v>
       </c>
       <c r="E88" t="n">
-        <v>326.015420175935</v>
+        <v>326.01541851906</v>
       </c>
       <c r="F88" t="n">
         <v>400.837090297355</v>
       </c>
       <c r="G88" t="n">
-        <v>74.82167012142</v>
+        <v>74.8216717782959</v>
       </c>
       <c r="H88" t="n">
-        <v>25.2003612344488</v>
+        <v>25.2003616685839</v>
       </c>
       <c r="I88" t="n">
-        <v>105.914748406337</v>
+        <v>105.914748427017</v>
       </c>
       <c r="J88" t="n">
-        <v>400.837090297354</v>
+        <v>400.837090297355</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.00000000000136424205265939</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="89">
@@ -6894,31 +6894,31 @@
         <v>30.4415467331331</v>
       </c>
       <c r="C89" t="n">
-        <v>-154.271639008019</v>
+        <v>-154.271639017486</v>
       </c>
       <c r="D89" t="n">
-        <v>90.003170335351</v>
+        <v>90.0031699129123</v>
       </c>
       <c r="E89" t="n">
-        <v>326.015420175935</v>
+        <v>326.01541851906</v>
       </c>
       <c r="F89" t="n">
         <v>400.837090297355</v>
       </c>
       <c r="G89" t="n">
-        <v>74.82167012142</v>
+        <v>74.8216717782959</v>
       </c>
       <c r="H89" t="n">
-        <v>18.9753680177643</v>
+        <v>18.9753683463299</v>
       </c>
       <c r="I89" t="n">
-        <v>108.978538353115</v>
+        <v>108.978538259242</v>
       </c>
       <c r="J89" t="n">
-        <v>400.837090297354</v>
+        <v>400.837090297355</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.00000000000136424205265939</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="90">
@@ -6929,31 +6929,31 @@
         <v>29.785657601326</v>
       </c>
       <c r="C90" t="n">
-        <v>-11.3095789465415</v>
+        <v>-11.3095789497673</v>
       </c>
       <c r="D90" t="n">
-        <v>106.655483400295</v>
+        <v>106.655483365296</v>
       </c>
       <c r="E90" t="n">
-        <v>448.606790813043</v>
+        <v>448.606790651787</v>
       </c>
       <c r="F90" t="n">
         <v>431.679681741255</v>
       </c>
       <c r="G90" t="n">
-        <v>-16.9271090717883</v>
+        <v>-16.9271089105317</v>
       </c>
       <c r="H90" t="n">
-        <v>3.14293448864335</v>
+        <v>3.14293463893893</v>
       </c>
       <c r="I90" t="n">
-        <v>109.798417888938</v>
+        <v>109.798418004235</v>
       </c>
       <c r="J90" t="n">
-        <v>431.679681741254</v>
+        <v>431.679681741255</v>
       </c>
       <c r="K90" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>-0.000000000000056843418860808</v>
       </c>
     </row>
     <row r="91">
@@ -6964,31 +6964,31 @@
         <v>30.0660556110785</v>
       </c>
       <c r="C91" t="n">
-        <v>-11.3095789465415</v>
+        <v>-11.3095789497673</v>
       </c>
       <c r="D91" t="n">
-        <v>108.067089619095</v>
+        <v>108.067089582731</v>
       </c>
       <c r="E91" t="n">
-        <v>448.606790813043</v>
+        <v>448.606790651787</v>
       </c>
       <c r="F91" t="n">
         <v>431.679681741255</v>
       </c>
       <c r="G91" t="n">
-        <v>-16.9271090717883</v>
+        <v>-16.9271089105317</v>
       </c>
       <c r="H91" t="n">
-        <v>-6.1399236256413</v>
+        <v>-6.13992359064623</v>
       </c>
       <c r="I91" t="n">
-        <v>101.927165993453</v>
+        <v>101.927165992085</v>
       </c>
       <c r="J91" t="n">
-        <v>431.679681741254</v>
+        <v>431.679681741255</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>-0.000000000000056843418860808</v>
       </c>
     </row>
     <row r="92">
@@ -6999,31 +6999,31 @@
         <v>30.6000332292611</v>
       </c>
       <c r="C92" t="n">
-        <v>-11.3095789465415</v>
+        <v>-11.3095789497673</v>
       </c>
       <c r="D92" t="n">
-        <v>110.755290320633</v>
+        <v>110.75529028167</v>
       </c>
       <c r="E92" t="n">
-        <v>448.606790813043</v>
+        <v>448.606790651787</v>
       </c>
       <c r="F92" t="n">
         <v>431.679681741255</v>
       </c>
       <c r="G92" t="n">
-        <v>-16.9271090717883</v>
+        <v>-16.9271089105317</v>
       </c>
       <c r="H92" t="n">
-        <v>-8.87320632508963</v>
+        <v>-8.87320634242553</v>
       </c>
       <c r="I92" t="n">
-        <v>101.882083995544</v>
+        <v>101.882083939244</v>
       </c>
       <c r="J92" t="n">
-        <v>431.679681741254</v>
+        <v>431.679681741255</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>-0.000000000000056843418860808</v>
       </c>
     </row>
     <row r="93">
@@ -7034,31 +7034,31 @@
         <v>33.0579022756853</v>
       </c>
       <c r="C93" t="n">
-        <v>-11.3095789465415</v>
+        <v>-11.3095789497673</v>
       </c>
       <c r="D93" t="n">
-        <v>123.128927473021</v>
+        <v>123.128927422091</v>
       </c>
       <c r="E93" t="n">
-        <v>448.606790813043</v>
+        <v>448.606790651787</v>
       </c>
       <c r="F93" t="n">
         <v>431.679681741255</v>
       </c>
       <c r="G93" t="n">
-        <v>-16.9271090717883</v>
+        <v>-16.9271089105317</v>
       </c>
       <c r="H93" t="n">
-        <v>-5.05691360970164</v>
+        <v>-5.05691361639898</v>
       </c>
       <c r="I93" t="n">
-        <v>118.072013863319</v>
+        <v>118.072013805692</v>
       </c>
       <c r="J93" t="n">
-        <v>431.679681741254</v>
+        <v>431.679681741255</v>
       </c>
       <c r="K93" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>-0.000000000000056843418860808</v>
       </c>
     </row>
     <row r="94">
@@ -7066,34 +7066,34 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>31.5323192214638</v>
+        <v>31.5323192085143</v>
       </c>
       <c r="C94" t="n">
-        <v>-23.2413491185133</v>
+        <v>-23.2413490803715</v>
       </c>
       <c r="D94" t="n">
-        <v>113.783289008231</v>
+        <v>113.783288873314</v>
       </c>
       <c r="E94" t="n">
-        <v>463.81550676572</v>
+        <v>463.81550624045</v>
       </c>
       <c r="F94" t="n">
         <v>521.331863303597</v>
       </c>
       <c r="G94" t="n">
-        <v>57.5163565378767</v>
+        <v>57.5163570631471</v>
       </c>
       <c r="H94" t="n">
-        <v>5.30895452052268</v>
+        <v>5.30895458743342</v>
       </c>
       <c r="I94" t="n">
-        <v>119.092243528754</v>
+        <v>119.092243460748</v>
       </c>
       <c r="J94" t="n">
-        <v>521.331863303596</v>
+        <v>521.331863303597</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -7101,34 +7101,34 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>31.8402897751419</v>
+        <v>31.8402897656666</v>
       </c>
       <c r="C95" t="n">
-        <v>-23.2413491185133</v>
+        <v>-23.2413490803715</v>
       </c>
       <c r="D95" t="n">
-        <v>115.333703539216</v>
+        <v>115.333703420289</v>
       </c>
       <c r="E95" t="n">
-        <v>463.81550676572</v>
+        <v>463.81550624045</v>
       </c>
       <c r="F95" t="n">
         <v>521.331863303597</v>
       </c>
       <c r="G95" t="n">
-        <v>57.5163565378767</v>
+        <v>57.5163570631471</v>
       </c>
       <c r="H95" t="n">
-        <v>13.0833556181909</v>
+        <v>13.0833557403077</v>
       </c>
       <c r="I95" t="n">
-        <v>128.417059157407</v>
+        <v>128.417059160597</v>
       </c>
       <c r="J95" t="n">
-        <v>521.331863303596</v>
+        <v>521.331863303597</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -7136,34 +7136,34 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>31.7842500528192</v>
+        <v>31.78425004077</v>
       </c>
       <c r="C96" t="n">
-        <v>-23.2413491185133</v>
+        <v>-23.2413490803715</v>
       </c>
       <c r="D96" t="n">
-        <v>115.051583061255</v>
+        <v>115.051582929644</v>
       </c>
       <c r="E96" t="n">
-        <v>463.81550676572</v>
+        <v>463.81550624045</v>
       </c>
       <c r="F96" t="n">
         <v>521.331863303597</v>
       </c>
       <c r="G96" t="n">
-        <v>57.5163565378767</v>
+        <v>57.5163570631471</v>
       </c>
       <c r="H96" t="n">
-        <v>18.2662896833031</v>
+        <v>18.2662898422239</v>
       </c>
       <c r="I96" t="n">
-        <v>133.317872744558</v>
+        <v>133.317872771868</v>
       </c>
       <c r="J96" t="n">
-        <v>521.331863303596</v>
+        <v>521.331863303597</v>
       </c>
       <c r="K96" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -7171,34 +7171,34 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>32.6970587688838</v>
+        <v>32.6970587560878</v>
       </c>
       <c r="C97" t="n">
-        <v>-23.2413491185133</v>
+        <v>-23.2413490803715</v>
       </c>
       <c r="D97" t="n">
-        <v>119.646931157018</v>
+        <v>119.646931017203</v>
       </c>
       <c r="E97" t="n">
-        <v>463.81550676572</v>
+        <v>463.81550624045</v>
       </c>
       <c r="F97" t="n">
         <v>521.331863303597</v>
       </c>
       <c r="G97" t="n">
-        <v>57.5163565378767</v>
+        <v>57.5163570631471</v>
       </c>
       <c r="H97" t="n">
-        <v>20.8577567158591</v>
+        <v>20.857756893182</v>
       </c>
       <c r="I97" t="n">
-        <v>140.504687872877</v>
+        <v>140.504687910385</v>
       </c>
       <c r="J97" t="n">
-        <v>521.331863303596</v>
+        <v>521.331863303597</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7231,13 +7231,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>20.6875840798076</v>
+        <v>20.6875840988558</v>
       </c>
       <c r="C2" t="n">
         <v>11.1469028155255</v>
       </c>
       <c r="D2" t="n">
-        <v>8.39961637108207</v>
+        <v>8.39961588747034</v>
       </c>
     </row>
     <row r="3">
@@ -7245,13 +7245,13 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>23.6156277832207</v>
+        <v>23.6156277935456</v>
       </c>
       <c r="C3" t="n">
         <v>11.6813206587827</v>
       </c>
       <c r="D3" t="n">
-        <v>8.39961637108207</v>
+        <v>8.39961588747034</v>
       </c>
     </row>
     <row r="4">
@@ -7259,13 +7259,13 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>24.780255458371</v>
+        <v>24.7802554557865</v>
       </c>
       <c r="C4" t="n">
         <v>11.8182562487431</v>
       </c>
       <c r="D4" t="n">
-        <v>8.39961637108207</v>
+        <v>8.39961588747034</v>
       </c>
     </row>
     <row r="5">
@@ -7273,13 +7273,13 @@
         <v>34</v>
       </c>
       <c r="B5" t="n">
-        <v>31.5314128818406</v>
+        <v>31.5314128550522</v>
       </c>
       <c r="C5" t="n">
         <v>13.0176848533636</v>
       </c>
       <c r="D5" t="n">
-        <v>8.39961637108207</v>
+        <v>8.39961588747034</v>
       </c>
     </row>
     <row r="6">
@@ -7287,13 +7287,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.9874279549276</v>
+        <v>31.9874279792772</v>
       </c>
       <c r="C6" t="n">
         <v>12.3892763792865</v>
       </c>
       <c r="D6" t="n">
-        <v>27.5223693667206</v>
+        <v>27.5223690355917</v>
       </c>
     </row>
     <row r="7">
@@ -7301,13 +7301,13 @@
         <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>31.3417025275023</v>
+        <v>31.3417025320769</v>
       </c>
       <c r="C7" t="n">
         <v>12.2749895402599</v>
       </c>
       <c r="D7" t="n">
-        <v>27.5223693667206</v>
+        <v>27.5223690355917</v>
       </c>
     </row>
     <row r="8">
@@ -7315,13 +7315,13 @@
         <v>36</v>
       </c>
       <c r="B8" t="n">
-        <v>27.5352880154357</v>
+        <v>27.5352880064589</v>
       </c>
       <c r="C8" t="n">
         <v>11.7356560380167</v>
       </c>
       <c r="D8" t="n">
-        <v>27.5223693667206</v>
+        <v>27.5223690355917</v>
       </c>
     </row>
     <row r="9">
@@ -7329,13 +7329,13 @@
         <v>37</v>
       </c>
       <c r="B9" t="n">
-        <v>24.3342303489197</v>
+        <v>24.3342303289728</v>
       </c>
       <c r="C9" t="n">
         <v>11.5193540330228</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5223693667206</v>
+        <v>27.5223690355917</v>
       </c>
     </row>
     <row r="10">
@@ -7343,13 +7343,13 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>31.6762006962695</v>
+        <v>31.6762006959562</v>
       </c>
       <c r="C10" t="n">
         <v>13.2313468461927</v>
       </c>
       <c r="D10" t="n">
-        <v>40.8218319659803</v>
+        <v>40.8218316360935</v>
       </c>
     </row>
     <row r="11">
@@ -7357,13 +7357,13 @@
         <v>38</v>
       </c>
       <c r="B11" t="n">
-        <v>33.2054595657092</v>
+        <v>33.2054595600762</v>
       </c>
       <c r="C11" t="n">
         <v>14.1226585458536</v>
       </c>
       <c r="D11" t="n">
-        <v>40.8218319659803</v>
+        <v>40.8218316360935</v>
       </c>
     </row>
     <row r="12">
@@ -7371,13 +7371,13 @@
         <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>31.0837435109751</v>
+        <v>31.0837435106118</v>
       </c>
       <c r="C12" t="n">
         <v>14.2539598031749</v>
       </c>
       <c r="D12" t="n">
-        <v>40.8218319659803</v>
+        <v>40.8218316360935</v>
       </c>
     </row>
     <row r="13">
@@ -7385,13 +7385,13 @@
         <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>34.8087822948793</v>
+        <v>34.8087823011896</v>
       </c>
       <c r="C13" t="n">
         <v>15.5118564485863</v>
       </c>
       <c r="D13" t="n">
-        <v>40.8218319659803</v>
+        <v>40.8218316360935</v>
       </c>
     </row>
     <row r="14">
@@ -7399,13 +7399,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>31.1390943604829</v>
+        <v>31.1390943073377</v>
       </c>
       <c r="C14" t="n">
         <v>16.1184436592147</v>
       </c>
       <c r="D14" t="n">
-        <v>10.079110823115</v>
+        <v>10.0791105380232</v>
       </c>
     </row>
     <row r="15">
@@ -7413,13 +7413,13 @@
         <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>32.0187454759667</v>
+        <v>32.0187454466014</v>
       </c>
       <c r="C15" t="n">
         <v>16.415677221503</v>
       </c>
       <c r="D15" t="n">
-        <v>10.079110823115</v>
+        <v>10.0791105380232</v>
       </c>
     </row>
     <row r="16">
@@ -7427,13 +7427,13 @@
         <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>12.1129621836542</v>
+        <v>12.1129622054669</v>
       </c>
       <c r="C16" t="n">
         <v>12.2234703618602</v>
       </c>
       <c r="D16" t="n">
-        <v>10.079110823115</v>
+        <v>10.0791105380232</v>
       </c>
     </row>
     <row r="17">
@@ -7441,13 +7441,13 @@
         <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>12.4617020955333</v>
+        <v>12.4617021562317</v>
       </c>
       <c r="C17" t="n">
         <v>11.6938999707585</v>
       </c>
       <c r="D17" t="n">
-        <v>10.079110823115</v>
+        <v>10.0791105380232</v>
       </c>
     </row>
     <row r="18">
@@ -7455,13 +7455,13 @@
         <v>7</v>
       </c>
       <c r="B18" t="n">
-        <v>30.0386256741338</v>
+        <v>30.0386256521418</v>
       </c>
       <c r="C18" t="n">
         <v>15.3258805423762</v>
       </c>
       <c r="D18" t="n">
-        <v>-29.5979987745932</v>
+        <v>-29.597999062939</v>
       </c>
     </row>
     <row r="19">
@@ -7469,13 +7469,13 @@
         <v>44</v>
       </c>
       <c r="B19" t="n">
-        <v>30.3042545238644</v>
+        <v>30.3042545283106</v>
       </c>
       <c r="C19" t="n">
         <v>14.8733170138056</v>
       </c>
       <c r="D19" t="n">
-        <v>-29.5979987745932</v>
+        <v>-29.597999062939</v>
       </c>
     </row>
     <row r="20">
@@ -7483,13 +7483,13 @@
         <v>45</v>
       </c>
       <c r="B20" t="n">
-        <v>25.5451962654351</v>
+        <v>25.545196281355</v>
       </c>
       <c r="C20" t="n">
         <v>13.8768502823917</v>
       </c>
       <c r="D20" t="n">
-        <v>-29.5979987745932</v>
+        <v>-29.597999062939</v>
       </c>
     </row>
     <row r="21">
@@ -7497,13 +7497,13 @@
         <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>26.931948577918</v>
+        <v>26.931948579544</v>
       </c>
       <c r="C21" t="n">
         <v>14.555360709698</v>
       </c>
       <c r="D21" t="n">
-        <v>-29.5979987745932</v>
+        <v>-29.597999062939</v>
       </c>
     </row>
     <row r="22">
@@ -7511,13 +7511,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>27.1606021076845</v>
+        <v>27.1606021175457</v>
       </c>
       <c r="C22" t="n">
         <v>15.0667257975563</v>
       </c>
       <c r="D22" t="n">
-        <v>-15.4848241688878</v>
+        <v>-15.4848244466202</v>
       </c>
     </row>
     <row r="23">
@@ -7525,13 +7525,13 @@
         <v>47</v>
       </c>
       <c r="B23" t="n">
-        <v>27.3810358410094</v>
+        <v>27.3810358332759</v>
       </c>
       <c r="C23" t="n">
         <v>15.6731164614357</v>
       </c>
       <c r="D23" t="n">
-        <v>-15.4848241688878</v>
+        <v>-15.4848244466202</v>
       </c>
     </row>
     <row r="24">
@@ -7539,13 +7539,13 @@
         <v>48</v>
       </c>
       <c r="B24" t="n">
-        <v>26.3375806321254</v>
+        <v>26.3375806234145</v>
       </c>
       <c r="C24" t="n">
         <v>15.7338178579393</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.4848241688878</v>
+        <v>-15.4848244466202</v>
       </c>
     </row>
     <row r="25">
@@ -7553,13 +7553,13 @@
         <v>49</v>
       </c>
       <c r="B25" t="n">
-        <v>24.3874512616519</v>
+        <v>24.3874512682357</v>
       </c>
       <c r="C25" t="n">
         <v>15.3197862581617</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.4848241688878</v>
+        <v>-15.4848244466202</v>
       </c>
     </row>
     <row r="26">
@@ -7567,13 +7567,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>19.7741818499806</v>
+        <v>19.7741818258663</v>
       </c>
       <c r="C26" t="n">
         <v>14.7328890677592</v>
       </c>
       <c r="D26" t="n">
-        <v>-38.956809690297</v>
+        <v>-38.9568099526343</v>
       </c>
     </row>
     <row r="27">
@@ -7581,13 +7581,13 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>21.047014886685</v>
+        <v>21.0470148834192</v>
       </c>
       <c r="C27" t="n">
         <v>14.7581102218019</v>
       </c>
       <c r="D27" t="n">
-        <v>-38.956809690297</v>
+        <v>-38.9568099526343</v>
       </c>
     </row>
     <row r="28">
@@ -7595,13 +7595,13 @@
         <v>51</v>
       </c>
       <c r="B28" t="n">
-        <v>22.6532668257199</v>
+        <v>22.6532668362559</v>
       </c>
       <c r="C28" t="n">
         <v>14.9432457255233</v>
       </c>
       <c r="D28" t="n">
-        <v>-38.956809690297</v>
+        <v>-38.9568099526343</v>
       </c>
     </row>
     <row r="29">
@@ -7609,13 +7609,13 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>25.0539467561409</v>
+        <v>25.0539467729859</v>
       </c>
       <c r="C29" t="n">
         <v>15.3798692978029</v>
       </c>
       <c r="D29" t="n">
-        <v>-38.956809690297</v>
+        <v>-38.9568099526343</v>
       </c>
     </row>
     <row r="30">
@@ -7623,13 +7623,13 @@
         <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>28.8509564334777</v>
+        <v>28.8509564281329</v>
       </c>
       <c r="C30" t="n">
         <v>16.3753445128911</v>
       </c>
       <c r="D30" t="n">
-        <v>-45.7305282727894</v>
+        <v>-45.7305285447635</v>
       </c>
     </row>
     <row r="31">
@@ -7637,13 +7637,13 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>21.9389533859392</v>
+        <v>21.9389533889704</v>
       </c>
       <c r="C31" t="n">
         <v>15.0887588439557</v>
       </c>
       <c r="D31" t="n">
-        <v>-45.7305282727894</v>
+        <v>-45.7305285447635</v>
       </c>
     </row>
     <row r="32">
@@ -7651,13 +7651,13 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>23.0159070500761</v>
+        <v>23.0159070535421</v>
       </c>
       <c r="C32" t="n">
         <v>15.4220345279437</v>
       </c>
       <c r="D32" t="n">
-        <v>-45.7305282727894</v>
+        <v>-45.7305285447635</v>
       </c>
     </row>
     <row r="33">
@@ -7665,13 +7665,13 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>29.0946804022551</v>
+        <v>29.0946804011035</v>
       </c>
       <c r="C33" t="n">
         <v>16.7818139661638</v>
       </c>
       <c r="D33" t="n">
-        <v>-45.7305282727894</v>
+        <v>-45.7305285447635</v>
       </c>
     </row>
     <row r="34">
@@ -7679,13 +7679,13 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>26.8707871080478</v>
+        <v>26.8707870985463</v>
       </c>
       <c r="C34" t="n">
         <v>16.6647643679365</v>
       </c>
       <c r="D34" t="n">
-        <v>-50.7597952727682</v>
+        <v>-50.759795525979</v>
       </c>
     </row>
     <row r="35">
@@ -7693,13 +7693,13 @@
         <v>56</v>
       </c>
       <c r="B35" t="n">
-        <v>22.2986456920337</v>
+        <v>22.2986456904723</v>
       </c>
       <c r="C35" t="n">
         <v>15.8762559792141</v>
       </c>
       <c r="D35" t="n">
-        <v>-50.7597952727682</v>
+        <v>-50.759795525979</v>
       </c>
     </row>
     <row r="36">
@@ -7707,13 +7707,13 @@
         <v>57</v>
       </c>
       <c r="B36" t="n">
-        <v>23.9748997241839</v>
+        <v>23.9748997269921</v>
       </c>
       <c r="C36" t="n">
         <v>16.2633429336138</v>
       </c>
       <c r="D36" t="n">
-        <v>-50.7597952727682</v>
+        <v>-50.759795525979</v>
       </c>
     </row>
     <row r="37">
@@ -7721,13 +7721,13 @@
         <v>58</v>
       </c>
       <c r="B37" t="n">
-        <v>27.0931637675933</v>
+        <v>27.0931637758488</v>
       </c>
       <c r="C37" t="n">
         <v>16.8712965733395</v>
       </c>
       <c r="D37" t="n">
-        <v>-50.7597952727682</v>
+        <v>-50.759795525979</v>
       </c>
     </row>
     <row r="38">
@@ -7735,13 +7735,13 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>21.5679220723922</v>
+        <v>21.5679220623213</v>
       </c>
       <c r="C38" t="n">
         <v>16.0508175345883</v>
       </c>
       <c r="D38" t="n">
-        <v>-63.5301900436575</v>
+        <v>-63.5301902870934</v>
       </c>
     </row>
     <row r="39">
@@ -7749,13 +7749,13 @@
         <v>59</v>
       </c>
       <c r="B39" t="n">
-        <v>21.857234976307</v>
+        <v>21.8572349752125</v>
       </c>
       <c r="C39" t="n">
         <v>16.0463647623357</v>
       </c>
       <c r="D39" t="n">
-        <v>-63.5301900436575</v>
+        <v>-63.5301902870934</v>
       </c>
     </row>
     <row r="40">
@@ -7763,13 +7763,13 @@
         <v>60</v>
       </c>
       <c r="B40" t="n">
-        <v>22.4949303293213</v>
+        <v>22.4949303351873</v>
       </c>
       <c r="C40" t="n">
         <v>16.1262140171378</v>
       </c>
       <c r="D40" t="n">
-        <v>-63.5301900436575</v>
+        <v>-63.5301902870934</v>
       </c>
     </row>
     <row r="41">
@@ -7777,13 +7777,13 @@
         <v>61</v>
       </c>
       <c r="B41" t="n">
-        <v>29.1788866827235</v>
+        <v>29.1788866880237</v>
       </c>
       <c r="C41" t="n">
         <v>17.4221779704851</v>
       </c>
       <c r="D41" t="n">
-        <v>-63.5301900436575</v>
+        <v>-63.5301902870934</v>
       </c>
     </row>
     <row r="42">
@@ -7791,13 +7791,13 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>24.3979251360161</v>
+        <v>24.3979251360919</v>
       </c>
       <c r="C42" t="n">
         <v>16.5941465714623</v>
       </c>
       <c r="D42" t="n">
-        <v>-68.5172526509313</v>
+        <v>-68.5172528945136</v>
       </c>
     </row>
     <row r="43">
@@ -7805,13 +7805,13 @@
         <v>62</v>
       </c>
       <c r="B43" t="n">
-        <v>23.2518287419084</v>
+        <v>23.2518287463601</v>
       </c>
       <c r="C43" t="n">
         <v>16.300238106994</v>
       </c>
       <c r="D43" t="n">
-        <v>-68.5172526509313</v>
+        <v>-68.5172528945136</v>
       </c>
     </row>
     <row r="44">
@@ -7819,13 +7819,13 @@
         <v>63</v>
       </c>
       <c r="B44" t="n">
-        <v>30.0873798795504</v>
+        <v>30.0873798797072</v>
       </c>
       <c r="C44" t="n">
         <v>17.5421545403324</v>
       </c>
       <c r="D44" t="n">
-        <v>-68.5172526509313</v>
+        <v>-68.5172528945136</v>
       </c>
     </row>
     <row r="45">
@@ -7833,13 +7833,13 @@
         <v>64</v>
       </c>
       <c r="B45" t="n">
-        <v>36.502908357026</v>
+        <v>36.5029083523424</v>
       </c>
       <c r="C45" t="n">
         <v>18.6510086357636</v>
       </c>
       <c r="D45" t="n">
-        <v>-68.5172526509313</v>
+        <v>-68.5172528945136</v>
       </c>
     </row>
     <row r="46">
@@ -7847,13 +7847,13 @@
         <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>36.3831808324847</v>
+        <v>36.3831808357755</v>
       </c>
       <c r="C46" t="n">
         <v>18.361815043837</v>
       </c>
       <c r="D46" t="n">
-        <v>-66.7040939523594</v>
+        <v>-66.7040941791837</v>
       </c>
     </row>
     <row r="47">
@@ -7861,13 +7861,13 @@
         <v>65</v>
       </c>
       <c r="B47" t="n">
-        <v>30.7644641690533</v>
+        <v>30.7644641754221</v>
       </c>
       <c r="C47" t="n">
         <v>17.2006632053819</v>
       </c>
       <c r="D47" t="n">
-        <v>-66.7040939523594</v>
+        <v>-66.7040941791837</v>
       </c>
     </row>
     <row r="48">
@@ -7875,13 +7875,13 @@
         <v>66</v>
       </c>
       <c r="B48" t="n">
-        <v>33.0774352178172</v>
+        <v>33.0774352168248</v>
       </c>
       <c r="C48" t="n">
         <v>17.7851196072229</v>
       </c>
       <c r="D48" t="n">
-        <v>-66.7040939523594</v>
+        <v>-66.7040941791837</v>
       </c>
     </row>
     <row r="49">
@@ -7889,13 +7889,13 @@
         <v>67</v>
       </c>
       <c r="B49" t="n">
-        <v>32.8512547686927</v>
+        <v>32.8512547600265</v>
       </c>
       <c r="C49" t="n">
         <v>18.0352823363172</v>
       </c>
       <c r="D49" t="n">
-        <v>-66.7040939523594</v>
+        <v>-66.7040941791837</v>
       </c>
     </row>
     <row r="50">
@@ -7903,13 +7903,13 @@
         <v>15</v>
       </c>
       <c r="B50" t="n">
-        <v>41.4082897100689</v>
+        <v>41.4082897045338</v>
       </c>
       <c r="C50" t="n">
         <v>19.9983332810654</v>
       </c>
       <c r="D50" t="n">
-        <v>-59.4231805399072</v>
+        <v>-59.4231807555562</v>
       </c>
     </row>
     <row r="51">
@@ -7917,13 +7917,13 @@
         <v>68</v>
       </c>
       <c r="B51" t="n">
-        <v>38.9348356320134</v>
+        <v>38.9348356262708</v>
       </c>
       <c r="C51" t="n">
         <v>19.8484447947693</v>
       </c>
       <c r="D51" t="n">
-        <v>-59.4231805399072</v>
+        <v>-59.4231807555562</v>
       </c>
     </row>
     <row r="52">
@@ -7931,13 +7931,13 @@
         <v>69</v>
       </c>
       <c r="B52" t="n">
-        <v>38.1956630157084</v>
+        <v>38.1956630161423</v>
       </c>
       <c r="C52" t="n">
         <v>19.9193142906925</v>
       </c>
       <c r="D52" t="n">
-        <v>-59.4231805399072</v>
+        <v>-59.4231807555562</v>
       </c>
     </row>
     <row r="53">
@@ -7945,13 +7945,13 @@
         <v>70</v>
       </c>
       <c r="B53" t="n">
-        <v>41.4131278582436</v>
+        <v>41.4131278690887</v>
       </c>
       <c r="C53" t="n">
         <v>20.6523851333131</v>
       </c>
       <c r="D53" t="n">
-        <v>-59.4231805399072</v>
+        <v>-59.4231807555562</v>
       </c>
     </row>
     <row r="54">
@@ -7959,13 +7959,13 @@
         <v>16</v>
       </c>
       <c r="B54" t="n">
-        <v>38.2534232244561</v>
+        <v>38.2534232136571</v>
       </c>
       <c r="C54" t="n">
         <v>20.5110058990967</v>
       </c>
       <c r="D54" t="n">
-        <v>-78.0354590884903</v>
+        <v>-78.0354592601475</v>
       </c>
     </row>
     <row r="55">
@@ -7973,13 +7973,13 @@
         <v>71</v>
       </c>
       <c r="B55" t="n">
-        <v>37.8939094547667</v>
+        <v>37.8939094606533</v>
       </c>
       <c r="C55" t="n">
         <v>20.2414536890036</v>
       </c>
       <c r="D55" t="n">
-        <v>-78.0354590884903</v>
+        <v>-78.0354592601475</v>
       </c>
     </row>
     <row r="56">
@@ -7987,13 +7987,13 @@
         <v>72</v>
       </c>
       <c r="B56" t="n">
-        <v>48.5782573381608</v>
+        <v>48.5782573448062</v>
       </c>
       <c r="C56" t="n">
         <v>21.9972618567386</v>
       </c>
       <c r="D56" t="n">
-        <v>-78.0354590884903</v>
+        <v>-78.0354592601475</v>
       </c>
     </row>
     <row r="57">
@@ -8001,13 +8001,13 @@
         <v>73</v>
       </c>
       <c r="B57" t="n">
-        <v>63.2845487922885</v>
+        <v>63.2845487905568</v>
       </c>
       <c r="C57" t="n">
         <v>24.3836137539239</v>
       </c>
       <c r="D57" t="n">
-        <v>-78.0354590884903</v>
+        <v>-78.0354592601475</v>
       </c>
     </row>
     <row r="58">
@@ -8015,13 +8015,13 @@
         <v>17</v>
       </c>
       <c r="B58" t="n">
-        <v>33.0273772085754</v>
+        <v>33.0273772250828</v>
       </c>
       <c r="C58" t="n">
         <v>17.8294871120887</v>
       </c>
       <c r="D58" t="n">
-        <v>-83.7818091254651</v>
+        <v>-83.7818092644295</v>
       </c>
     </row>
     <row r="59">
@@ -8029,13 +8029,13 @@
         <v>74</v>
       </c>
       <c r="B59" t="n">
-        <v>30.1554841459168</v>
+        <v>30.1554841622047</v>
       </c>
       <c r="C59" t="n">
         <v>16.337537831675</v>
       </c>
       <c r="D59" t="n">
-        <v>-83.7818091254651</v>
+        <v>-83.7818092644295</v>
       </c>
     </row>
     <row r="60">
@@ -8043,13 +8043,13 @@
         <v>75</v>
       </c>
       <c r="B60" t="n">
-        <v>45.1995417181122</v>
+        <v>45.1995417132577</v>
       </c>
       <c r="C60" t="n">
         <v>18.1861209559625</v>
       </c>
       <c r="D60" t="n">
-        <v>-83.7818091254651</v>
+        <v>-83.7818092644295</v>
       </c>
     </row>
     <row r="61">
@@ -8057,13 +8057,13 @@
         <v>76</v>
       </c>
       <c r="B61" t="n">
-        <v>58.5337949706745</v>
+        <v>58.5337949427349</v>
       </c>
       <c r="C61" t="n">
         <v>19.4768244803585</v>
       </c>
       <c r="D61" t="n">
-        <v>-83.7818091254651</v>
+        <v>-83.7818092644295</v>
       </c>
     </row>
     <row r="62">
@@ -8071,13 +8071,13 @@
         <v>18</v>
       </c>
       <c r="B62" t="n">
-        <v>76.4676936763679</v>
+        <v>76.467693764484</v>
       </c>
       <c r="C62" t="n">
         <v>19.9117759252905</v>
       </c>
       <c r="D62" t="n">
-        <v>-27.8341012521888</v>
+        <v>-27.834101465661</v>
       </c>
     </row>
     <row r="63">
@@ -8085,13 +8085,13 @@
         <v>77</v>
       </c>
       <c r="B63" t="n">
-        <v>83.9473561150473</v>
+        <v>83.9473561624335</v>
       </c>
       <c r="C63" t="n">
         <v>19.5096031794059</v>
       </c>
       <c r="D63" t="n">
-        <v>-27.8341012521888</v>
+        <v>-27.834101465661</v>
       </c>
     </row>
     <row r="64">
@@ -8099,13 +8099,13 @@
         <v>78</v>
       </c>
       <c r="B64" t="n">
-        <v>99.023715463205</v>
+        <v>99.0237154428039</v>
       </c>
       <c r="C64" t="n">
         <v>20.3047333337203</v>
       </c>
       <c r="D64" t="n">
-        <v>-27.8341012521888</v>
+        <v>-27.834101465661</v>
       </c>
     </row>
     <row r="65">
@@ -8113,13 +8113,13 @@
         <v>79</v>
       </c>
       <c r="B65" t="n">
-        <v>121.546117430299</v>
+        <v>121.546117315199</v>
       </c>
       <c r="C65" t="n">
         <v>22.267240788115</v>
       </c>
       <c r="D65" t="n">
-        <v>-27.8341012521888</v>
+        <v>-27.834101465661</v>
       </c>
     </row>
     <row r="66">
@@ -8127,13 +8127,13 @@
         <v>19</v>
       </c>
       <c r="B66" t="n">
-        <v>160.901549836884</v>
+        <v>160.901550056842</v>
       </c>
       <c r="C66" t="n">
         <v>22.7451956072487</v>
       </c>
       <c r="D66" t="n">
-        <v>135.06911883157</v>
+        <v>135.06911866758</v>
       </c>
     </row>
     <row r="67">
@@ -8141,13 +8141,13 @@
         <v>80</v>
       </c>
       <c r="B67" t="n">
-        <v>165.469734754496</v>
+        <v>165.469734845311</v>
       </c>
       <c r="C67" t="n">
         <v>22.1727590834854</v>
       </c>
       <c r="D67" t="n">
-        <v>135.06911883157</v>
+        <v>135.06911866758</v>
       </c>
     </row>
     <row r="68">
@@ -8155,13 +8155,13 @@
         <v>81</v>
       </c>
       <c r="B68" t="n">
-        <v>158.968321702106</v>
+        <v>158.968321642388</v>
       </c>
       <c r="C68" t="n">
         <v>20.7446089013393</v>
       </c>
       <c r="D68" t="n">
-        <v>135.06911883157</v>
+        <v>135.06911866758</v>
       </c>
     </row>
     <row r="69">
@@ -8169,13 +8169,13 @@
         <v>82</v>
       </c>
       <c r="B69" t="n">
-        <v>161.467338736695</v>
+        <v>161.467338485642</v>
       </c>
       <c r="C69" t="n">
         <v>22.4474063888097</v>
       </c>
       <c r="D69" t="n">
-        <v>135.06911883157</v>
+        <v>135.06911866758</v>
       </c>
     </row>
     <row r="70">
@@ -8183,13 +8183,13 @@
         <v>20</v>
       </c>
       <c r="B70" t="n">
-        <v>187.728716203127</v>
+        <v>187.728716371811</v>
       </c>
       <c r="C70" t="n">
         <v>23.697173383041</v>
       </c>
       <c r="D70" t="n">
-        <v>370.09832977221</v>
+        <v>370.098329638001</v>
       </c>
     </row>
     <row r="71">
@@ -8197,13 +8197,13 @@
         <v>83</v>
       </c>
       <c r="B71" t="n">
-        <v>169.283476147334</v>
+        <v>169.283476164101</v>
       </c>
       <c r="C71" t="n">
         <v>23.7909819053948</v>
       </c>
       <c r="D71" t="n">
-        <v>370.09832977221</v>
+        <v>370.098329638001</v>
       </c>
     </row>
     <row r="72">
@@ -8211,13 +8211,13 @@
         <v>84</v>
       </c>
       <c r="B72" t="n">
-        <v>134.068610927559</v>
+        <v>134.068610859889</v>
       </c>
       <c r="C72" t="n">
         <v>21.7619159153809</v>
       </c>
       <c r="D72" t="n">
-        <v>370.09832977221</v>
+        <v>370.098329638001</v>
       </c>
     </row>
     <row r="73">
@@ -8225,13 +8225,13 @@
         <v>85</v>
       </c>
       <c r="B73" t="n">
-        <v>116.360281213173</v>
+        <v>116.360281095393</v>
       </c>
       <c r="C73" t="n">
         <v>24.418508207518</v>
       </c>
       <c r="D73" t="n">
-        <v>370.09832977221</v>
+        <v>370.098329638001</v>
       </c>
     </row>
     <row r="74">
@@ -8239,13 +8239,13 @@
         <v>21</v>
       </c>
       <c r="B74" t="n">
-        <v>66.1439665335733</v>
+        <v>66.1439662624607</v>
       </c>
       <c r="C74" t="n">
         <v>23.6932818309947</v>
       </c>
       <c r="D74" t="n">
-        <v>302.748791150652</v>
+        <v>302.748791043506</v>
       </c>
     </row>
     <row r="75">
@@ -8253,13 +8253,13 @@
         <v>86</v>
       </c>
       <c r="B75" t="n">
-        <v>43.577114053786</v>
+        <v>43.5771139041173</v>
       </c>
       <c r="C75" t="n">
         <v>23.1865842158533</v>
       </c>
       <c r="D75" t="n">
-        <v>302.748791150652</v>
+        <v>302.748791043506</v>
       </c>
     </row>
     <row r="76">
@@ -8267,13 +8267,13 @@
         <v>87</v>
       </c>
       <c r="B76" t="n">
-        <v>51.1370684661875</v>
+        <v>51.137068524421</v>
       </c>
       <c r="C76" t="n">
         <v>25.2577942325929</v>
       </c>
       <c r="D76" t="n">
-        <v>302.748791150652</v>
+        <v>302.748791043506</v>
       </c>
     </row>
     <row r="77">
@@ -8281,13 +8281,13 @@
         <v>88</v>
       </c>
       <c r="B77" t="n">
-        <v>78.5308509464521</v>
+        <v>78.5308513090006</v>
       </c>
       <c r="C77" t="n">
         <v>27.8623397205592</v>
       </c>
       <c r="D77" t="n">
-        <v>302.748791150652</v>
+        <v>302.748791043506</v>
       </c>
     </row>
     <row r="78">
@@ -8295,13 +8295,13 @@
         <v>22</v>
       </c>
       <c r="B78" t="n">
-        <v>46.7044265624819</v>
+        <v>46.7044262800641</v>
       </c>
       <c r="C78" t="n">
         <v>26.3851917433467</v>
       </c>
       <c r="D78" t="n">
-        <v>-97.1775305531693</v>
+        <v>-97.1775306294895</v>
       </c>
     </row>
     <row r="79">
@@ -8309,13 +8309,13 @@
         <v>89</v>
       </c>
       <c r="B79" t="n">
-        <v>70.2604052162952</v>
+        <v>70.2604052136151</v>
       </c>
       <c r="C79" t="n">
         <v>27.1759284750954</v>
       </c>
       <c r="D79" t="n">
-        <v>-97.1775305531693</v>
+        <v>-97.1775306294895</v>
       </c>
     </row>
     <row r="80">
@@ -8323,13 +8323,13 @@
         <v>90</v>
       </c>
       <c r="B80" t="n">
-        <v>91.1800411724877</v>
+        <v>91.1800413082116</v>
       </c>
       <c r="C80" t="n">
         <v>29.7979194213777</v>
       </c>
       <c r="D80" t="n">
-        <v>-97.1775305531693</v>
+        <v>-97.1775306294895</v>
       </c>
     </row>
     <row r="81">
@@ -8337,13 +8337,13 @@
         <v>91</v>
       </c>
       <c r="B81" t="n">
-        <v>92.319127048734</v>
+        <v>92.3191271981088</v>
       </c>
       <c r="C81" t="n">
         <v>30.8456811231635</v>
       </c>
       <c r="D81" t="n">
-        <v>-97.1775305531693</v>
+        <v>-97.1775306294895</v>
       </c>
     </row>
     <row r="82">
@@ -8351,13 +8351,13 @@
         <v>23</v>
       </c>
       <c r="B82" t="n">
-        <v>62.1561204207402</v>
+        <v>62.1561204504143</v>
       </c>
       <c r="C82" t="n">
         <v>28.3199367135976</v>
       </c>
       <c r="D82" t="n">
-        <v>-107.61328122878</v>
+        <v>-107.613281235941</v>
       </c>
     </row>
     <row r="83">
@@ -8365,13 +8365,13 @@
         <v>92</v>
       </c>
       <c r="B83" t="n">
-        <v>50.635007887796</v>
+        <v>50.6350078653609</v>
       </c>
       <c r="C83" t="n">
         <v>27.291562099305</v>
       </c>
       <c r="D83" t="n">
-        <v>-107.61328122878</v>
+        <v>-107.613281235941</v>
       </c>
     </row>
     <row r="84">
@@ -8379,13 +8379,13 @@
         <v>93</v>
       </c>
       <c r="B84" t="n">
-        <v>57.474250528508</v>
+        <v>57.4742505020865</v>
       </c>
       <c r="C84" t="n">
         <v>27.9939672419872</v>
       </c>
       <c r="D84" t="n">
-        <v>-107.61328122878</v>
+        <v>-107.613281235941</v>
       </c>
     </row>
     <row r="85">
@@ -8393,13 +8393,13 @@
         <v>94</v>
       </c>
       <c r="B85" t="n">
-        <v>81.1554620076049</v>
+        <v>81.1554620267882</v>
       </c>
       <c r="C85" t="n">
         <v>30.1255435904953</v>
       </c>
       <c r="D85" t="n">
-        <v>-107.61328122878</v>
+        <v>-107.613281235941</v>
       </c>
     </row>
     <row r="86">
@@ -8407,13 +8407,13 @@
         <v>24</v>
       </c>
       <c r="B86" t="n">
-        <v>88.5327091217904</v>
+        <v>88.5327091364836</v>
       </c>
       <c r="C86" t="n">
         <v>28.3958802543955</v>
       </c>
       <c r="D86" t="n">
-        <v>-154.271639008019</v>
+        <v>-154.271639017486</v>
       </c>
     </row>
     <row r="87">
@@ -8421,13 +8421,13 @@
         <v>95</v>
       </c>
       <c r="B87" t="n">
-        <v>97.4110944161112</v>
+        <v>97.4110944746124</v>
       </c>
       <c r="C87" t="n">
         <v>27.5791815217975</v>
       </c>
       <c r="D87" t="n">
-        <v>-154.271639008019</v>
+        <v>-154.271639017486</v>
       </c>
     </row>
     <row r="88">
@@ -8435,13 +8435,13 @@
         <v>96</v>
       </c>
       <c r="B88" t="n">
-        <v>105.914748406337</v>
+        <v>105.914748427017</v>
       </c>
       <c r="C88" t="n">
         <v>28.596445544594</v>
       </c>
       <c r="D88" t="n">
-        <v>-154.271639008019</v>
+        <v>-154.271639017486</v>
       </c>
     </row>
     <row r="89">
@@ -8449,13 +8449,13 @@
         <v>97</v>
       </c>
       <c r="B89" t="n">
-        <v>108.978538353115</v>
+        <v>108.978538259242</v>
       </c>
       <c r="C89" t="n">
         <v>30.4415467331331</v>
       </c>
       <c r="D89" t="n">
-        <v>-154.271639008019</v>
+        <v>-154.271639017486</v>
       </c>
     </row>
     <row r="90">
@@ -8463,13 +8463,13 @@
         <v>25</v>
       </c>
       <c r="B90" t="n">
-        <v>109.798417888938</v>
+        <v>109.798418004235</v>
       </c>
       <c r="C90" t="n">
         <v>29.785657601326</v>
       </c>
       <c r="D90" t="n">
-        <v>-11.3095789465415</v>
+        <v>-11.3095789497673</v>
       </c>
     </row>
     <row r="91">
@@ -8477,13 +8477,13 @@
         <v>98</v>
       </c>
       <c r="B91" t="n">
-        <v>101.927165993453</v>
+        <v>101.927165992085</v>
       </c>
       <c r="C91" t="n">
         <v>30.0660556110785</v>
       </c>
       <c r="D91" t="n">
-        <v>-11.3095789465415</v>
+        <v>-11.3095789497673</v>
       </c>
     </row>
     <row r="92">
@@ -8491,13 +8491,13 @@
         <v>99</v>
       </c>
       <c r="B92" t="n">
-        <v>101.882083995544</v>
+        <v>101.882083939244</v>
       </c>
       <c r="C92" t="n">
         <v>30.6000332292611</v>
       </c>
       <c r="D92" t="n">
-        <v>-11.3095789465415</v>
+        <v>-11.3095789497673</v>
       </c>
     </row>
     <row r="93">
@@ -8505,13 +8505,13 @@
         <v>100</v>
       </c>
       <c r="B93" t="n">
-        <v>118.072013863319</v>
+        <v>118.072013805692</v>
       </c>
       <c r="C93" t="n">
         <v>33.0579022756853</v>
       </c>
       <c r="D93" t="n">
-        <v>-11.3095789465415</v>
+        <v>-11.3095789497673</v>
       </c>
     </row>
     <row r="94">
@@ -8519,13 +8519,13 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>119.092243528754</v>
+        <v>119.092243460748</v>
       </c>
       <c r="C94" t="n">
-        <v>31.5323192214638</v>
+        <v>31.5323192085143</v>
       </c>
       <c r="D94" t="n">
-        <v>-23.2413491185133</v>
+        <v>-23.2413490803715</v>
       </c>
     </row>
     <row r="95">
@@ -8533,13 +8533,13 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>128.417059157407</v>
+        <v>128.417059160597</v>
       </c>
       <c r="C95" t="n">
-        <v>31.8402897751419</v>
+        <v>31.8402897656666</v>
       </c>
       <c r="D95" t="n">
-        <v>-23.2413491185133</v>
+        <v>-23.2413490803715</v>
       </c>
     </row>
     <row r="96">
@@ -8547,13 +8547,13 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>133.317872744558</v>
+        <v>133.317872771868</v>
       </c>
       <c r="C96" t="n">
-        <v>31.7842500528192</v>
+        <v>31.78425004077</v>
       </c>
       <c r="D96" t="n">
-        <v>-23.2413491185133</v>
+        <v>-23.2413490803715</v>
       </c>
     </row>
     <row r="97">
@@ -8561,13 +8561,13 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>140.504687872877</v>
+        <v>140.504687910385</v>
       </c>
       <c r="C97" t="n">
-        <v>32.6970587688838</v>
+        <v>32.6970587560878</v>
       </c>
       <c r="D97" t="n">
-        <v>-23.2413491185133</v>
+        <v>-23.2413490803715</v>
       </c>
     </row>
     <row r="98">
@@ -8575,13 +8575,13 @@
         <v>104</v>
       </c>
       <c r="B98" t="n">
-        <v>133.817408438996</v>
+        <v>133.817408508508</v>
       </c>
       <c r="C98" t="n">
-        <v>33.5169651606282</v>
+        <v>33.516965146993</v>
       </c>
       <c r="D98" t="n">
-        <v>12.1775983157876</v>
+        <v>12.177598369374</v>
       </c>
     </row>
     <row r="99">
@@ -8589,13 +8589,13 @@
         <v>105</v>
       </c>
       <c r="B99" t="n">
-        <v>132.111554700977</v>
+        <v>132.111554769331</v>
       </c>
       <c r="C99" t="n">
-        <v>33.22436311866</v>
+        <v>33.2243631044807</v>
       </c>
       <c r="D99" t="n">
-        <v>11.7606091359862</v>
+        <v>11.7606091978644</v>
       </c>
     </row>
     <row r="100">
@@ -8603,13 +8603,13 @@
         <v>106</v>
       </c>
       <c r="B100" t="n">
-        <v>131.235261886297</v>
+        <v>131.235261956425</v>
       </c>
       <c r="C100" t="n">
-        <v>33.1427876072489</v>
+        <v>33.142787593281</v>
       </c>
       <c r="D100" t="n">
-        <v>10.9266307763835</v>
+        <v>10.9266308548453</v>
       </c>
     </row>
     <row r="101">
@@ -8617,13 +8617,13 @@
         <v>107</v>
       </c>
       <c r="B101" t="n">
-        <v>137.098998333419</v>
+        <v>137.098998390342</v>
       </c>
       <c r="C101" t="n">
-        <v>34.4462796137029</v>
+        <v>34.4462795982792</v>
       </c>
       <c r="D101" t="n">
-        <v>9.6756632369793</v>
+        <v>9.67566334031663</v>
       </c>
     </row>
     <row r="102">
@@ -8631,13 +8631,13 @@
         <v>108</v>
       </c>
       <c r="B102" t="n">
-        <v>134.845529488576</v>
+        <v>134.845529557187</v>
       </c>
       <c r="C102" t="n">
-        <v>34.1836343729682</v>
+        <v>34.1836343594878</v>
       </c>
       <c r="D102" t="n">
-        <v>8.00770651777375</v>
+        <v>8.00770665427838</v>
       </c>
     </row>
     <row r="103">
@@ -8645,13 +8645,13 @@
         <v>109</v>
       </c>
       <c r="B103" t="n">
-        <v>134.338414251379</v>
+        <v>134.338414299544</v>
       </c>
       <c r="C103" t="n">
-        <v>34.2363371732698</v>
+        <v>34.236337156172</v>
       </c>
       <c r="D103" t="n">
-        <v>6.6241776380312</v>
+        <v>6.62417779757438</v>
       </c>
     </row>
     <row r="104">
@@ -8659,13 +8659,13 @@
         <v>110</v>
       </c>
       <c r="B104" t="n">
-        <v>135.190736454906</v>
+        <v>135.190736500987</v>
       </c>
       <c r="C104" t="n">
-        <v>34.5275319327195</v>
+        <v>34.5275319163994</v>
       </c>
       <c r="D104" t="n">
-        <v>5.52507659775166</v>
+        <v>5.52507677020462</v>
       </c>
     </row>
     <row r="105">
@@ -8673,13 +8673,13 @@
         <v>111</v>
       </c>
       <c r="B105" t="n">
-        <v>142.380036823407</v>
+        <v>142.380036848561</v>
       </c>
       <c r="C105" t="n">
-        <v>36.0459451771383</v>
+        <v>36.0459451595572</v>
       </c>
       <c r="D105" t="n">
-        <v>4.71040339693512</v>
+        <v>4.71040357216911</v>
       </c>
     </row>
     <row r="106">
@@ -8687,13 +8687,13 @@
         <v>112</v>
       </c>
       <c r="B106" t="n">
-        <v>138.39303090417</v>
+        <v>138.393030926402</v>
       </c>
       <c r="C106" t="n">
-        <v>35.31278088015</v>
+        <v>35.3127808632242</v>
       </c>
       <c r="D106" t="n">
-        <v>4.18015803558159</v>
+        <v>4.18015820346785</v>
       </c>
     </row>
     <row r="107">
@@ -8701,13 +8701,13 @@
         <v>113</v>
       </c>
       <c r="B107" t="n">
-        <v>135.937294267995</v>
+        <v>135.937294276144</v>
       </c>
       <c r="C107" t="n">
-        <v>34.8799634722967</v>
+        <v>34.8799634540408</v>
       </c>
       <c r="D107" t="n">
-        <v>3.68436407154196</v>
+        <v>3.68436423194923</v>
       </c>
     </row>
     <row r="108">
@@ -8715,13 +8715,13 @@
         <v>114</v>
       </c>
       <c r="B108" t="n">
-        <v>140.996827414622</v>
+        <v>140.996827404227</v>
       </c>
       <c r="C108" t="n">
-        <v>35.9361401897114</v>
+        <v>35.9361401706202</v>
       </c>
       <c r="D108" t="n">
-        <v>3.22302150481623</v>
+        <v>3.22302165761326</v>
       </c>
     </row>
     <row r="109">
@@ -8729,13 +8729,13 @@
         <v>115</v>
       </c>
       <c r="B109" t="n">
-        <v>148.597529157197</v>
+        <v>148.597529129516</v>
       </c>
       <c r="C109" t="n">
-        <v>37.4932677278757</v>
+        <v>37.493267708625</v>
       </c>
       <c r="D109" t="n">
-        <v>2.79613033540442</v>
+        <v>2.79613048045993</v>
       </c>
     </row>
     <row r="110">
@@ -8743,13 +8743,13 @@
         <v>116</v>
       </c>
       <c r="B110" t="n">
-        <v>145.424658371933</v>
+        <v>145.424658314686</v>
       </c>
       <c r="C110" t="n">
-        <v>36.906538447268</v>
+        <v>36.9065384232864</v>
       </c>
       <c r="D110" t="n">
-        <v>2.4036905633065</v>
+        <v>2.40369070048924</v>
       </c>
     </row>
     <row r="111">
@@ -8757,13 +8757,13 @@
         <v>117</v>
       </c>
       <c r="B111" t="n">
-        <v>146.783397551437</v>
+        <v>146.783397501935</v>
       </c>
       <c r="C111" t="n">
-        <v>37.2145090009642</v>
+        <v>37.2145089804564</v>
       </c>
       <c r="D111" t="n">
-        <v>2.06037648201453</v>
+        <v>2.06037661102588</v>
       </c>
     </row>
     <row r="112">
@@ -8771,13 +8771,13 @@
         <v>118</v>
       </c>
       <c r="B112" t="n">
-        <v>146.337029038678</v>
+        <v>146.337028968607</v>
       </c>
       <c r="C112" t="n">
-        <v>37.1584692786435</v>
+        <v>37.1584692555621</v>
       </c>
       <c r="D112" t="n">
-        <v>1.76618809152852</v>
+        <v>1.76618821206985</v>
       </c>
     </row>
     <row r="113">
@@ -8785,13 +8785,13 @@
         <v>119</v>
       </c>
       <c r="B113" t="n">
-        <v>150.795556416568</v>
+        <v>150.795556330769</v>
       </c>
       <c r="C113" t="n">
-        <v>38.0712779947429</v>
+        <v>38.0712779709145</v>
       </c>
       <c r="D113" t="n">
-        <v>1.52112539184845</v>
+        <v>1.52112550362113</v>
       </c>
     </row>
     <row r="114">
@@ -8799,13 +8799,13 @@
         <v>120</v>
       </c>
       <c r="B114" t="n">
-        <v>154.813813430651</v>
+        <v>154.813813329472</v>
       </c>
       <c r="C114" t="n">
-        <v>38.8911843864894</v>
+        <v>38.891184361822</v>
       </c>
       <c r="D114" t="n">
-        <v>1.32518838297434</v>
+        <v>1.32518848567975</v>
       </c>
     </row>
     <row r="115">
@@ -8813,13 +8813,13 @@
         <v>121</v>
       </c>
       <c r="B115" t="n">
-        <v>153.242682786266</v>
+        <v>153.242682677107</v>
       </c>
       <c r="C115" t="n">
-        <v>38.5985823444912</v>
+        <v>38.5985823192796</v>
       </c>
       <c r="D115" t="n">
-        <v>1.14950480033166</v>
+        <v>1.14950489447478</v>
       </c>
     </row>
     <row r="116">
@@ -8827,13 +8827,13 @@
         <v>122</v>
       </c>
       <c r="B116" t="n">
-        <v>152.745229560669</v>
+        <v>152.745229446805</v>
       </c>
       <c r="C116" t="n">
-        <v>38.5170068331256</v>
+        <v>38.5170068081253</v>
       </c>
       <c r="D116" t="n">
-        <v>0.994074643920439</v>
+        <v>0.99407473000623</v>
       </c>
     </row>
     <row r="117">
@@ -8841,13 +8841,13 @@
         <v>123</v>
       </c>
       <c r="B117" t="n">
-        <v>159.231922091357</v>
+        <v>159.231921958152</v>
       </c>
       <c r="C117" t="n">
-        <v>39.8204988395082</v>
+        <v>39.8204988130522</v>
       </c>
       <c r="D117" t="n">
-        <v>0.858897913740659</v>
+        <v>0.858897992274101</v>
       </c>
     </row>
     <row r="118">
@@ -8855,13 +8855,13 @@
         <v>124</v>
       </c>
       <c r="B118" t="n">
-        <v>157.845525825593</v>
+        <v>157.845525698283</v>
       </c>
       <c r="C118" t="n">
-        <v>39.5578535987905</v>
+        <v>39.5578535742778</v>
       </c>
       <c r="D118" t="n">
-        <v>0.743974609792324</v>
+        <v>0.743974681278393</v>
       </c>
     </row>
     <row r="119">
@@ -8869,13 +8869,13 @@
         <v>125</v>
       </c>
       <c r="B119" t="n">
-        <v>158.053932294574</v>
+        <v>158.053932144022</v>
       </c>
       <c r="C119" t="n">
-        <v>39.6105563991039</v>
+        <v>39.6105563709737</v>
       </c>
       <c r="D119" t="n">
-        <v>0.642032930319371</v>
+        <v>0.64203299521526</v>
       </c>
     </row>
     <row r="120">
@@ -8883,13 +8883,13 @@
         <v>126</v>
       </c>
       <c r="B120" t="n">
-        <v>159.470225331538</v>
+        <v>159.470225179106</v>
       </c>
       <c r="C120" t="n">
-        <v>39.9017511585922</v>
+        <v>39.9017511312398</v>
       </c>
       <c r="D120" t="n">
-        <v>0.553072875321799</v>
+        <v>0.553072934084703</v>
       </c>
     </row>
     <row r="121">
@@ -8897,13 +8897,13 @@
         <v>127</v>
       </c>
       <c r="B121" t="n">
-        <v>167.071945660227</v>
+        <v>167.07194549007</v>
       </c>
       <c r="C121" t="n">
-        <v>41.4201644029753</v>
+        <v>41.4201643743618</v>
       </c>
       <c r="D121" t="n">
-        <v>0.477094444799609</v>
+        <v>0.477094497886721</v>
       </c>
     </row>
     <row r="122">
@@ -8911,13 +8911,13 @@
         <v>128</v>
       </c>
       <c r="B122" t="n">
-        <v>163.345808828451</v>
+        <v>163.345808661573</v>
       </c>
       <c r="C122" t="n">
-        <v>40.6870001059811</v>
+        <v>40.6870000780231</v>
       </c>
       <c r="D122" t="n">
-        <v>0.414097638752801</v>
+        <v>0.414097686621316</v>
       </c>
     </row>
     <row r="123">
@@ -8925,13 +8925,13 @@
         <v>129</v>
       </c>
       <c r="B123" t="n">
-        <v>161.135646323062</v>
+        <v>161.135646148325</v>
       </c>
       <c r="C123" t="n">
-        <v>40.2541826981545</v>
+        <v>40.2541826688663</v>
       </c>
       <c r="D123" t="n">
-        <v>0.35815708498683</v>
+        <v>0.358157128071254</v>
       </c>
     </row>
     <row r="124">
@@ -8939,13 +8939,13 @@
         <v>130</v>
       </c>
       <c r="B124" t="n">
-        <v>166.425458643506</v>
+        <v>166.425458456468</v>
       </c>
       <c r="C124" t="n">
-        <v>41.3103594155696</v>
+        <v>41.3103593854461</v>
       </c>
       <c r="D124" t="n">
-        <v>0.309272783501696</v>
+        <v>0.309272822236535</v>
       </c>
     </row>
     <row r="125">
@@ -8953,13 +8953,13 @@
         <v>131</v>
       </c>
       <c r="B125" t="n">
-        <v>174.24114460297</v>
+        <v>174.241144404913</v>
       </c>
       <c r="C125" t="n">
-        <v>42.8674869537172</v>
+        <v>42.8674869234342</v>
       </c>
       <c r="D125" t="n">
-        <v>0.267444734297398</v>
+        <v>0.267444769117156</v>
       </c>
     </row>
     <row r="126">
@@ -8967,13 +8967,13 @@
         <v>132</v>
       </c>
       <c r="B126" t="n">
-        <v>171.267963077912</v>
+        <v>171.267962856579</v>
       </c>
       <c r="C126" t="n">
-        <v>42.2807576731237</v>
+        <v>42.2807576381096</v>
       </c>
       <c r="D126" t="n">
-        <v>0.232672937373938</v>
+        <v>0.232672968713121</v>
       </c>
     </row>
     <row r="127">
@@ -8981,13 +8981,13 @@
         <v>133</v>
       </c>
       <c r="B127" t="n">
-        <v>172.800699560139</v>
+        <v>172.800699352614</v>
       </c>
       <c r="C127" t="n">
-        <v>42.5887282268286</v>
+        <v>42.5887281952884</v>
       </c>
       <c r="D127" t="n">
-        <v>0.201009381966839</v>
+        <v>0.201009410009712</v>
       </c>
     </row>
     <row r="128">
@@ -8995,13 +8995,13 @@
         <v>134</v>
       </c>
       <c r="B128" t="n">
-        <v>172.5026363925</v>
+        <v>172.502636170248</v>
       </c>
       <c r="C128" t="n">
-        <v>42.532688504488</v>
+        <v>42.5326884703742</v>
       </c>
       <c r="D128" t="n">
-        <v>0.172454068076103</v>
+        <v>0.172454093006929</v>
       </c>
     </row>
     <row r="129">
@@ -9009,13 +9009,13 @@
         <v>135</v>
       </c>
       <c r="B129" t="n">
-        <v>177.083777157946</v>
+        <v>177.083776925583</v>
       </c>
       <c r="C129" t="n">
-        <v>43.4454972205459</v>
+        <v>43.4454971856852</v>
       </c>
       <c r="D129" t="n">
-        <v>0.147006995701728</v>
+        <v>0.147007017704773</v>
       </c>
     </row>
     <row r="130">
@@ -9023,13 +9023,13 @@
         <v>136</v>
       </c>
       <c r="B130" t="n">
-        <v>181.198955602303</v>
+        <v>181.198955359951</v>
       </c>
       <c r="C130" t="n">
-        <v>44.2654036122858</v>
+        <v>44.2654035765857</v>
       </c>
       <c r="D130" t="n">
-        <v>0.124668164843716</v>
+        <v>0.124668184103243</v>
       </c>
     </row>
     <row r="131">
@@ -9037,13 +9037,13 @@
         <v>137</v>
       </c>
       <c r="B131" t="n">
-        <v>179.716556710525</v>
+        <v>179.71655646553</v>
       </c>
       <c r="C131" t="n">
-        <v>43.9728015703475</v>
+        <v>43.9728015341035</v>
       </c>
       <c r="D131" t="n">
-        <v>0.107914041700206</v>
+        <v>0.107914058902096</v>
       </c>
     </row>
     <row r="132">
@@ -9051,13 +9051,13 @@
         <v>138</v>
       </c>
       <c r="B132" t="n">
-        <v>179.299645559048</v>
+        <v>179.299645314628</v>
       </c>
       <c r="C132" t="n">
-        <v>43.8912260589448</v>
+        <v>43.8912260229122</v>
       </c>
       <c r="D132" t="n">
-        <v>0.0967446262712</v>
+        <v>0.0967446421013306</v>
       </c>
     </row>
     <row r="133">
@@ -9065,13 +9065,13 @@
         <v>139</v>
       </c>
       <c r="B133" t="n">
-        <v>185.858690486248</v>
+        <v>185.858690227711</v>
       </c>
       <c r="C133" t="n">
-        <v>45.1947180653687</v>
+        <v>45.1947180278802</v>
       </c>
       <c r="D133" t="n">
-        <v>0.091159918556697</v>
+        <v>0.091159933700948</v>
       </c>
     </row>
   </sheetData>
@@ -9098,7 +9098,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>20.6875840798076</v>
+        <v>20.6875840988558</v>
       </c>
     </row>
     <row r="3">
@@ -9106,7 +9106,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>23.6156277832207</v>
+        <v>23.6156277935456</v>
       </c>
     </row>
     <row r="4">
@@ -9114,7 +9114,7 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>24.780255458371</v>
+        <v>24.7802554557865</v>
       </c>
     </row>
     <row r="5">
@@ -9122,7 +9122,7 @@
         <v>34</v>
       </c>
       <c r="B5" t="n">
-        <v>31.5314128818406</v>
+        <v>31.5314128550522</v>
       </c>
     </row>
     <row r="6">
@@ -9130,7 +9130,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.9874279549276</v>
+        <v>31.9874279792772</v>
       </c>
     </row>
     <row r="7">
@@ -9138,7 +9138,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>31.3417025275023</v>
+        <v>31.3417025320769</v>
       </c>
     </row>
     <row r="8">
@@ -9146,7 +9146,7 @@
         <v>36</v>
       </c>
       <c r="B8" t="n">
-        <v>27.5352880154357</v>
+        <v>27.5352880064589</v>
       </c>
     </row>
     <row r="9">
@@ -9154,7 +9154,7 @@
         <v>37</v>
       </c>
       <c r="B9" t="n">
-        <v>24.3342303489197</v>
+        <v>24.3342303289728</v>
       </c>
     </row>
     <row r="10">
@@ -9162,7 +9162,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>31.6762006962695</v>
+        <v>31.6762006959562</v>
       </c>
     </row>
     <row r="11">
@@ -9170,7 +9170,7 @@
         <v>38</v>
       </c>
       <c r="B11" t="n">
-        <v>33.2054595657092</v>
+        <v>33.2054595600762</v>
       </c>
     </row>
     <row r="12">
@@ -9178,7 +9178,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>31.0837435109751</v>
+        <v>31.0837435106118</v>
       </c>
     </row>
     <row r="13">
@@ -9186,7 +9186,7 @@
         <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>34.8087822948793</v>
+        <v>34.8087823011896</v>
       </c>
     </row>
     <row r="14">
@@ -9194,7 +9194,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>31.1390943604829</v>
+        <v>31.1390943073377</v>
       </c>
     </row>
     <row r="15">
@@ -9202,7 +9202,7 @@
         <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>32.0187454759667</v>
+        <v>32.0187454466014</v>
       </c>
     </row>
     <row r="16">
@@ -9210,7 +9210,7 @@
         <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>12.1129621836542</v>
+        <v>12.1129622054669</v>
       </c>
     </row>
     <row r="17">
@@ -9218,7 +9218,7 @@
         <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>12.4617020955333</v>
+        <v>12.4617021562317</v>
       </c>
     </row>
     <row r="18">
@@ -9226,7 +9226,7 @@
         <v>7</v>
       </c>
       <c r="B18" t="n">
-        <v>30.0386256741338</v>
+        <v>30.0386256521418</v>
       </c>
     </row>
     <row r="19">
@@ -9234,7 +9234,7 @@
         <v>44</v>
       </c>
       <c r="B19" t="n">
-        <v>30.3042545238644</v>
+        <v>30.3042545283106</v>
       </c>
     </row>
     <row r="20">
@@ -9242,7 +9242,7 @@
         <v>45</v>
       </c>
       <c r="B20" t="n">
-        <v>25.5451962654351</v>
+        <v>25.545196281355</v>
       </c>
     </row>
     <row r="21">
@@ -9250,7 +9250,7 @@
         <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>26.931948577918</v>
+        <v>26.931948579544</v>
       </c>
     </row>
     <row r="22">
@@ -9258,7 +9258,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>27.1606021076845</v>
+        <v>27.1606021175457</v>
       </c>
     </row>
     <row r="23">
@@ -9266,7 +9266,7 @@
         <v>47</v>
       </c>
       <c r="B23" t="n">
-        <v>27.3810358410094</v>
+        <v>27.3810358332759</v>
       </c>
     </row>
     <row r="24">
@@ -9274,7 +9274,7 @@
         <v>48</v>
       </c>
       <c r="B24" t="n">
-        <v>26.3375806321254</v>
+        <v>26.3375806234145</v>
       </c>
     </row>
     <row r="25">
@@ -9282,7 +9282,7 @@
         <v>49</v>
       </c>
       <c r="B25" t="n">
-        <v>24.3874512616519</v>
+        <v>24.3874512682357</v>
       </c>
     </row>
     <row r="26">
@@ -9290,7 +9290,7 @@
         <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>19.7741818499806</v>
+        <v>19.7741818258663</v>
       </c>
     </row>
     <row r="27">
@@ -9298,7 +9298,7 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>21.047014886685</v>
+        <v>21.0470148834192</v>
       </c>
     </row>
     <row r="28">
@@ -9306,7 +9306,7 @@
         <v>51</v>
       </c>
       <c r="B28" t="n">
-        <v>22.6532668257199</v>
+        <v>22.6532668362559</v>
       </c>
     </row>
     <row r="29">
@@ -9314,7 +9314,7 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>25.0539467561409</v>
+        <v>25.0539467729859</v>
       </c>
     </row>
     <row r="30">
@@ -9322,7 +9322,7 @@
         <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>28.8509564334777</v>
+        <v>28.8509564281329</v>
       </c>
     </row>
     <row r="31">
@@ -9330,7 +9330,7 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>21.9389533859392</v>
+        <v>21.9389533889704</v>
       </c>
     </row>
     <row r="32">
@@ -9338,7 +9338,7 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>23.0159070500761</v>
+        <v>23.0159070535421</v>
       </c>
     </row>
     <row r="33">
@@ -9346,7 +9346,7 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>29.0946804022551</v>
+        <v>29.0946804011035</v>
       </c>
     </row>
     <row r="34">
@@ -9354,7 +9354,7 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>26.8707871080478</v>
+        <v>26.8707870985463</v>
       </c>
     </row>
     <row r="35">
@@ -9362,7 +9362,7 @@
         <v>56</v>
       </c>
       <c r="B35" t="n">
-        <v>22.2986456920337</v>
+        <v>22.2986456904723</v>
       </c>
     </row>
     <row r="36">
@@ -9370,7 +9370,7 @@
         <v>57</v>
       </c>
       <c r="B36" t="n">
-        <v>23.9748997241839</v>
+        <v>23.9748997269921</v>
       </c>
     </row>
     <row r="37">
@@ -9378,7 +9378,7 @@
         <v>58</v>
       </c>
       <c r="B37" t="n">
-        <v>27.0931637675933</v>
+        <v>27.0931637758488</v>
       </c>
     </row>
     <row r="38">
@@ -9386,7 +9386,7 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>21.5679220723922</v>
+        <v>21.5679220623213</v>
       </c>
     </row>
     <row r="39">
@@ -9394,7 +9394,7 @@
         <v>59</v>
       </c>
       <c r="B39" t="n">
-        <v>21.857234976307</v>
+        <v>21.8572349752125</v>
       </c>
     </row>
     <row r="40">
@@ -9402,7 +9402,7 @@
         <v>60</v>
       </c>
       <c r="B40" t="n">
-        <v>22.4949303293213</v>
+        <v>22.4949303351873</v>
       </c>
     </row>
     <row r="41">
@@ -9410,7 +9410,7 @@
         <v>61</v>
       </c>
       <c r="B41" t="n">
-        <v>29.1788866827235</v>
+        <v>29.1788866880237</v>
       </c>
     </row>
     <row r="42">
@@ -9418,7 +9418,7 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>24.3979251360161</v>
+        <v>24.3979251360919</v>
       </c>
     </row>
     <row r="43">
@@ -9426,7 +9426,7 @@
         <v>62</v>
       </c>
       <c r="B43" t="n">
-        <v>23.2518287419084</v>
+        <v>23.2518287463601</v>
       </c>
     </row>
     <row r="44">
@@ -9434,7 +9434,7 @@
         <v>63</v>
       </c>
       <c r="B44" t="n">
-        <v>30.0873798795504</v>
+        <v>30.0873798797072</v>
       </c>
     </row>
     <row r="45">
@@ -9442,7 +9442,7 @@
         <v>64</v>
       </c>
       <c r="B45" t="n">
-        <v>36.502908357026</v>
+        <v>36.5029083523424</v>
       </c>
     </row>
     <row r="46">
@@ -9450,7 +9450,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>36.3831808324847</v>
+        <v>36.3831808357755</v>
       </c>
     </row>
     <row r="47">
@@ -9458,7 +9458,7 @@
         <v>65</v>
       </c>
       <c r="B47" t="n">
-        <v>30.7644641690533</v>
+        <v>30.7644641754221</v>
       </c>
     </row>
     <row r="48">
@@ -9466,7 +9466,7 @@
         <v>66</v>
       </c>
       <c r="B48" t="n">
-        <v>33.0774352178172</v>
+        <v>33.0774352168248</v>
       </c>
     </row>
     <row r="49">
@@ -9474,7 +9474,7 @@
         <v>67</v>
       </c>
       <c r="B49" t="n">
-        <v>32.8512547686927</v>
+        <v>32.8512547600265</v>
       </c>
     </row>
     <row r="50">
@@ -9482,7 +9482,7 @@
         <v>15</v>
       </c>
       <c r="B50" t="n">
-        <v>41.4082897100689</v>
+        <v>41.4082897045338</v>
       </c>
     </row>
     <row r="51">
@@ -9490,7 +9490,7 @@
         <v>68</v>
       </c>
       <c r="B51" t="n">
-        <v>38.9348356320134</v>
+        <v>38.9348356262708</v>
       </c>
     </row>
     <row r="52">
@@ -9498,7 +9498,7 @@
         <v>69</v>
       </c>
       <c r="B52" t="n">
-        <v>38.1956630157084</v>
+        <v>38.1956630161423</v>
       </c>
     </row>
     <row r="53">
@@ -9506,7 +9506,7 @@
         <v>70</v>
       </c>
       <c r="B53" t="n">
-        <v>41.4131278582436</v>
+        <v>41.4131278690887</v>
       </c>
     </row>
     <row r="54">
@@ -9514,7 +9514,7 @@
         <v>16</v>
       </c>
       <c r="B54" t="n">
-        <v>38.2534232244561</v>
+        <v>38.2534232136571</v>
       </c>
     </row>
     <row r="55">
@@ -9522,7 +9522,7 @@
         <v>71</v>
       </c>
       <c r="B55" t="n">
-        <v>37.8939094547667</v>
+        <v>37.8939094606533</v>
       </c>
     </row>
     <row r="56">
@@ -9530,7 +9530,7 @@
         <v>72</v>
       </c>
       <c r="B56" t="n">
-        <v>48.5782573381608</v>
+        <v>48.5782573448062</v>
       </c>
     </row>
     <row r="57">
@@ -9538,7 +9538,7 @@
         <v>73</v>
       </c>
       <c r="B57" t="n">
-        <v>63.2845487922885</v>
+        <v>63.2845487905568</v>
       </c>
     </row>
     <row r="58">
@@ -9546,7 +9546,7 @@
         <v>17</v>
       </c>
       <c r="B58" t="n">
-        <v>33.0273772085754</v>
+        <v>33.0273772250828</v>
       </c>
     </row>
     <row r="59">
@@ -9554,7 +9554,7 @@
         <v>74</v>
       </c>
       <c r="B59" t="n">
-        <v>30.1554841459168</v>
+        <v>30.1554841622047</v>
       </c>
     </row>
     <row r="60">
@@ -9562,7 +9562,7 @@
         <v>75</v>
       </c>
       <c r="B60" t="n">
-        <v>45.1995417181122</v>
+        <v>45.1995417132577</v>
       </c>
     </row>
     <row r="61">
@@ -9570,7 +9570,7 @@
         <v>76</v>
       </c>
       <c r="B61" t="n">
-        <v>58.5337949706745</v>
+        <v>58.5337949427349</v>
       </c>
     </row>
     <row r="62">
@@ -9578,7 +9578,7 @@
         <v>18</v>
       </c>
       <c r="B62" t="n">
-        <v>76.4676936763679</v>
+        <v>76.467693764484</v>
       </c>
     </row>
     <row r="63">
@@ -9586,7 +9586,7 @@
         <v>77</v>
       </c>
       <c r="B63" t="n">
-        <v>83.9473561150473</v>
+        <v>83.9473561624335</v>
       </c>
     </row>
     <row r="64">
@@ -9594,7 +9594,7 @@
         <v>78</v>
       </c>
       <c r="B64" t="n">
-        <v>99.023715463205</v>
+        <v>99.0237154428039</v>
       </c>
     </row>
     <row r="65">
@@ -9602,7 +9602,7 @@
         <v>79</v>
       </c>
       <c r="B65" t="n">
-        <v>121.546117430299</v>
+        <v>121.546117315199</v>
       </c>
     </row>
     <row r="66">
@@ -9610,7 +9610,7 @@
         <v>19</v>
       </c>
       <c r="B66" t="n">
-        <v>160.901549836884</v>
+        <v>160.901550056842</v>
       </c>
     </row>
     <row r="67">
@@ -9618,7 +9618,7 @@
         <v>80</v>
       </c>
       <c r="B67" t="n">
-        <v>165.469734754496</v>
+        <v>165.469734845311</v>
       </c>
     </row>
     <row r="68">
@@ -9626,7 +9626,7 @@
         <v>81</v>
       </c>
       <c r="B68" t="n">
-        <v>158.968321702106</v>
+        <v>158.968321642388</v>
       </c>
     </row>
     <row r="69">
@@ -9634,7 +9634,7 @@
         <v>82</v>
       </c>
       <c r="B69" t="n">
-        <v>161.467338736695</v>
+        <v>161.467338485642</v>
       </c>
     </row>
     <row r="70">
@@ -9642,7 +9642,7 @@
         <v>20</v>
       </c>
       <c r="B70" t="n">
-        <v>187.728716203127</v>
+        <v>187.728716371811</v>
       </c>
     </row>
     <row r="71">
@@ -9650,7 +9650,7 @@
         <v>83</v>
       </c>
       <c r="B71" t="n">
-        <v>169.283476147334</v>
+        <v>169.283476164101</v>
       </c>
     </row>
     <row r="72">
@@ -9658,7 +9658,7 @@
         <v>84</v>
       </c>
       <c r="B72" t="n">
-        <v>134.068610927559</v>
+        <v>134.068610859889</v>
       </c>
     </row>
     <row r="73">
@@ -9666,7 +9666,7 @@
         <v>85</v>
       </c>
       <c r="B73" t="n">
-        <v>116.360281213173</v>
+        <v>116.360281095393</v>
       </c>
     </row>
     <row r="74">
@@ -9674,7 +9674,7 @@
         <v>21</v>
       </c>
       <c r="B74" t="n">
-        <v>66.1439665335733</v>
+        <v>66.1439662624607</v>
       </c>
     </row>
     <row r="75">
@@ -9682,7 +9682,7 @@
         <v>86</v>
       </c>
       <c r="B75" t="n">
-        <v>43.577114053786</v>
+        <v>43.5771139041173</v>
       </c>
     </row>
     <row r="76">
@@ -9690,7 +9690,7 @@
         <v>87</v>
       </c>
       <c r="B76" t="n">
-        <v>51.1370684661875</v>
+        <v>51.137068524421</v>
       </c>
     </row>
     <row r="77">
@@ -9698,7 +9698,7 @@
         <v>88</v>
       </c>
       <c r="B77" t="n">
-        <v>78.5308509464521</v>
+        <v>78.5308513090006</v>
       </c>
     </row>
     <row r="78">
@@ -9706,7 +9706,7 @@
         <v>22</v>
       </c>
       <c r="B78" t="n">
-        <v>46.7044265624819</v>
+        <v>46.7044262800641</v>
       </c>
     </row>
     <row r="79">
@@ -9714,7 +9714,7 @@
         <v>89</v>
       </c>
       <c r="B79" t="n">
-        <v>70.2604052162952</v>
+        <v>70.2604052136151</v>
       </c>
     </row>
     <row r="80">
@@ -9722,7 +9722,7 @@
         <v>90</v>
       </c>
       <c r="B80" t="n">
-        <v>91.1800411724877</v>
+        <v>91.1800413082116</v>
       </c>
     </row>
     <row r="81">
@@ -9730,7 +9730,7 @@
         <v>91</v>
       </c>
       <c r="B81" t="n">
-        <v>92.319127048734</v>
+        <v>92.3191271981088</v>
       </c>
     </row>
     <row r="82">
@@ -9738,7 +9738,7 @@
         <v>23</v>
       </c>
       <c r="B82" t="n">
-        <v>62.1561204207402</v>
+        <v>62.1561204504143</v>
       </c>
     </row>
     <row r="83">
@@ -9746,7 +9746,7 @@
         <v>92</v>
       </c>
       <c r="B83" t="n">
-        <v>50.635007887796</v>
+        <v>50.6350078653609</v>
       </c>
     </row>
     <row r="84">
@@ -9754,7 +9754,7 @@
         <v>93</v>
       </c>
       <c r="B84" t="n">
-        <v>57.474250528508</v>
+        <v>57.4742505020865</v>
       </c>
     </row>
     <row r="85">
@@ -9762,7 +9762,7 @@
         <v>94</v>
       </c>
       <c r="B85" t="n">
-        <v>81.1554620076049</v>
+        <v>81.1554620267882</v>
       </c>
     </row>
     <row r="86">
@@ -9770,7 +9770,7 @@
         <v>24</v>
       </c>
       <c r="B86" t="n">
-        <v>88.5327091217904</v>
+        <v>88.5327091364836</v>
       </c>
     </row>
     <row r="87">
@@ -9778,7 +9778,7 @@
         <v>95</v>
       </c>
       <c r="B87" t="n">
-        <v>97.4110944161112</v>
+        <v>97.4110944746124</v>
       </c>
     </row>
     <row r="88">
@@ -9786,7 +9786,7 @@
         <v>96</v>
       </c>
       <c r="B88" t="n">
-        <v>105.914748406337</v>
+        <v>105.914748427017</v>
       </c>
     </row>
     <row r="89">
@@ -9794,7 +9794,7 @@
         <v>97</v>
       </c>
       <c r="B89" t="n">
-        <v>108.978538353115</v>
+        <v>108.978538259242</v>
       </c>
     </row>
     <row r="90">
@@ -9802,7 +9802,7 @@
         <v>25</v>
       </c>
       <c r="B90" t="n">
-        <v>109.798417888938</v>
+        <v>109.798418004235</v>
       </c>
     </row>
     <row r="91">
@@ -9810,7 +9810,7 @@
         <v>98</v>
       </c>
       <c r="B91" t="n">
-        <v>101.927165993453</v>
+        <v>101.927165992085</v>
       </c>
     </row>
     <row r="92">
@@ -9818,7 +9818,7 @@
         <v>99</v>
       </c>
       <c r="B92" t="n">
-        <v>101.882083995544</v>
+        <v>101.882083939244</v>
       </c>
     </row>
     <row r="93">
@@ -9826,7 +9826,7 @@
         <v>100</v>
       </c>
       <c r="B93" t="n">
-        <v>118.072013863319</v>
+        <v>118.072013805692</v>
       </c>
     </row>
     <row r="94">
@@ -9834,7 +9834,7 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>119.092243528754</v>
+        <v>119.092243460748</v>
       </c>
     </row>
     <row r="95">
@@ -9842,7 +9842,7 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>128.417059157407</v>
+        <v>128.417059160597</v>
       </c>
     </row>
     <row r="96">
@@ -9850,7 +9850,7 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>133.317872744558</v>
+        <v>133.317872771868</v>
       </c>
     </row>
     <row r="97">
@@ -9858,7 +9858,7 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>140.504687872877</v>
+        <v>140.504687910385</v>
       </c>
     </row>
     <row r="98">
@@ -9866,7 +9866,7 @@
         <v>104</v>
       </c>
       <c r="B98" t="n">
-        <v>133.817408438996</v>
+        <v>133.817408508508</v>
       </c>
     </row>
     <row r="99">
@@ -9874,7 +9874,7 @@
         <v>105</v>
       </c>
       <c r="B99" t="n">
-        <v>132.111554700977</v>
+        <v>132.111554769331</v>
       </c>
     </row>
     <row r="100">
@@ -9882,7 +9882,7 @@
         <v>106</v>
       </c>
       <c r="B100" t="n">
-        <v>131.235261886297</v>
+        <v>131.235261956425</v>
       </c>
     </row>
     <row r="101">
@@ -9890,7 +9890,7 @@
         <v>107</v>
       </c>
       <c r="B101" t="n">
-        <v>137.098998333419</v>
+        <v>137.098998390342</v>
       </c>
     </row>
     <row r="102">
@@ -9898,7 +9898,7 @@
         <v>108</v>
       </c>
       <c r="B102" t="n">
-        <v>134.845529488576</v>
+        <v>134.845529557187</v>
       </c>
     </row>
     <row r="103">
@@ -9906,7 +9906,7 @@
         <v>109</v>
       </c>
       <c r="B103" t="n">
-        <v>134.338414251379</v>
+        <v>134.338414299544</v>
       </c>
     </row>
     <row r="104">
@@ -9914,7 +9914,7 @@
         <v>110</v>
       </c>
       <c r="B104" t="n">
-        <v>135.190736454906</v>
+        <v>135.190736500987</v>
       </c>
     </row>
     <row r="105">
@@ -9922,7 +9922,7 @@
         <v>111</v>
       </c>
       <c r="B105" t="n">
-        <v>142.380036823407</v>
+        <v>142.380036848561</v>
       </c>
     </row>
     <row r="106">
@@ -9930,7 +9930,7 @@
         <v>112</v>
       </c>
       <c r="B106" t="n">
-        <v>138.39303090417</v>
+        <v>138.393030926402</v>
       </c>
     </row>
     <row r="107">
@@ -9938,7 +9938,7 @@
         <v>113</v>
       </c>
       <c r="B107" t="n">
-        <v>135.937294267995</v>
+        <v>135.937294276144</v>
       </c>
     </row>
     <row r="108">
@@ -9946,7 +9946,7 @@
         <v>114</v>
       </c>
       <c r="B108" t="n">
-        <v>140.996827414622</v>
+        <v>140.996827404227</v>
       </c>
     </row>
     <row r="109">
@@ -9954,7 +9954,7 @@
         <v>115</v>
       </c>
       <c r="B109" t="n">
-        <v>148.597529157197</v>
+        <v>148.597529129516</v>
       </c>
     </row>
     <row r="110">
@@ -9962,7 +9962,7 @@
         <v>116</v>
       </c>
       <c r="B110" t="n">
-        <v>145.424658371933</v>
+        <v>145.424658314686</v>
       </c>
     </row>
     <row r="111">
@@ -9970,7 +9970,7 @@
         <v>117</v>
       </c>
       <c r="B111" t="n">
-        <v>146.783397551437</v>
+        <v>146.783397501935</v>
       </c>
     </row>
     <row r="112">
@@ -9978,7 +9978,7 @@
         <v>118</v>
       </c>
       <c r="B112" t="n">
-        <v>146.337029038678</v>
+        <v>146.337028968607</v>
       </c>
     </row>
     <row r="113">
@@ -9986,7 +9986,7 @@
         <v>119</v>
       </c>
       <c r="B113" t="n">
-        <v>150.795556416568</v>
+        <v>150.795556330769</v>
       </c>
     </row>
     <row r="114">
@@ -9994,7 +9994,7 @@
         <v>120</v>
       </c>
       <c r="B114" t="n">
-        <v>154.813813430651</v>
+        <v>154.813813329472</v>
       </c>
     </row>
     <row r="115">
@@ -10002,7 +10002,7 @@
         <v>121</v>
       </c>
       <c r="B115" t="n">
-        <v>153.242682786266</v>
+        <v>153.242682677107</v>
       </c>
     </row>
     <row r="116">
@@ -10010,7 +10010,7 @@
         <v>122</v>
       </c>
       <c r="B116" t="n">
-        <v>152.745229560669</v>
+        <v>152.745229446805</v>
       </c>
     </row>
     <row r="117">
@@ -10018,7 +10018,7 @@
         <v>123</v>
       </c>
       <c r="B117" t="n">
-        <v>159.231922091357</v>
+        <v>159.231921958152</v>
       </c>
     </row>
     <row r="118">
@@ -10026,7 +10026,7 @@
         <v>124</v>
       </c>
       <c r="B118" t="n">
-        <v>157.845525825593</v>
+        <v>157.845525698283</v>
       </c>
     </row>
     <row r="119">
@@ -10034,7 +10034,7 @@
         <v>125</v>
       </c>
       <c r="B119" t="n">
-        <v>158.053932294574</v>
+        <v>158.053932144022</v>
       </c>
     </row>
     <row r="120">
@@ -10042,7 +10042,7 @@
         <v>126</v>
       </c>
       <c r="B120" t="n">
-        <v>159.470225331538</v>
+        <v>159.470225179106</v>
       </c>
     </row>
     <row r="121">
@@ -10050,7 +10050,7 @@
         <v>127</v>
       </c>
       <c r="B121" t="n">
-        <v>167.071945660227</v>
+        <v>167.07194549007</v>
       </c>
     </row>
     <row r="122">
@@ -10058,7 +10058,7 @@
         <v>128</v>
       </c>
       <c r="B122" t="n">
-        <v>163.345808828451</v>
+        <v>163.345808661573</v>
       </c>
     </row>
     <row r="123">
@@ -10066,7 +10066,7 @@
         <v>129</v>
       </c>
       <c r="B123" t="n">
-        <v>161.135646323062</v>
+        <v>161.135646148325</v>
       </c>
     </row>
     <row r="124">
@@ -10074,7 +10074,7 @@
         <v>130</v>
       </c>
       <c r="B124" t="n">
-        <v>166.425458643506</v>
+        <v>166.425458456468</v>
       </c>
     </row>
     <row r="125">
@@ -10082,7 +10082,7 @@
         <v>131</v>
       </c>
       <c r="B125" t="n">
-        <v>174.24114460297</v>
+        <v>174.241144404913</v>
       </c>
     </row>
     <row r="126">
@@ -10090,7 +10090,7 @@
         <v>132</v>
       </c>
       <c r="B126" t="n">
-        <v>171.267963077912</v>
+        <v>171.267962856579</v>
       </c>
     </row>
     <row r="127">
@@ -10098,7 +10098,7 @@
         <v>133</v>
       </c>
       <c r="B127" t="n">
-        <v>172.800699560139</v>
+        <v>172.800699352614</v>
       </c>
     </row>
     <row r="128">
@@ -10106,7 +10106,7 @@
         <v>134</v>
       </c>
       <c r="B128" t="n">
-        <v>172.5026363925</v>
+        <v>172.502636170248</v>
       </c>
     </row>
     <row r="129">
@@ -10114,7 +10114,7 @@
         <v>135</v>
       </c>
       <c r="B129" t="n">
-        <v>177.083777157946</v>
+        <v>177.083776925583</v>
       </c>
     </row>
     <row r="130">
@@ -10122,7 +10122,7 @@
         <v>136</v>
       </c>
       <c r="B130" t="n">
-        <v>181.198955602303</v>
+        <v>181.198955359951</v>
       </c>
     </row>
     <row r="131">
@@ -10130,7 +10130,7 @@
         <v>137</v>
       </c>
       <c r="B131" t="n">
-        <v>179.716556710525</v>
+        <v>179.71655646553</v>
       </c>
     </row>
     <row r="132">
@@ -10138,7 +10138,7 @@
         <v>138</v>
       </c>
       <c r="B132" t="n">
-        <v>179.299645559048</v>
+        <v>179.299645314628</v>
       </c>
     </row>
     <row r="133">
@@ -10146,7 +10146,7 @@
         <v>139</v>
       </c>
       <c r="B133" t="n">
-        <v>185.858690486248</v>
+        <v>185.858690227711</v>
       </c>
     </row>
   </sheetData>
